--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="668">
   <si>
     <t>Denumire client</t>
   </si>
@@ -2612,15 +2612,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E464"/>
+  <dimension ref="A1:F464"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42.42578125" style="1" customWidth="1"/>
-    <col min="2" max="5" width="8.85546875" style="8"/>
-    <col min="6" max="16384" width="8.85546875" style="1"/>
+    <col min="2" max="6" width="15.7109375" style="8" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2636,8 +2636,11 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2653,8 +2656,11 @@
       <c r="E2" s="5">
         <v>524.65</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="5">
+        <v>524.65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2670,8 +2676,11 @@
       <c r="E3" s="6">
         <v>1536.44</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="6">
+        <v>1536.44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2696,11 @@
       <c r="E4" s="6">
         <v>2508.38</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="6">
+        <v>2508.38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -2704,8 +2716,11 @@
       <c r="E5" s="5">
         <v>483.88</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="5">
+        <v>483.88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -2721,8 +2736,11 @@
       <c r="E6" s="5">
         <v>287.20999999999998</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="5">
+        <v>287.20999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -2738,8 +2756,11 @@
       <c r="E7" s="6">
         <v>1321.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="6">
+        <v>1321.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2755,8 +2776,11 @@
       <c r="E8" s="6">
         <v>1825.31</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="6">
+        <v>1825.31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2796,11 @@
       <c r="E9" s="5">
         <v>761.15</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="5">
+        <v>761.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -2789,8 +2816,11 @@
       <c r="E10" s="6">
         <v>1144.98</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="6">
+        <v>1144.98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -2806,8 +2836,11 @@
       <c r="E11" s="6">
         <v>2387.75</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="6">
+        <v>2387.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -2823,8 +2856,11 @@
       <c r="E12" s="6">
         <v>1990.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="6">
+        <v>1990.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -2840,8 +2876,11 @@
       <c r="E13" s="5">
         <v>438.87</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="5">
+        <v>438.87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2857,8 +2896,11 @@
       <c r="E14" s="5">
         <v>376.22</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="5">
+        <v>376.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -2874,8 +2916,11 @@
       <c r="E15" s="5">
         <v>790.79</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="5">
+        <v>790.79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -2891,8 +2936,11 @@
       <c r="E16" s="6">
         <v>1938.46</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="6">
+        <v>1938.46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
@@ -2908,8 +2956,11 @@
       <c r="E17" s="5">
         <v>245.39</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="5">
+        <v>245.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -2925,8 +2976,11 @@
       <c r="E18" s="5">
         <v>345.12</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="5">
+        <v>345.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -2942,8 +2996,11 @@
       <c r="E19" s="5">
         <v>936.33</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="5">
+        <v>936.33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
@@ -2959,8 +3016,11 @@
       <c r="E20" s="5">
         <v>358.71</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="5">
+        <v>358.71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
@@ -2976,8 +3036,11 @@
       <c r="E21" s="6">
         <v>1749</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="6">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="E22" s="5">
         <v>371.24</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="5">
+        <v>371.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
@@ -3010,8 +3076,11 @@
       <c r="E23" s="5">
         <v>149.44</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="5">
+        <v>149.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>33</v>
       </c>
@@ -3027,8 +3096,11 @@
       <c r="E24" s="5">
         <v>250.83</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="5">
+        <v>250.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -3044,8 +3116,11 @@
       <c r="E25" s="5">
         <v>177.94</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="5">
+        <v>177.94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>37</v>
       </c>
@@ -3061,8 +3136,11 @@
       <c r="E26" s="5">
         <v>393.18</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="5">
+        <v>393.18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
@@ -3078,8 +3156,11 @@
       <c r="E27" s="6">
         <v>1311.16</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="6">
+        <v>1311.16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -3095,8 +3176,11 @@
       <c r="E28" s="5">
         <v>109.38</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="5">
+        <v>109.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>37</v>
       </c>
@@ -3112,8 +3196,11 @@
       <c r="E29" s="6">
         <v>1961.14</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="6">
+        <v>1961.14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
         <v>37</v>
       </c>
@@ -3129,8 +3216,11 @@
       <c r="E30" s="6">
         <v>1140.42</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="6">
+        <v>1140.42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
         <v>37</v>
       </c>
@@ -3146,8 +3236,11 @@
       <c r="E31" s="5">
         <v>607.47</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="5">
+        <v>607.47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
@@ -3163,8 +3256,11 @@
       <c r="E32" s="5">
         <v>581.70000000000005</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="5">
+        <v>581.70000000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
@@ -3180,8 +3276,11 @@
       <c r="E33" s="6">
         <v>4322.8500000000004</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="6">
+        <v>4322.8500000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
         <v>51</v>
       </c>
@@ -3197,8 +3296,11 @@
       <c r="E34" s="6">
         <v>3684.3</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="6">
+        <v>3684.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
         <v>51</v>
       </c>
@@ -3214,8 +3316,11 @@
       <c r="E35" s="6">
         <v>1001.25</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="6">
+        <v>1001.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
         <v>51</v>
       </c>
@@ -3231,8 +3336,11 @@
       <c r="E36" s="6">
         <v>1001.25</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="6">
+        <v>1001.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
         <v>51</v>
       </c>
@@ -3248,8 +3356,11 @@
       <c r="E37" s="6">
         <v>1219.4000000000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="6">
+        <v>1219.4000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>51</v>
       </c>
@@ -3265,8 +3376,11 @@
       <c r="E38" s="6">
         <v>8524.73</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="6">
+        <v>8524.73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
         <v>57</v>
       </c>
@@ -3282,8 +3396,11 @@
       <c r="E39" s="5">
         <v>158.12</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="5">
+        <v>158.12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
         <v>57</v>
       </c>
@@ -3299,8 +3416,11 @@
       <c r="E40" s="6">
         <v>1260.6600000000001</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="6">
+        <v>1260.6600000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
         <v>57</v>
       </c>
@@ -3316,8 +3436,11 @@
       <c r="E41" s="5">
         <v>972.6</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="5">
+        <v>972.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
         <v>57</v>
       </c>
@@ -3333,8 +3456,11 @@
       <c r="E42" s="5">
         <v>911.42</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="5">
+        <v>911.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
         <v>57</v>
       </c>
@@ -3350,8 +3476,11 @@
       <c r="E43" s="6">
         <v>1237.92</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" s="6">
+        <v>1237.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
         <v>63</v>
       </c>
@@ -3367,8 +3496,11 @@
       <c r="E44" s="5">
         <v>572.84</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" s="5">
+        <v>572.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
         <v>63</v>
       </c>
@@ -3384,8 +3516,11 @@
       <c r="E45" s="6">
         <v>1127.1600000000001</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" s="6">
+        <v>1127.1600000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
         <v>63</v>
       </c>
@@ -3401,8 +3536,11 @@
       <c r="E46" s="5">
         <v>455.71</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="5">
+        <v>455.71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
         <v>69</v>
       </c>
@@ -3418,8 +3556,11 @@
       <c r="E47" s="6">
         <v>1787.54</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="6">
+        <v>1787.54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
         <v>70</v>
       </c>
@@ -3435,8 +3576,11 @@
       <c r="E48" s="5">
         <v>774.25</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" s="5">
+        <v>774.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
         <v>70</v>
       </c>
@@ -3452,8 +3596,11 @@
       <c r="E49" s="5">
         <v>493.77</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="5">
+        <v>493.77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
         <v>70</v>
       </c>
@@ -3469,8 +3616,11 @@
       <c r="E50" s="5">
         <v>527.75</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" s="5">
+        <v>527.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
         <v>73</v>
       </c>
@@ -3486,8 +3636,11 @@
       <c r="E51" s="5">
         <v>892.34</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" s="5">
+        <v>892.34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
         <v>73</v>
       </c>
@@ -3503,8 +3656,11 @@
       <c r="E52" s="5">
         <v>768.39</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" s="5">
+        <v>768.39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="2" t="s">
         <v>73</v>
       </c>
@@ -3520,8 +3676,11 @@
       <c r="E53" s="6">
         <v>1084.49</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" s="6">
+        <v>1084.49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="2" t="s">
         <v>73</v>
       </c>
@@ -3537,8 +3696,11 @@
       <c r="E54" s="5">
         <v>964.53</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" s="5">
+        <v>964.53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
         <v>77</v>
       </c>
@@ -3554,8 +3716,11 @@
       <c r="E55" s="5">
         <v>15.47</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" s="5">
+        <v>15.47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
         <v>77</v>
       </c>
@@ -3571,8 +3736,11 @@
       <c r="E56" s="5">
         <v>303.18</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" s="5">
+        <v>303.18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
         <v>77</v>
       </c>
@@ -3588,8 +3756,11 @@
       <c r="E57" s="5">
         <v>268.45999999999998</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" s="5">
+        <v>268.45999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
         <v>77</v>
       </c>
@@ -3605,8 +3776,11 @@
       <c r="E58" s="5">
         <v>388.33</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" s="5">
+        <v>388.33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
         <v>85</v>
       </c>
@@ -3622,8 +3796,11 @@
       <c r="E59" s="5">
         <v>198.84</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" s="5">
+        <v>198.84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
         <v>85</v>
       </c>
@@ -3639,8 +3816,11 @@
       <c r="E60" s="5">
         <v>437.08</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" s="5">
+        <v>437.08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
         <v>85</v>
       </c>
@@ -3656,8 +3836,11 @@
       <c r="E61" s="5">
         <v>465.62</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" s="5">
+        <v>465.62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
         <v>88</v>
       </c>
@@ -3673,8 +3856,11 @@
       <c r="E62" s="5">
         <v>390.86</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62" s="5">
+        <v>390.86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
         <v>88</v>
       </c>
@@ -3690,8 +3876,11 @@
       <c r="E63" s="6">
         <v>4946.04</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63" s="6">
+        <v>4946.04</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
         <v>88</v>
       </c>
@@ -3707,8 +3896,11 @@
       <c r="E64" s="6">
         <v>3164.86</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64" s="6">
+        <v>3164.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
         <v>88</v>
       </c>
@@ -3724,8 +3916,11 @@
       <c r="E65" s="6">
         <v>2018.53</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" s="6">
+        <v>2018.53</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
         <v>88</v>
       </c>
@@ -3741,8 +3936,11 @@
       <c r="E66" s="5">
         <v>149.36000000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66" s="5">
+        <v>149.36000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
         <v>88</v>
       </c>
@@ -3758,8 +3956,11 @@
       <c r="E67" s="6">
         <v>1045.26</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67" s="6">
+        <v>1045.26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
         <v>88</v>
       </c>
@@ -3775,8 +3976,11 @@
       <c r="E68" s="5">
         <v>65.459999999999994</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68" s="5">
+        <v>65.459999999999994</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
         <v>100</v>
       </c>
@@ -3792,8 +3996,11 @@
       <c r="E69" s="5">
         <v>340.18</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69" s="5">
+        <v>340.18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
         <v>100</v>
       </c>
@@ -3809,8 +4016,11 @@
       <c r="E70" s="5">
         <v>334.17</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70" s="5">
+        <v>334.17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
         <v>100</v>
       </c>
@@ -3826,8 +4036,11 @@
       <c r="E71" s="5">
         <v>239.26</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" s="5">
+        <v>239.26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
         <v>100</v>
       </c>
@@ -3843,8 +4056,11 @@
       <c r="E72" s="5">
         <v>490.77</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72" s="5">
+        <v>490.77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
         <v>100</v>
       </c>
@@ -3860,8 +4076,11 @@
       <c r="E73" s="5">
         <v>384.88</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73" s="5">
+        <v>384.88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
         <v>100</v>
       </c>
@@ -3877,8 +4096,11 @@
       <c r="E74" s="5">
         <v>541.19000000000005</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74" s="5">
+        <v>541.19000000000005</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
         <v>100</v>
       </c>
@@ -3894,8 +4116,11 @@
       <c r="E75" s="5">
         <v>411.95</v>
       </c>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="F75" s="5">
+        <v>411.95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
         <v>100</v>
       </c>
@@ -3911,8 +4136,11 @@
       <c r="E76" s="5">
         <v>363.47</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76" s="5">
+        <v>363.47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
         <v>100</v>
       </c>
@@ -3928,8 +4156,11 @@
       <c r="E77" s="6">
         <v>-1186.45</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77" s="6">
+        <v>-1186.45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
         <v>115</v>
       </c>
@@ -3945,8 +4176,11 @@
       <c r="E78" s="6">
         <v>4448.6000000000004</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78" s="6">
+        <v>4448.6000000000004</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
         <v>116</v>
       </c>
@@ -3962,8 +4196,11 @@
       <c r="E79" s="5">
         <v>952.17</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79" s="5">
+        <v>952.17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
         <v>119</v>
       </c>
@@ -3979,8 +4216,11 @@
       <c r="E80" s="5">
         <v>842.01</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80" s="5">
+        <v>842.01</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
         <v>119</v>
       </c>
@@ -3996,8 +4236,11 @@
       <c r="E81" s="5">
         <v>784.99</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81" s="5">
+        <v>784.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
         <v>123</v>
       </c>
@@ -4013,8 +4256,11 @@
       <c r="E82" s="6">
         <v>2416.3200000000002</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82" s="6">
+        <v>2416.3200000000002</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
         <v>125</v>
       </c>
@@ -4030,8 +4276,11 @@
       <c r="E83" s="6">
         <v>1483.41</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83" s="6">
+        <v>1483.41</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
         <v>125</v>
       </c>
@@ -4047,8 +4296,11 @@
       <c r="E84" s="5">
         <v>568.25</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84" s="5">
+        <v>568.25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
         <v>125</v>
       </c>
@@ -4064,8 +4316,11 @@
       <c r="E85" s="5">
         <v>149.44</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85" s="5">
+        <v>149.44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
         <v>125</v>
       </c>
@@ -4081,8 +4336,11 @@
       <c r="E86" s="5">
         <v>377.52</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="F86" s="5">
+        <v>377.52</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
         <v>125</v>
       </c>
@@ -4098,8 +4356,11 @@
       <c r="E87" s="6">
         <v>4684.08</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87" s="6">
+        <v>4684.08</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
         <v>125</v>
       </c>
@@ -4115,8 +4376,11 @@
       <c r="E88" s="6">
         <v>2164.9699999999998</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88" s="6">
+        <v>2164.9699999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
         <v>133</v>
       </c>
@@ -4132,8 +4396,11 @@
       <c r="E89" s="5">
         <v>890.95</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89" s="5">
+        <v>890.95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
         <v>133</v>
       </c>
@@ -4149,8 +4416,11 @@
       <c r="E90" s="5">
         <v>418.2</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90" s="5">
+        <v>418.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
         <v>133</v>
       </c>
@@ -4166,8 +4436,11 @@
       <c r="E91" s="5">
         <v>271.20999999999998</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="F91" s="5">
+        <v>271.20999999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
         <v>133</v>
       </c>
@@ -4183,8 +4456,11 @@
       <c r="E92" s="5">
         <v>651.34</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" s="5">
+        <v>651.34</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
         <v>138</v>
       </c>
@@ -4200,8 +4476,11 @@
       <c r="E93" s="6">
         <v>4445.34</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" s="6">
+        <v>4445.34</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
         <v>138</v>
       </c>
@@ -4217,8 +4496,11 @@
       <c r="E94" s="6">
         <v>7737.85</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94" s="6">
+        <v>7737.85</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
         <v>141</v>
       </c>
@@ -4234,8 +4516,11 @@
       <c r="E95" s="6">
         <v>5346.27</v>
       </c>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="F95" s="6">
+        <v>5346.27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
         <v>141</v>
       </c>
@@ -4251,8 +4536,11 @@
       <c r="E96" s="5">
         <v>301.58</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96" s="5">
+        <v>301.58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
         <v>141</v>
       </c>
@@ -4268,8 +4556,11 @@
       <c r="E97" s="5">
         <v>428.78</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" s="5">
+        <v>428.78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
         <v>141</v>
       </c>
@@ -4285,8 +4576,11 @@
       <c r="E98" s="6">
         <v>5152.92</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="6">
+        <v>5152.92</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
         <v>141</v>
       </c>
@@ -4302,8 +4596,11 @@
       <c r="E99" s="5">
         <v>193.56</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" s="5">
+        <v>193.56</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
         <v>141</v>
       </c>
@@ -4319,8 +4616,11 @@
       <c r="E100" s="5">
         <v>274.11</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" s="5">
+        <v>274.11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
         <v>141</v>
       </c>
@@ -4336,8 +4636,11 @@
       <c r="E101" s="5">
         <v>551.74</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101" s="5">
+        <v>551.74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
         <v>141</v>
       </c>
@@ -4353,8 +4656,11 @@
       <c r="E102" s="6">
         <v>5257.39</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102" s="6">
+        <v>5257.39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
         <v>141</v>
       </c>
@@ -4370,8 +4676,11 @@
       <c r="E103" s="5">
         <v>190.03</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" s="5">
+        <v>190.03</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
         <v>141</v>
       </c>
@@ -4387,8 +4696,11 @@
       <c r="E104" s="6">
         <v>-10410.31</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" s="6">
+        <v>-10410.31</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
         <v>160</v>
       </c>
@@ -4404,8 +4716,11 @@
       <c r="E105" s="6">
         <v>1056.79</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="F105" s="6">
+        <v>1056.79</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
         <v>160</v>
       </c>
@@ -4421,8 +4736,11 @@
       <c r="E106" s="5">
         <v>684.26</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106" s="5">
+        <v>684.26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
         <v>160</v>
       </c>
@@ -4438,8 +4756,11 @@
       <c r="E107" s="5">
         <v>398.08</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" s="5">
+        <v>398.08</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
         <v>160</v>
       </c>
@@ -4455,8 +4776,11 @@
       <c r="E108" s="5">
         <v>377.52</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" s="5">
+        <v>377.52</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
         <v>165</v>
       </c>
@@ -4472,8 +4796,11 @@
       <c r="E109" s="5">
         <v>755.04</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" s="5">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
         <v>165</v>
       </c>
@@ -4489,8 +4816,11 @@
       <c r="E110" s="6">
         <v>1824.1</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110" s="6">
+        <v>1824.1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
         <v>167</v>
       </c>
@@ -4506,8 +4836,11 @@
       <c r="E111" s="6">
         <v>3500</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111" s="6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
         <v>167</v>
       </c>
@@ -4523,8 +4856,11 @@
       <c r="E112" s="6">
         <v>4039.03</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112" s="6">
+        <v>4039.03</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
         <v>169</v>
       </c>
@@ -4540,8 +4876,11 @@
       <c r="E113" s="5">
         <v>631.35</v>
       </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="F113" s="5">
+        <v>631.35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
         <v>171</v>
       </c>
@@ -4557,8 +4896,11 @@
       <c r="E114" s="6">
         <v>4148.4399999999996</v>
       </c>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="F114" s="6">
+        <v>4148.4399999999996</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
         <v>171</v>
       </c>
@@ -4574,8 +4916,11 @@
       <c r="E115" s="6">
         <v>2326.6</v>
       </c>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="F115" s="6">
+        <v>2326.6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
         <v>175</v>
       </c>
@@ -4591,8 +4936,11 @@
       <c r="E116" s="5">
         <v>249.36</v>
       </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="F116" s="5">
+        <v>249.36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
         <v>175</v>
       </c>
@@ -4608,8 +4956,11 @@
       <c r="E117" s="5">
         <v>316.27</v>
       </c>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="F117" s="5">
+        <v>316.27</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
         <v>175</v>
       </c>
@@ -4625,8 +4976,11 @@
       <c r="E118" s="5">
         <v>262.48</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118" s="5">
+        <v>262.48</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
         <v>175</v>
       </c>
@@ -4642,8 +4996,11 @@
       <c r="E119" s="5">
         <v>219.43</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119" s="5">
+        <v>219.43</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="2" t="s">
         <v>175</v>
       </c>
@@ -4659,8 +5016,11 @@
       <c r="E120" s="5">
         <v>261.86</v>
       </c>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="F120" s="5">
+        <v>261.86</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
         <v>175</v>
       </c>
@@ -4676,8 +5036,11 @@
       <c r="E121" s="5">
         <v>455.71</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="F121" s="5">
+        <v>455.71</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
         <v>175</v>
       </c>
@@ -4693,8 +5056,11 @@
       <c r="E122" s="5">
         <v>711.77</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="F122" s="5">
+        <v>711.77</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
         <v>175</v>
       </c>
@@ -4710,8 +5076,11 @@
       <c r="E123" s="5">
         <v>196.81</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="F123" s="5">
+        <v>196.81</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
         <v>175</v>
       </c>
@@ -4727,8 +5096,11 @@
       <c r="E124" s="5">
         <v>541.96</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124" s="5">
+        <v>541.96</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
         <v>184</v>
       </c>
@@ -4744,8 +5116,11 @@
       <c r="E125" s="6">
         <v>2333.9499999999998</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="F125" s="6">
+        <v>2333.9499999999998</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
         <v>184</v>
       </c>
@@ -4761,8 +5136,11 @@
       <c r="E126" s="6">
         <v>5665.62</v>
       </c>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="F126" s="6">
+        <v>5665.62</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
         <v>184</v>
       </c>
@@ -4778,8 +5156,11 @@
       <c r="E127" s="5">
         <v>914.71</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="F127" s="5">
+        <v>914.71</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
         <v>190</v>
       </c>
@@ -4795,8 +5176,11 @@
       <c r="E128" s="5">
         <v>168.97</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" s="5">
+        <v>168.97</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
         <v>190</v>
       </c>
@@ -4812,8 +5196,11 @@
       <c r="E129" s="6">
         <v>8875.52</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" s="6">
+        <v>8875.52</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
         <v>190</v>
       </c>
@@ -4829,8 +5216,11 @@
       <c r="E130" s="5">
         <v>537.76</v>
       </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130" s="5">
+        <v>537.76</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
         <v>190</v>
       </c>
@@ -4846,8 +5236,11 @@
       <c r="E131" s="5">
         <v>168.97</v>
       </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="F131" s="5">
+        <v>168.97</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
         <v>190</v>
       </c>
@@ -4863,8 +5256,11 @@
       <c r="E132" s="6">
         <v>6864.42</v>
       </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132" s="6">
+        <v>6864.42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
         <v>190</v>
       </c>
@@ -4880,8 +5276,11 @@
       <c r="E133" s="5">
         <v>659.82</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" s="5">
+        <v>659.82</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
         <v>198</v>
       </c>
@@ -4897,8 +5296,11 @@
       <c r="E134" s="5">
         <v>340.09</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" s="5">
+        <v>340.09</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="2" t="s">
         <v>200</v>
       </c>
@@ -4914,8 +5316,11 @@
       <c r="E135" s="5">
         <v>536.92999999999995</v>
       </c>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="F135" s="5">
+        <v>536.92999999999995</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="2" t="s">
         <v>201</v>
       </c>
@@ -4931,8 +5336,11 @@
       <c r="E136" s="5">
         <v>735.97</v>
       </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="F136" s="5">
+        <v>735.97</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="2" t="s">
         <v>203</v>
       </c>
@@ -4948,8 +5356,11 @@
       <c r="E137" s="5">
         <v>961.96</v>
       </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137" s="5">
+        <v>961.96</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="2" t="s">
         <v>205</v>
       </c>
@@ -4965,8 +5376,11 @@
       <c r="E138" s="5">
         <v>378.31</v>
       </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" s="5">
+        <v>378.31</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="2" t="s">
         <v>208</v>
       </c>
@@ -4982,8 +5396,11 @@
       <c r="E139" s="5">
         <v>459.91</v>
       </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" s="5">
+        <v>459.91</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="2" t="s">
         <v>208</v>
       </c>
@@ -4999,8 +5416,11 @@
       <c r="E140" s="5">
         <v>308.08999999999997</v>
       </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="F140" s="5">
+        <v>308.08999999999997</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="2" t="s">
         <v>208</v>
       </c>
@@ -5016,8 +5436,11 @@
       <c r="E141" s="6">
         <v>1391.53</v>
       </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="F141" s="6">
+        <v>1391.53</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="2" t="s">
         <v>208</v>
       </c>
@@ -5033,8 +5456,11 @@
       <c r="E142" s="5">
         <v>760.73</v>
       </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142" s="5">
+        <v>760.73</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="2" t="s">
         <v>208</v>
       </c>
@@ -5050,8 +5476,11 @@
       <c r="E143" s="6">
         <v>1584.94</v>
       </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" s="6">
+        <v>1584.94</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="2" t="s">
         <v>212</v>
       </c>
@@ -5067,8 +5496,11 @@
       <c r="E144" s="6">
         <v>1533.02</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144" s="6">
+        <v>1533.02</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="2" t="s">
         <v>212</v>
       </c>
@@ -5084,8 +5516,11 @@
       <c r="E145" s="5">
         <v>298.87</v>
       </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="F145" s="5">
+        <v>298.87</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="2" t="s">
         <v>214</v>
       </c>
@@ -5101,8 +5536,11 @@
       <c r="E146" s="5">
         <v>222.03</v>
       </c>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="F146" s="5">
+        <v>222.03</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="2" t="s">
         <v>214</v>
       </c>
@@ -5118,8 +5556,11 @@
       <c r="E147" s="5">
         <v>483.88</v>
       </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147" s="5">
+        <v>483.88</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="2" t="s">
         <v>214</v>
       </c>
@@ -5135,8 +5576,11 @@
       <c r="E148" s="5">
         <v>569.72</v>
       </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148" s="5">
+        <v>569.72</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="2" t="s">
         <v>214</v>
       </c>
@@ -5152,8 +5596,11 @@
       <c r="E149" s="5">
         <v>667.9</v>
       </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149" s="5">
+        <v>667.9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="2" t="s">
         <v>214</v>
       </c>
@@ -5169,8 +5616,11 @@
       <c r="E150" s="5">
         <v>454.15</v>
       </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="F150" s="5">
+        <v>454.15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="2" t="s">
         <v>214</v>
       </c>
@@ -5186,8 +5636,11 @@
       <c r="E151" s="6">
         <v>1147.26</v>
       </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="F151" s="6">
+        <v>1147.26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="2" t="s">
         <v>220</v>
       </c>
@@ -5203,8 +5656,11 @@
       <c r="E152" s="6">
         <v>1379.09</v>
       </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152" s="6">
+        <v>1379.09</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="2" t="s">
         <v>222</v>
       </c>
@@ -5220,8 +5676,11 @@
       <c r="E153" s="5">
         <v>576.96</v>
       </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153" s="5">
+        <v>576.96</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="2" t="s">
         <v>222</v>
       </c>
@@ -5237,8 +5696,11 @@
       <c r="E154" s="5">
         <v>881.9</v>
       </c>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="F154" s="5">
+        <v>881.9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
         <v>222</v>
       </c>
@@ -5254,8 +5716,11 @@
       <c r="E155" s="5">
         <v>706.04</v>
       </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="F155" s="5">
+        <v>706.04</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" s="2" t="s">
         <v>222</v>
       </c>
@@ -5271,8 +5736,11 @@
       <c r="E156" s="6">
         <v>2313.5100000000002</v>
       </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="F156" s="6">
+        <v>2313.5100000000002</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" s="2" t="s">
         <v>226</v>
       </c>
@@ -5288,8 +5756,11 @@
       <c r="E157" s="6">
         <v>1326.33</v>
       </c>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="F157" s="6">
+        <v>1326.33</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" s="2" t="s">
         <v>226</v>
       </c>
@@ -5305,8 +5776,11 @@
       <c r="E158" s="5">
         <v>216</v>
       </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="F158" s="5">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" s="2" t="s">
         <v>226</v>
       </c>
@@ -5322,8 +5796,11 @@
       <c r="E159" s="5">
         <v>251.63</v>
       </c>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="F159" s="5">
+        <v>251.63</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" s="2" t="s">
         <v>232</v>
       </c>
@@ -5339,8 +5816,11 @@
       <c r="E160" s="5">
         <v>245.39</v>
       </c>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="F160" s="5">
+        <v>245.39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" s="2" t="s">
         <v>234</v>
       </c>
@@ -5356,8 +5836,11 @@
       <c r="E161" s="5">
         <v>195.77</v>
       </c>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="F161" s="5">
+        <v>195.77</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" s="2" t="s">
         <v>234</v>
       </c>
@@ -5373,8 +5856,11 @@
       <c r="E162" s="6">
         <v>1551.64</v>
       </c>
-    </row>
-    <row r="163" spans="1:5">
+      <c r="F162" s="6">
+        <v>1551.64</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" s="2" t="s">
         <v>234</v>
       </c>
@@ -5390,8 +5876,11 @@
       <c r="E163" s="5">
         <v>328.76</v>
       </c>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="F163" s="5">
+        <v>328.76</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" s="2" t="s">
         <v>234</v>
       </c>
@@ -5407,8 +5896,11 @@
       <c r="E164" s="5">
         <v>466.08</v>
       </c>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="F164" s="5">
+        <v>466.08</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" s="2" t="s">
         <v>234</v>
       </c>
@@ -5424,8 +5916,11 @@
       <c r="E165" s="5">
         <v>163.47</v>
       </c>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="F165" s="5">
+        <v>163.47</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" s="2" t="s">
         <v>240</v>
       </c>
@@ -5441,8 +5936,11 @@
       <c r="E166" s="5">
         <v>505.48</v>
       </c>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="F166" s="5">
+        <v>505.48</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" s="2" t="s">
         <v>241</v>
       </c>
@@ -5458,8 +5956,11 @@
       <c r="E167" s="5">
         <v>603.02</v>
       </c>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="F167" s="5">
+        <v>603.02</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" s="2" t="s">
         <v>241</v>
       </c>
@@ -5475,8 +5976,11 @@
       <c r="E168" s="5">
         <v>316.20999999999998</v>
       </c>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="F168" s="5">
+        <v>316.20999999999998</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" s="2" t="s">
         <v>241</v>
       </c>
@@ -5492,8 +5996,11 @@
       <c r="E169" s="5">
         <v>775.8</v>
       </c>
-    </row>
-    <row r="170" spans="1:5">
+      <c r="F169" s="5">
+        <v>775.8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" s="2" t="s">
         <v>241</v>
       </c>
@@ -5509,8 +6016,11 @@
       <c r="E170" s="5">
         <v>603.02</v>
       </c>
-    </row>
-    <row r="171" spans="1:5">
+      <c r="F170" s="5">
+        <v>603.02</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" s="2" t="s">
         <v>245</v>
       </c>
@@ -5526,8 +6036,11 @@
       <c r="E171" s="6">
         <v>7918.02</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="F171" s="6">
+        <v>7918.02</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" s="2" t="s">
         <v>246</v>
       </c>
@@ -5543,8 +6056,11 @@
       <c r="E172" s="5">
         <v>596.84</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="F172" s="5">
+        <v>596.84</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" s="2" t="s">
         <v>246</v>
       </c>
@@ -5560,8 +6076,11 @@
       <c r="E173" s="5">
         <v>401.14</v>
       </c>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="F173" s="5">
+        <v>401.14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" s="2" t="s">
         <v>246</v>
       </c>
@@ -5577,8 +6096,11 @@
       <c r="E174" s="5">
         <v>429.91</v>
       </c>
-    </row>
-    <row r="175" spans="1:5">
+      <c r="F174" s="5">
+        <v>429.91</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" s="2" t="s">
         <v>250</v>
       </c>
@@ -5594,8 +6116,11 @@
       <c r="E175" s="6">
         <v>3528.34</v>
       </c>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="F175" s="6">
+        <v>3528.34</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" s="2" t="s">
         <v>253</v>
       </c>
@@ -5611,8 +6136,11 @@
       <c r="E176" s="6">
         <v>10726.46</v>
       </c>
-    </row>
-    <row r="177" spans="1:5">
+      <c r="F176" s="6">
+        <v>10726.46</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" s="2" t="s">
         <v>253</v>
       </c>
@@ -5628,8 +6156,11 @@
       <c r="E177" s="6">
         <v>2086.77</v>
       </c>
-    </row>
-    <row r="178" spans="1:5">
+      <c r="F177" s="6">
+        <v>2086.77</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" s="2" t="s">
         <v>253</v>
       </c>
@@ -5645,8 +6176,11 @@
       <c r="E178" s="6">
         <v>1100.7</v>
       </c>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="F178" s="6">
+        <v>1100.7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" s="2" t="s">
         <v>253</v>
       </c>
@@ -5662,8 +6196,11 @@
       <c r="E179" s="6">
         <v>2201.4</v>
       </c>
-    </row>
-    <row r="180" spans="1:5">
+      <c r="F179" s="6">
+        <v>2201.4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" s="2" t="s">
         <v>253</v>
       </c>
@@ -5679,8 +6216,11 @@
       <c r="E180" s="5">
         <v>376.95</v>
       </c>
-    </row>
-    <row r="181" spans="1:5">
+      <c r="F180" s="5">
+        <v>376.95</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" s="2" t="s">
         <v>253</v>
       </c>
@@ -5696,8 +6236,11 @@
       <c r="E181" s="5">
         <v>295.83</v>
       </c>
-    </row>
-    <row r="182" spans="1:5">
+      <c r="F181" s="5">
+        <v>295.83</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" s="2" t="s">
         <v>260</v>
       </c>
@@ -5713,8 +6256,11 @@
       <c r="E182" s="5">
         <v>311.14999999999998</v>
       </c>
-    </row>
-    <row r="183" spans="1:5">
+      <c r="F182" s="5">
+        <v>311.14999999999998</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" s="2" t="s">
         <v>260</v>
       </c>
@@ -5730,8 +6276,11 @@
       <c r="E183" s="5">
         <v>391.05</v>
       </c>
-    </row>
-    <row r="184" spans="1:5">
+      <c r="F183" s="5">
+        <v>391.05</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" s="2" t="s">
         <v>260</v>
       </c>
@@ -5747,8 +6296,11 @@
       <c r="E184" s="5">
         <v>418.15</v>
       </c>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="F184" s="5">
+        <v>418.15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" s="2" t="s">
         <v>260</v>
       </c>
@@ -5764,8 +6316,11 @@
       <c r="E185" s="5">
         <v>93.82</v>
       </c>
-    </row>
-    <row r="186" spans="1:5">
+      <c r="F185" s="5">
+        <v>93.82</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186" s="2" t="s">
         <v>260</v>
       </c>
@@ -5781,8 +6336,11 @@
       <c r="E186" s="5">
         <v>404.89</v>
       </c>
-    </row>
-    <row r="187" spans="1:5">
+      <c r="F186" s="5">
+        <v>404.89</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187" s="2" t="s">
         <v>260</v>
       </c>
@@ -5798,8 +6356,11 @@
       <c r="E187" s="5">
         <v>398.26</v>
       </c>
-    </row>
-    <row r="188" spans="1:5">
+      <c r="F187" s="5">
+        <v>398.26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" s="2" t="s">
         <v>260</v>
       </c>
@@ -5815,8 +6376,11 @@
       <c r="E188" s="5">
         <v>261.86</v>
       </c>
-    </row>
-    <row r="189" spans="1:5">
+      <c r="F188" s="5">
+        <v>261.86</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189" s="2" t="s">
         <v>260</v>
       </c>
@@ -5832,8 +6396,11 @@
       <c r="E189" s="5">
         <v>270.98</v>
       </c>
-    </row>
-    <row r="190" spans="1:5">
+      <c r="F189" s="5">
+        <v>270.98</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190" s="2" t="s">
         <v>260</v>
       </c>
@@ -5849,8 +6416,11 @@
       <c r="E190" s="5">
         <v>430.93</v>
       </c>
-    </row>
-    <row r="191" spans="1:5">
+      <c r="F190" s="5">
+        <v>430.93</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191" s="2" t="s">
         <v>260</v>
       </c>
@@ -5866,8 +6436,11 @@
       <c r="E191" s="5">
         <v>457.36</v>
       </c>
-    </row>
-    <row r="192" spans="1:5">
+      <c r="F191" s="5">
+        <v>457.36</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192" s="2" t="s">
         <v>272</v>
       </c>
@@ -5883,8 +6456,11 @@
       <c r="E192" s="6">
         <v>1583.6</v>
       </c>
-    </row>
-    <row r="193" spans="1:5">
+      <c r="F192" s="6">
+        <v>1583.6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193" s="2" t="s">
         <v>274</v>
       </c>
@@ -5900,8 +6476,11 @@
       <c r="E193" s="5">
         <v>467.44</v>
       </c>
-    </row>
-    <row r="194" spans="1:5">
+      <c r="F193" s="5">
+        <v>467.44</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
       <c r="A194" s="2" t="s">
         <v>274</v>
       </c>
@@ -5917,8 +6496,11 @@
       <c r="E194" s="5">
         <v>271.20999999999998</v>
       </c>
-    </row>
-    <row r="195" spans="1:5">
+      <c r="F194" s="5">
+        <v>271.20999999999998</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195" s="2" t="s">
         <v>274</v>
       </c>
@@ -5934,8 +6516,11 @@
       <c r="E195" s="5">
         <v>270.98</v>
       </c>
-    </row>
-    <row r="196" spans="1:5">
+      <c r="F195" s="5">
+        <v>270.98</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196" s="2" t="s">
         <v>274</v>
       </c>
@@ -5951,8 +6536,11 @@
       <c r="E196" s="5">
         <v>350.72</v>
       </c>
-    </row>
-    <row r="197" spans="1:5">
+      <c r="F196" s="5">
+        <v>350.72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197" s="2" t="s">
         <v>274</v>
       </c>
@@ -5968,8 +6556,11 @@
       <c r="E197" s="5">
         <v>310.2</v>
       </c>
-    </row>
-    <row r="198" spans="1:5">
+      <c r="F197" s="5">
+        <v>310.2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198" s="2" t="s">
         <v>279</v>
       </c>
@@ -5985,8 +6576,11 @@
       <c r="E198" s="6">
         <v>3153.65</v>
       </c>
-    </row>
-    <row r="199" spans="1:5">
+      <c r="F198" s="6">
+        <v>3153.65</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199" s="2" t="s">
         <v>279</v>
       </c>
@@ -6002,8 +6596,11 @@
       <c r="E199" s="6">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="200" spans="1:5">
+      <c r="F199" s="6">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200" s="2" t="s">
         <v>279</v>
       </c>
@@ -6019,8 +6616,11 @@
       <c r="E200" s="5">
         <v>734.31</v>
       </c>
-    </row>
-    <row r="201" spans="1:5">
+      <c r="F200" s="5">
+        <v>734.31</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201" s="2" t="s">
         <v>279</v>
       </c>
@@ -6036,8 +6636,11 @@
       <c r="E201" s="6">
         <v>2820.19</v>
       </c>
-    </row>
-    <row r="202" spans="1:5">
+      <c r="F201" s="6">
+        <v>2820.19</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
       <c r="A202" s="2" t="s">
         <v>279</v>
       </c>
@@ -6053,8 +6656,11 @@
       <c r="E202" s="6">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="203" spans="1:5">
+      <c r="F202" s="6">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
       <c r="A203" s="2" t="s">
         <v>285</v>
       </c>
@@ -6070,8 +6676,11 @@
       <c r="E203" s="5">
         <v>738.85</v>
       </c>
-    </row>
-    <row r="204" spans="1:5">
+      <c r="F203" s="5">
+        <v>738.85</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
       <c r="A204" s="2" t="s">
         <v>287</v>
       </c>
@@ -6087,8 +6696,11 @@
       <c r="E204" s="6">
         <v>5514.78</v>
       </c>
-    </row>
-    <row r="205" spans="1:5">
+      <c r="F204" s="6">
+        <v>5514.78</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205" s="2" t="s">
         <v>287</v>
       </c>
@@ -6104,8 +6716,11 @@
       <c r="E205" s="6">
         <v>1142.45</v>
       </c>
-    </row>
-    <row r="206" spans="1:5">
+      <c r="F205" s="6">
+        <v>1142.45</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
       <c r="A206" s="2" t="s">
         <v>290</v>
       </c>
@@ -6121,8 +6736,11 @@
       <c r="E206" s="5">
         <v>147.55000000000001</v>
       </c>
-    </row>
-    <row r="207" spans="1:5">
+      <c r="F206" s="5">
+        <v>147.55000000000001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
       <c r="A207" s="2" t="s">
         <v>290</v>
       </c>
@@ -6138,8 +6756,11 @@
       <c r="E207" s="5">
         <v>376.95</v>
       </c>
-    </row>
-    <row r="208" spans="1:5">
+      <c r="F207" s="5">
+        <v>376.95</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208" s="2" t="s">
         <v>290</v>
       </c>
@@ -6155,8 +6776,11 @@
       <c r="E208" s="5">
         <v>376.95</v>
       </c>
-    </row>
-    <row r="209" spans="1:5">
+      <c r="F208" s="5">
+        <v>376.95</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
       <c r="A209" s="2" t="s">
         <v>290</v>
       </c>
@@ -6172,8 +6796,11 @@
       <c r="E209" s="5">
         <v>325.68</v>
       </c>
-    </row>
-    <row r="210" spans="1:5">
+      <c r="F209" s="5">
+        <v>325.68</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210" s="2" t="s">
         <v>290</v>
       </c>
@@ -6189,8 +6816,11 @@
       <c r="E210" s="5">
         <v>270.98</v>
       </c>
-    </row>
-    <row r="211" spans="1:5">
+      <c r="F210" s="5">
+        <v>270.98</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
       <c r="A211" s="2" t="s">
         <v>293</v>
       </c>
@@ -6206,8 +6836,11 @@
       <c r="E211" s="6">
         <v>4007.37</v>
       </c>
-    </row>
-    <row r="212" spans="1:5">
+      <c r="F211" s="6">
+        <v>4007.37</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212" s="2" t="s">
         <v>293</v>
       </c>
@@ -6223,8 +6856,11 @@
       <c r="E212" s="6">
         <v>4165.26</v>
       </c>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="F212" s="6">
+        <v>4165.26</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" s="2" t="s">
         <v>293</v>
       </c>
@@ -6240,8 +6876,11 @@
       <c r="E213" s="5">
         <v>572.52</v>
       </c>
-    </row>
-    <row r="214" spans="1:5">
+      <c r="F213" s="5">
+        <v>572.52</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214" s="2" t="s">
         <v>296</v>
       </c>
@@ -6257,8 +6896,11 @@
       <c r="E214" s="5">
         <v>323.64999999999998</v>
       </c>
-    </row>
-    <row r="215" spans="1:5">
+      <c r="F214" s="5">
+        <v>323.64999999999998</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215" s="2" t="s">
         <v>296</v>
       </c>
@@ -6274,8 +6916,11 @@
       <c r="E215" s="5">
         <v>288.73</v>
       </c>
-    </row>
-    <row r="216" spans="1:5">
+      <c r="F215" s="5">
+        <v>288.73</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216" s="2" t="s">
         <v>296</v>
       </c>
@@ -6291,8 +6936,11 @@
       <c r="E216" s="5">
         <v>272.25</v>
       </c>
-    </row>
-    <row r="217" spans="1:5">
+      <c r="F216" s="5">
+        <v>272.25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" s="2" t="s">
         <v>296</v>
       </c>
@@ -6308,8 +6956,11 @@
       <c r="E217" s="5">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="F217" s="5">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218" s="2" t="s">
         <v>299</v>
       </c>
@@ -6325,8 +6976,11 @@
       <c r="E218" s="6">
         <v>1218.0899999999999</v>
       </c>
-    </row>
-    <row r="219" spans="1:5">
+      <c r="F218" s="6">
+        <v>1218.0899999999999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219" s="2" t="s">
         <v>299</v>
       </c>
@@ -6342,8 +6996,11 @@
       <c r="E219" s="5">
         <v>162.1</v>
       </c>
-    </row>
-    <row r="220" spans="1:5">
+      <c r="F219" s="5">
+        <v>162.1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
       <c r="A220" s="2" t="s">
         <v>299</v>
       </c>
@@ -6359,8 +7016,11 @@
       <c r="E220" s="5">
         <v>672.42</v>
       </c>
-    </row>
-    <row r="221" spans="1:5">
+      <c r="F220" s="5">
+        <v>672.42</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
       <c r="A221" s="2" t="s">
         <v>303</v>
       </c>
@@ -6376,8 +7036,11 @@
       <c r="E221" s="5">
         <v>916</v>
       </c>
-    </row>
-    <row r="222" spans="1:5">
+      <c r="F221" s="5">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
       <c r="A222" s="2" t="s">
         <v>331</v>
       </c>
@@ -6393,8 +7056,11 @@
       <c r="E222" s="5">
         <v>911.88</v>
       </c>
-    </row>
-    <row r="223" spans="1:5">
+      <c r="F222" s="5">
+        <v>911.88</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
       <c r="A223" s="2" t="s">
         <v>331</v>
       </c>
@@ -6410,8 +7076,11 @@
       <c r="E223" s="5">
         <v>222.3</v>
       </c>
-    </row>
-    <row r="224" spans="1:5">
+      <c r="F223" s="5">
+        <v>222.3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
       <c r="A224" s="2" t="s">
         <v>331</v>
       </c>
@@ -6427,8 +7096,11 @@
       <c r="E224" s="5">
         <v>589.88</v>
       </c>
-    </row>
-    <row r="225" spans="1:5">
+      <c r="F224" s="5">
+        <v>589.88</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
         <v>336</v>
       </c>
@@ -6444,8 +7116,11 @@
       <c r="E225" s="6">
         <v>6601.54</v>
       </c>
-    </row>
-    <row r="226" spans="1:5">
+      <c r="F225" s="6">
+        <v>6601.54</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
       <c r="A226" s="2" t="s">
         <v>338</v>
       </c>
@@ -6461,8 +7136,11 @@
       <c r="E226" s="5">
         <v>17.61</v>
       </c>
-    </row>
-    <row r="227" spans="1:5">
+      <c r="F226" s="5">
+        <v>17.61</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
       <c r="A227" s="2" t="s">
         <v>338</v>
       </c>
@@ -6478,8 +7156,11 @@
       <c r="E227" s="5">
         <v>222.65</v>
       </c>
-    </row>
-    <row r="228" spans="1:5">
+      <c r="F227" s="5">
+        <v>222.65</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
       <c r="A228" s="2" t="s">
         <v>338</v>
       </c>
@@ -6495,8 +7176,11 @@
       <c r="E228" s="5">
         <v>351.09</v>
       </c>
-    </row>
-    <row r="229" spans="1:5">
+      <c r="F228" s="5">
+        <v>351.09</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
       <c r="A229" s="2" t="s">
         <v>344</v>
       </c>
@@ -6512,8 +7196,11 @@
       <c r="E229" s="5">
         <v>219.77</v>
       </c>
-    </row>
-    <row r="230" spans="1:5">
+      <c r="F229" s="5">
+        <v>219.77</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
       <c r="A230" s="2" t="s">
         <v>344</v>
       </c>
@@ -6529,8 +7216,11 @@
       <c r="E230" s="5">
         <v>838.68</v>
       </c>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="F230" s="5">
+        <v>838.68</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
       <c r="A231" s="2" t="s">
         <v>344</v>
       </c>
@@ -6546,8 +7236,11 @@
       <c r="E231" s="6">
         <v>3440.81</v>
       </c>
-    </row>
-    <row r="232" spans="1:5">
+      <c r="F231" s="6">
+        <v>3440.81</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
       <c r="A232" s="2" t="s">
         <v>344</v>
       </c>
@@ -6563,8 +7256,11 @@
       <c r="E232" s="5">
         <v>353.93</v>
       </c>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="F232" s="5">
+        <v>353.93</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
       <c r="A233" s="2" t="s">
         <v>344</v>
       </c>
@@ -6580,8 +7276,11 @@
       <c r="E233" s="5">
         <v>750.28</v>
       </c>
-    </row>
-    <row r="234" spans="1:5">
+      <c r="F233" s="5">
+        <v>750.28</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
       <c r="A234" s="2" t="s">
         <v>344</v>
       </c>
@@ -6597,8 +7296,11 @@
       <c r="E234" s="5">
         <v>210.36</v>
       </c>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="F234" s="5">
+        <v>210.36</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
       <c r="A235" s="2" t="s">
         <v>344</v>
       </c>
@@ -6614,8 +7316,11 @@
       <c r="E235" s="5">
         <v>810.63</v>
       </c>
-    </row>
-    <row r="236" spans="1:5">
+      <c r="F235" s="5">
+        <v>810.63</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
       <c r="A236" s="2" t="s">
         <v>344</v>
       </c>
@@ -6631,8 +7336,11 @@
       <c r="E236" s="6">
         <v>1305.2</v>
       </c>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="F236" s="6">
+        <v>1305.2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
       <c r="A237" s="2" t="s">
         <v>354</v>
       </c>
@@ -6648,8 +7356,11 @@
       <c r="E237" s="5">
         <v>377.52</v>
       </c>
-    </row>
-    <row r="238" spans="1:5">
+      <c r="F237" s="5">
+        <v>377.52</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
       <c r="A238" s="2" t="s">
         <v>354</v>
       </c>
@@ -6665,8 +7376,11 @@
       <c r="E238" s="5">
         <v>506.72</v>
       </c>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="F238" s="5">
+        <v>506.72</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
       <c r="A239" s="2" t="s">
         <v>357</v>
       </c>
@@ -6682,8 +7396,11 @@
       <c r="E239" s="5">
         <v>132.46</v>
       </c>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="F239" s="5">
+        <v>132.46</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240" s="2" t="s">
         <v>357</v>
       </c>
@@ -6699,8 +7416,11 @@
       <c r="E240" s="5">
         <v>152.68</v>
       </c>
-    </row>
-    <row r="241" spans="1:5">
+      <c r="F240" s="5">
+        <v>152.68</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
       <c r="A241" s="2" t="s">
         <v>357</v>
       </c>
@@ -6716,8 +7436,11 @@
       <c r="E241" s="5">
         <v>163.05000000000001</v>
       </c>
-    </row>
-    <row r="242" spans="1:5">
+      <c r="F241" s="5">
+        <v>163.05000000000001</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
       <c r="A242" s="2" t="s">
         <v>357</v>
       </c>
@@ -6733,8 +7456,11 @@
       <c r="E242" s="5">
         <v>220.74</v>
       </c>
-    </row>
-    <row r="243" spans="1:5">
+      <c r="F242" s="5">
+        <v>220.74</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
       <c r="A243" s="2" t="s">
         <v>357</v>
       </c>
@@ -6750,8 +7476,11 @@
       <c r="E243" s="5">
         <v>304.68</v>
       </c>
-    </row>
-    <row r="244" spans="1:5">
+      <c r="F243" s="5">
+        <v>304.68</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -6767,8 +7496,11 @@
       <c r="E244" s="5">
         <v>216.59</v>
       </c>
-    </row>
-    <row r="245" spans="1:5">
+      <c r="F244" s="5">
+        <v>216.59</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
       <c r="A245" s="2" t="s">
         <v>370</v>
       </c>
@@ -6784,8 +7516,11 @@
       <c r="E245" s="6">
         <v>2826.5</v>
       </c>
-    </row>
-    <row r="246" spans="1:5">
+      <c r="F245" s="6">
+        <v>2826.5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
       <c r="A246" s="2" t="s">
         <v>372</v>
       </c>
@@ -6801,8 +7536,11 @@
       <c r="E246" s="6">
         <v>2327.3200000000002</v>
       </c>
-    </row>
-    <row r="247" spans="1:5">
+      <c r="F246" s="6">
+        <v>2327.3200000000002</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
       <c r="A247" s="2" t="s">
         <v>372</v>
       </c>
@@ -6818,8 +7556,11 @@
       <c r="E247" s="5">
         <v>506.52</v>
       </c>
-    </row>
-    <row r="248" spans="1:5">
+      <c r="F247" s="5">
+        <v>506.52</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248" s="2" t="s">
         <v>372</v>
       </c>
@@ -6835,8 +7576,11 @@
       <c r="E248" s="6">
         <v>1786.76</v>
       </c>
-    </row>
-    <row r="249" spans="1:5">
+      <c r="F248" s="6">
+        <v>1786.76</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
       <c r="A249" s="2" t="s">
         <v>378</v>
       </c>
@@ -6852,8 +7596,11 @@
       <c r="E249" s="6">
         <v>1746.34</v>
       </c>
-    </row>
-    <row r="250" spans="1:5">
+      <c r="F249" s="6">
+        <v>1746.34</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
       <c r="A250" s="2" t="s">
         <v>378</v>
       </c>
@@ -6869,8 +7616,11 @@
       <c r="E250" s="5">
         <v>98.01</v>
       </c>
-    </row>
-    <row r="251" spans="1:5">
+      <c r="F250" s="5">
+        <v>98.01</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
       <c r="A251" s="2" t="s">
         <v>378</v>
       </c>
@@ -6886,8 +7636,11 @@
       <c r="E251" s="6">
         <v>1578.01</v>
       </c>
-    </row>
-    <row r="252" spans="1:5">
+      <c r="F251" s="6">
+        <v>1578.01</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
       <c r="A252" s="2" t="s">
         <v>378</v>
       </c>
@@ -6903,8 +7656,11 @@
       <c r="E252" s="5">
         <v>361.77</v>
       </c>
-    </row>
-    <row r="253" spans="1:5">
+      <c r="F252" s="5">
+        <v>361.77</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
       <c r="A253" s="2" t="s">
         <v>378</v>
       </c>
@@ -6920,8 +7676,11 @@
       <c r="E253" s="6">
         <v>1156.58</v>
       </c>
-    </row>
-    <row r="254" spans="1:5">
+      <c r="F253" s="6">
+        <v>1156.58</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
       <c r="A254" s="2" t="s">
         <v>378</v>
       </c>
@@ -6937,8 +7696,11 @@
       <c r="E254" s="5">
         <v>786.5</v>
       </c>
-    </row>
-    <row r="255" spans="1:5">
+      <c r="F254" s="5">
+        <v>786.5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
       <c r="A255" s="2" t="s">
         <v>378</v>
       </c>
@@ -6954,8 +7716,11 @@
       <c r="E255" s="6">
         <v>1479.19</v>
       </c>
-    </row>
-    <row r="256" spans="1:5">
+      <c r="F255" s="6">
+        <v>1479.19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
       <c r="A256" s="2" t="s">
         <v>387</v>
       </c>
@@ -6971,8 +7736,11 @@
       <c r="E256" s="5">
         <v>224.83</v>
       </c>
-    </row>
-    <row r="257" spans="1:5">
+      <c r="F256" s="5">
+        <v>224.83</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" s="2" t="s">
         <v>387</v>
       </c>
@@ -6988,8 +7756,11 @@
       <c r="E257" s="5">
         <v>483.88</v>
       </c>
-    </row>
-    <row r="258" spans="1:5">
+      <c r="F257" s="5">
+        <v>483.88</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" s="2" t="s">
         <v>387</v>
       </c>
@@ -7005,8 +7776,11 @@
       <c r="E258" s="5">
         <v>634.45000000000005</v>
       </c>
-    </row>
-    <row r="259" spans="1:5">
+      <c r="F258" s="5">
+        <v>634.45000000000005</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" s="2" t="s">
         <v>387</v>
       </c>
@@ -7022,8 +7796,11 @@
       <c r="E259" s="6">
         <v>1258.33</v>
       </c>
-    </row>
-    <row r="260" spans="1:5">
+      <c r="F259" s="6">
+        <v>1258.33</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" s="2" t="s">
         <v>387</v>
       </c>
@@ -7039,8 +7816,11 @@
       <c r="E260" s="5">
         <v>703.97</v>
       </c>
-    </row>
-    <row r="261" spans="1:5">
+      <c r="F260" s="5">
+        <v>703.97</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" s="2" t="s">
         <v>387</v>
       </c>
@@ -7056,8 +7836,11 @@
       <c r="E261" s="5">
         <v>522.53</v>
       </c>
-    </row>
-    <row r="262" spans="1:5">
+      <c r="F261" s="5">
+        <v>522.53</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" s="2" t="s">
         <v>387</v>
       </c>
@@ -7073,8 +7856,11 @@
       <c r="E262" s="5">
         <v>268.63</v>
       </c>
-    </row>
-    <row r="263" spans="1:5">
+      <c r="F262" s="5">
+        <v>268.63</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" s="2" t="s">
         <v>387</v>
       </c>
@@ -7090,8 +7876,11 @@
       <c r="E263" s="5">
         <v>110.33</v>
       </c>
-    </row>
-    <row r="264" spans="1:5">
+      <c r="F263" s="5">
+        <v>110.33</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" s="2" t="s">
         <v>387</v>
       </c>
@@ -7107,8 +7896,11 @@
       <c r="E264" s="5">
         <v>598.75</v>
       </c>
-    </row>
-    <row r="265" spans="1:5">
+      <c r="F264" s="5">
+        <v>598.75</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" s="2" t="s">
         <v>387</v>
       </c>
@@ -7124,8 +7916,11 @@
       <c r="E265" s="5">
         <v>609.71</v>
       </c>
-    </row>
-    <row r="266" spans="1:5">
+      <c r="F265" s="5">
+        <v>609.71</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" s="2" t="s">
         <v>387</v>
       </c>
@@ -7141,8 +7936,11 @@
       <c r="E266" s="5">
         <v>136.43</v>
       </c>
-    </row>
-    <row r="267" spans="1:5">
+      <c r="F266" s="5">
+        <v>136.43</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" s="2" t="s">
         <v>397</v>
       </c>
@@ -7158,8 +7956,11 @@
       <c r="E267" s="6">
         <v>1222.1600000000001</v>
       </c>
-    </row>
-    <row r="268" spans="1:5">
+      <c r="F267" s="6">
+        <v>1222.1600000000001</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" s="2" t="s">
         <v>397</v>
       </c>
@@ -7175,8 +7976,11 @@
       <c r="E268" s="5">
         <v>491.69</v>
       </c>
-    </row>
-    <row r="269" spans="1:5">
+      <c r="F268" s="5">
+        <v>491.69</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" s="2" t="s">
         <v>397</v>
       </c>
@@ -7192,8 +7996,11 @@
       <c r="E269" s="5">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="270" spans="1:5">
+      <c r="F269" s="5">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" s="2" t="s">
         <v>402</v>
       </c>
@@ -7209,8 +8016,11 @@
       <c r="E270" s="5">
         <v>953.74</v>
       </c>
-    </row>
-    <row r="271" spans="1:5">
+      <c r="F270" s="5">
+        <v>953.74</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" s="2" t="s">
         <v>402</v>
       </c>
@@ -7226,8 +8036,11 @@
       <c r="E271" s="5">
         <v>607.19000000000005</v>
       </c>
-    </row>
-    <row r="272" spans="1:5">
+      <c r="F271" s="5">
+        <v>607.19000000000005</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" s="2" t="s">
         <v>402</v>
       </c>
@@ -7243,8 +8056,11 @@
       <c r="E272" s="5">
         <v>250.31</v>
       </c>
-    </row>
-    <row r="273" spans="1:5">
+      <c r="F272" s="5">
+        <v>250.31</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" s="2" t="s">
         <v>402</v>
       </c>
@@ -7260,8 +8076,11 @@
       <c r="E273" s="5">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="274" spans="1:5">
+      <c r="F273" s="5">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" s="2" t="s">
         <v>408</v>
       </c>
@@ -7277,8 +8096,11 @@
       <c r="E274" s="5">
         <v>91.86</v>
       </c>
-    </row>
-    <row r="275" spans="1:5">
+      <c r="F274" s="5">
+        <v>91.86</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" s="2" t="s">
         <v>408</v>
       </c>
@@ -7294,8 +8116,11 @@
       <c r="E275" s="6">
         <v>3705.98</v>
       </c>
-    </row>
-    <row r="276" spans="1:5">
+      <c r="F275" s="6">
+        <v>3705.98</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" s="2" t="s">
         <v>408</v>
       </c>
@@ -7311,8 +8136,11 @@
       <c r="E276" s="5">
         <v>261.86</v>
       </c>
-    </row>
-    <row r="277" spans="1:5">
+      <c r="F276" s="5">
+        <v>261.86</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" s="2" t="s">
         <v>408</v>
       </c>
@@ -7328,8 +8156,11 @@
       <c r="E277" s="5">
         <v>772.98</v>
       </c>
-    </row>
-    <row r="278" spans="1:5">
+      <c r="F277" s="5">
+        <v>772.98</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" s="2" t="s">
         <v>408</v>
       </c>
@@ -7345,8 +8176,11 @@
       <c r="E278" s="5">
         <v>731.45</v>
       </c>
-    </row>
-    <row r="279" spans="1:5">
+      <c r="F278" s="5">
+        <v>731.45</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" s="2" t="s">
         <v>408</v>
       </c>
@@ -7362,8 +8196,11 @@
       <c r="E279" s="6">
         <v>1310.6199999999999</v>
       </c>
-    </row>
-    <row r="280" spans="1:5">
+      <c r="F279" s="6">
+        <v>1310.6199999999999</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" s="2" t="s">
         <v>408</v>
       </c>
@@ -7379,8 +8216,11 @@
       <c r="E280" s="5">
         <v>749.9</v>
       </c>
-    </row>
-    <row r="281" spans="1:5">
+      <c r="F280" s="5">
+        <v>749.9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" s="2" t="s">
         <v>408</v>
       </c>
@@ -7396,8 +8236,11 @@
       <c r="E281" s="6">
         <v>1994.85</v>
       </c>
-    </row>
-    <row r="282" spans="1:5">
+      <c r="F281" s="6">
+        <v>1994.85</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
         <v>408</v>
       </c>
@@ -7413,8 +8256,11 @@
       <c r="E282" s="5">
         <v>648.86</v>
       </c>
-    </row>
-    <row r="283" spans="1:5">
+      <c r="F282" s="5">
+        <v>648.86</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" s="2" t="s">
         <v>408</v>
       </c>
@@ -7430,8 +8276,11 @@
       <c r="E283" s="6">
         <v>1620.7</v>
       </c>
-    </row>
-    <row r="284" spans="1:5">
+      <c r="F283" s="6">
+        <v>1620.7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" s="2" t="s">
         <v>408</v>
       </c>
@@ -7447,8 +8296,11 @@
       <c r="E284" s="5">
         <v>259.98</v>
       </c>
-    </row>
-    <row r="285" spans="1:5">
+      <c r="F284" s="5">
+        <v>259.98</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" s="2" t="s">
         <v>408</v>
       </c>
@@ -7464,8 +8316,11 @@
       <c r="E285" s="6">
         <v>3358.91</v>
       </c>
-    </row>
-    <row r="286" spans="1:5">
+      <c r="F285" s="6">
+        <v>3358.91</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
         <v>408</v>
       </c>
@@ -7481,8 +8336,11 @@
       <c r="E286" s="5">
         <v>860.86</v>
       </c>
-    </row>
-    <row r="287" spans="1:5">
+      <c r="F286" s="5">
+        <v>860.86</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" s="2" t="s">
         <v>408</v>
       </c>
@@ -7498,8 +8356,11 @@
       <c r="E287" s="5">
         <v>986.83</v>
       </c>
-    </row>
-    <row r="288" spans="1:5">
+      <c r="F287" s="5">
+        <v>986.83</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" s="2" t="s">
         <v>408</v>
       </c>
@@ -7515,8 +8376,11 @@
       <c r="E288" s="5">
         <v>268.77999999999997</v>
       </c>
-    </row>
-    <row r="289" spans="1:5">
+      <c r="F288" s="5">
+        <v>268.77999999999997</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" s="2" t="s">
         <v>408</v>
       </c>
@@ -7532,8 +8396,11 @@
       <c r="E289" s="5">
         <v>259.04000000000002</v>
       </c>
-    </row>
-    <row r="290" spans="1:5">
+      <c r="F289" s="5">
+        <v>259.04000000000002</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" s="2" t="s">
         <v>116</v>
       </c>
@@ -7549,8 +8416,11 @@
       <c r="E290" s="5">
         <v>729.63</v>
       </c>
-    </row>
-    <row r="291" spans="1:5">
+      <c r="F290" s="5">
+        <v>729.63</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" s="2" t="s">
         <v>116</v>
       </c>
@@ -7566,8 +8436,11 @@
       <c r="E291" s="5">
         <v>349.33</v>
       </c>
-    </row>
-    <row r="292" spans="1:5">
+      <c r="F291" s="5">
+        <v>349.33</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" s="2" t="s">
         <v>116</v>
       </c>
@@ -7583,8 +8456,11 @@
       <c r="E292" s="5">
         <v>530.57000000000005</v>
       </c>
-    </row>
-    <row r="293" spans="1:5">
+      <c r="F292" s="5">
+        <v>530.57000000000005</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" s="2" t="s">
         <v>116</v>
       </c>
@@ -7600,8 +8476,11 @@
       <c r="E293" s="6">
         <v>1109.42</v>
       </c>
-    </row>
-    <row r="294" spans="1:5">
+      <c r="F293" s="6">
+        <v>1109.42</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" s="2" t="s">
         <v>116</v>
       </c>
@@ -7617,8 +8496,11 @@
       <c r="E294" s="5">
         <v>257.98</v>
       </c>
-    </row>
-    <row r="295" spans="1:5">
+      <c r="F294" s="5">
+        <v>257.98</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" s="2" t="s">
         <v>116</v>
       </c>
@@ -7634,8 +8516,11 @@
       <c r="E295" s="5">
         <v>246.58</v>
       </c>
-    </row>
-    <row r="296" spans="1:5">
+      <c r="F295" s="5">
+        <v>246.58</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" s="2" t="s">
         <v>116</v>
       </c>
@@ -7651,8 +8536,11 @@
       <c r="E296" s="5">
         <v>553.42999999999995</v>
       </c>
-    </row>
-    <row r="297" spans="1:5">
+      <c r="F296" s="5">
+        <v>553.42999999999995</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
       <c r="A297" s="2" t="s">
         <v>116</v>
       </c>
@@ -7668,8 +8556,11 @@
       <c r="E297" s="5">
         <v>519.86</v>
       </c>
-    </row>
-    <row r="298" spans="1:5">
+      <c r="F297" s="5">
+        <v>519.86</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
       <c r="A298" s="2" t="s">
         <v>430</v>
       </c>
@@ -7685,8 +8576,11 @@
       <c r="E298" s="6">
         <v>2437.29</v>
       </c>
-    </row>
-    <row r="299" spans="1:5">
+      <c r="F298" s="6">
+        <v>2437.29</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
       <c r="A299" s="2" t="s">
         <v>430</v>
       </c>
@@ -7702,8 +8596,11 @@
       <c r="E299" s="5">
         <v>403.75</v>
       </c>
-    </row>
-    <row r="300" spans="1:5">
+      <c r="F299" s="5">
+        <v>403.75</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
       <c r="A300" s="2" t="s">
         <v>430</v>
       </c>
@@ -7719,8 +8616,11 @@
       <c r="E300" s="5">
         <v>326.95</v>
       </c>
-    </row>
-    <row r="301" spans="1:5">
+      <c r="F300" s="5">
+        <v>326.95</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
       <c r="A301" s="2" t="s">
         <v>430</v>
       </c>
@@ -7736,8 +8636,11 @@
       <c r="E301" s="5">
         <v>708.92</v>
       </c>
-    </row>
-    <row r="302" spans="1:5">
+      <c r="F301" s="5">
+        <v>708.92</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
       <c r="A302" s="2" t="s">
         <v>430</v>
       </c>
@@ -7753,8 +8656,11 @@
       <c r="E302" s="5">
         <v>170.36</v>
       </c>
-    </row>
-    <row r="303" spans="1:5">
+      <c r="F302" s="5">
+        <v>170.36</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
       <c r="A303" s="2" t="s">
         <v>430</v>
       </c>
@@ -7770,8 +8676,11 @@
       <c r="E303" s="5">
         <v>417.37</v>
       </c>
-    </row>
-    <row r="304" spans="1:5">
+      <c r="F303" s="5">
+        <v>417.37</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
       <c r="A304" s="2" t="s">
         <v>430</v>
       </c>
@@ -7787,8 +8696,11 @@
       <c r="E304" s="5">
         <v>543.71</v>
       </c>
-    </row>
-    <row r="305" spans="1:5">
+      <c r="F304" s="5">
+        <v>543.71</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
       <c r="A305" s="2" t="s">
         <v>430</v>
       </c>
@@ -7804,8 +8716,11 @@
       <c r="E305" s="5">
         <v>351.53</v>
       </c>
-    </row>
-    <row r="306" spans="1:5">
+      <c r="F305" s="5">
+        <v>351.53</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
       <c r="A306" s="2" t="s">
         <v>441</v>
       </c>
@@ -7821,8 +8736,11 @@
       <c r="E306" s="6">
         <v>1448.37</v>
       </c>
-    </row>
-    <row r="307" spans="1:5">
+      <c r="F306" s="6">
+        <v>1448.37</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
       <c r="A307" s="2" t="s">
         <v>441</v>
       </c>
@@ -7838,8 +8756,11 @@
       <c r="E307" s="6">
         <v>1380.29</v>
       </c>
-    </row>
-    <row r="308" spans="1:5">
+      <c r="F307" s="6">
+        <v>1380.29</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
       <c r="A308" s="2" t="s">
         <v>444</v>
       </c>
@@ -7855,8 +8776,11 @@
       <c r="E308" s="5">
         <v>498.17</v>
       </c>
-    </row>
-    <row r="309" spans="1:5">
+      <c r="F308" s="5">
+        <v>498.17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
       <c r="A309" s="2" t="s">
         <v>444</v>
       </c>
@@ -7872,8 +8796,11 @@
       <c r="E309" s="6">
         <v>1575.72</v>
       </c>
-    </row>
-    <row r="310" spans="1:5">
+      <c r="F309" s="6">
+        <v>1575.72</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
       <c r="A310" s="2" t="s">
         <v>444</v>
       </c>
@@ -7889,8 +8816,11 @@
       <c r="E310" s="5">
         <v>63.48</v>
       </c>
-    </row>
-    <row r="311" spans="1:5">
+      <c r="F310" s="5">
+        <v>63.48</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
       <c r="A311" s="2" t="s">
         <v>444</v>
       </c>
@@ -7906,8 +8836,11 @@
       <c r="E311" s="5">
         <v>93.8</v>
       </c>
-    </row>
-    <row r="312" spans="1:5">
+      <c r="F311" s="5">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
       <c r="A312" s="2" t="s">
         <v>444</v>
       </c>
@@ -7923,8 +8856,11 @@
       <c r="E312" s="5">
         <v>852.76</v>
       </c>
-    </row>
-    <row r="313" spans="1:5">
+      <c r="F312" s="5">
+        <v>852.76</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
       <c r="A313" s="2" t="s">
         <v>444</v>
       </c>
@@ -7940,8 +8876,11 @@
       <c r="E313" s="5">
         <v>119.58</v>
       </c>
-    </row>
-    <row r="314" spans="1:5">
+      <c r="F313" s="5">
+        <v>119.58</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
       <c r="A314" s="2" t="s">
         <v>444</v>
       </c>
@@ -7957,8 +8896,11 @@
       <c r="E314" s="5">
         <v>467.32</v>
       </c>
-    </row>
-    <row r="315" spans="1:5">
+      <c r="F314" s="5">
+        <v>467.32</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
       <c r="A315" s="2" t="s">
         <v>457</v>
       </c>
@@ -7974,8 +8916,11 @@
       <c r="E315" s="5">
         <v>768.67</v>
       </c>
-    </row>
-    <row r="316" spans="1:5">
+      <c r="F315" s="5">
+        <v>768.67</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
       <c r="A316" s="2" t="s">
         <v>457</v>
       </c>
@@ -7991,8 +8936,11 @@
       <c r="E316" s="5">
         <v>778.34</v>
       </c>
-    </row>
-    <row r="317" spans="1:5">
+      <c r="F316" s="5">
+        <v>778.34</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
       <c r="A317" s="2" t="s">
         <v>457</v>
       </c>
@@ -8008,8 +8956,11 @@
       <c r="E317" s="6">
         <v>1052.3699999999999</v>
       </c>
-    </row>
-    <row r="318" spans="1:5">
+      <c r="F317" s="6">
+        <v>1052.3699999999999</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
         <v>457</v>
       </c>
@@ -8025,8 +8976,11 @@
       <c r="E318" s="6">
         <v>1352.99</v>
       </c>
-    </row>
-    <row r="319" spans="1:5">
+      <c r="F318" s="6">
+        <v>1352.99</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
         <v>457</v>
       </c>
@@ -8042,8 +8996,11 @@
       <c r="E319" s="5">
         <v>164.08</v>
       </c>
-    </row>
-    <row r="320" spans="1:5">
+      <c r="F319" s="5">
+        <v>164.08</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
         <v>457</v>
       </c>
@@ -8059,8 +9016,11 @@
       <c r="E320" s="5">
         <v>374.52</v>
       </c>
-    </row>
-    <row r="321" spans="1:5">
+      <c r="F320" s="5">
+        <v>374.52</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
       <c r="A321" s="2" t="s">
         <v>457</v>
       </c>
@@ -8076,8 +9036,11 @@
       <c r="E321" s="6">
         <v>1873.63</v>
       </c>
-    </row>
-    <row r="322" spans="1:5">
+      <c r="F321" s="6">
+        <v>1873.63</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
       <c r="A322" s="2" t="s">
         <v>457</v>
       </c>
@@ -8093,8 +9056,11 @@
       <c r="E322" s="5">
         <v>397.56</v>
       </c>
-    </row>
-    <row r="323" spans="1:5">
+      <c r="F322" s="5">
+        <v>397.56</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
       <c r="A323" s="2" t="s">
         <v>457</v>
       </c>
@@ -8110,8 +9076,11 @@
       <c r="E323" s="6">
         <v>1135.22</v>
       </c>
-    </row>
-    <row r="324" spans="1:5">
+      <c r="F323" s="6">
+        <v>1135.22</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
         <v>457</v>
       </c>
@@ -8127,8 +9096,11 @@
       <c r="E324" s="5">
         <v>910.84</v>
       </c>
-    </row>
-    <row r="325" spans="1:5">
+      <c r="F324" s="5">
+        <v>910.84</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
       <c r="A325" s="2" t="s">
         <v>457</v>
       </c>
@@ -8144,8 +9116,11 @@
       <c r="E325" s="6">
         <v>1313.79</v>
       </c>
-    </row>
-    <row r="326" spans="1:5">
+      <c r="F325" s="6">
+        <v>1313.79</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
         <v>457</v>
       </c>
@@ -8161,8 +9136,11 @@
       <c r="E326" s="5">
         <v>374.52</v>
       </c>
-    </row>
-    <row r="327" spans="1:5">
+      <c r="F326" s="5">
+        <v>374.52</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
         <v>457</v>
       </c>
@@ -8178,8 +9156,11 @@
       <c r="E327" s="5">
         <v>633.09</v>
       </c>
-    </row>
-    <row r="328" spans="1:5">
+      <c r="F327" s="5">
+        <v>633.09</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
         <v>457</v>
       </c>
@@ -8195,8 +9176,11 @@
       <c r="E328" s="6">
         <v>1120.5</v>
       </c>
-    </row>
-    <row r="329" spans="1:5">
+      <c r="F328" s="6">
+        <v>1120.5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
       <c r="A329" s="2" t="s">
         <v>457</v>
       </c>
@@ -8212,8 +9196,11 @@
       <c r="E329" s="6">
         <v>1202.8499999999999</v>
       </c>
-    </row>
-    <row r="330" spans="1:5">
+      <c r="F329" s="6">
+        <v>1202.8499999999999</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
       <c r="A330" s="2" t="s">
         <v>457</v>
       </c>
@@ -8229,8 +9216,11 @@
       <c r="E330" s="5">
         <v>651.34</v>
       </c>
-    </row>
-    <row r="331" spans="1:5">
+      <c r="F330" s="5">
+        <v>651.34</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
       <c r="A331" s="2" t="s">
         <v>457</v>
       </c>
@@ -8246,8 +9236,11 @@
       <c r="E331" s="6">
         <v>2250.61</v>
       </c>
-    </row>
-    <row r="332" spans="1:5">
+      <c r="F331" s="6">
+        <v>2250.61</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
         <v>457</v>
       </c>
@@ -8263,8 +9256,11 @@
       <c r="E332" s="5">
         <v>303.25</v>
       </c>
-    </row>
-    <row r="333" spans="1:5">
+      <c r="F332" s="5">
+        <v>303.25</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
       <c r="A333" s="2" t="s">
         <v>474</v>
       </c>
@@ -8280,8 +9276,11 @@
       <c r="E333" s="5">
         <v>136.09</v>
       </c>
-    </row>
-    <row r="334" spans="1:5">
+      <c r="F333" s="5">
+        <v>136.09</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
         <v>474</v>
       </c>
@@ -8297,8 +9296,11 @@
       <c r="E334" s="6">
         <v>1170.74</v>
       </c>
-    </row>
-    <row r="335" spans="1:5">
+      <c r="F334" s="6">
+        <v>1170.74</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
         <v>474</v>
       </c>
@@ -8314,8 +9316,11 @@
       <c r="E335" s="6">
         <v>1356.94</v>
       </c>
-    </row>
-    <row r="336" spans="1:5">
+      <c r="F335" s="6">
+        <v>1356.94</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
         <v>474</v>
       </c>
@@ -8331,8 +9336,11 @@
       <c r="E336" s="6">
         <v>1873.85</v>
       </c>
-    </row>
-    <row r="337" spans="1:5">
+      <c r="F336" s="6">
+        <v>1873.85</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
         <v>474</v>
       </c>
@@ -8348,8 +9356,11 @@
       <c r="E337" s="5">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="338" spans="1:5">
+      <c r="F337" s="5">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
       <c r="A338" s="2" t="s">
         <v>474</v>
       </c>
@@ -8365,8 +9376,11 @@
       <c r="E338" s="6">
         <v>1565.58</v>
       </c>
-    </row>
-    <row r="339" spans="1:5">
+      <c r="F338" s="6">
+        <v>1565.58</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
       <c r="A339" s="2" t="s">
         <v>484</v>
       </c>
@@ -8382,8 +9396,11 @@
       <c r="E339" s="5">
         <v>359.26</v>
       </c>
-    </row>
-    <row r="340" spans="1:5">
+      <c r="F339" s="5">
+        <v>359.26</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
       <c r="A340" s="2" t="s">
         <v>484</v>
       </c>
@@ -8399,8 +9416,11 @@
       <c r="E340" s="5">
         <v>117.98</v>
       </c>
-    </row>
-    <row r="341" spans="1:5">
+      <c r="F340" s="5">
+        <v>117.98</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
       <c r="A341" s="2" t="s">
         <v>487</v>
       </c>
@@ -8416,8 +9436,11 @@
       <c r="E341" s="5">
         <v>360.44</v>
       </c>
-    </row>
-    <row r="342" spans="1:5">
+      <c r="F341" s="5">
+        <v>360.44</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
       <c r="A342" s="2" t="s">
         <v>487</v>
       </c>
@@ -8433,8 +9456,11 @@
       <c r="E342" s="5">
         <v>315.98</v>
       </c>
-    </row>
-    <row r="343" spans="1:5">
+      <c r="F342" s="5">
+        <v>315.98</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
       <c r="A343" s="2" t="s">
         <v>487</v>
       </c>
@@ -8450,8 +9476,11 @@
       <c r="E343" s="6">
         <v>1012.32</v>
       </c>
-    </row>
-    <row r="344" spans="1:5">
+      <c r="F343" s="6">
+        <v>1012.32</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
       <c r="A344" s="2" t="s">
         <v>490</v>
       </c>
@@ -8467,8 +9496,11 @@
       <c r="E344" s="5">
         <v>598.82000000000005</v>
       </c>
-    </row>
-    <row r="345" spans="1:5">
+      <c r="F344" s="5">
+        <v>598.82000000000005</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
       <c r="A345" s="2" t="s">
         <v>493</v>
       </c>
@@ -8484,8 +9516,11 @@
       <c r="E345" s="5">
         <v>631.80999999999995</v>
       </c>
-    </row>
-    <row r="346" spans="1:5">
+      <c r="F345" s="5">
+        <v>631.80999999999995</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
       <c r="A346" s="2" t="s">
         <v>493</v>
       </c>
@@ -8501,8 +9536,11 @@
       <c r="E346" s="6">
         <v>1167.58</v>
       </c>
-    </row>
-    <row r="347" spans="1:5">
+      <c r="F346" s="6">
+        <v>1167.58</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
       <c r="A347" s="2" t="s">
         <v>496</v>
       </c>
@@ -8518,8 +9556,11 @@
       <c r="E347" s="6">
         <v>7003.29</v>
       </c>
-    </row>
-    <row r="348" spans="1:5">
+      <c r="F347" s="6">
+        <v>7003.29</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
       <c r="A348" s="2" t="s">
         <v>498</v>
       </c>
@@ -8535,8 +9576,11 @@
       <c r="E348" s="5">
         <v>-848.73</v>
       </c>
-    </row>
-    <row r="349" spans="1:5">
+      <c r="F348" s="5">
+        <v>-848.73</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
       <c r="A349" s="2" t="s">
         <v>500</v>
       </c>
@@ -8552,8 +9596,11 @@
       <c r="E349" s="6">
         <v>1106.8399999999999</v>
       </c>
-    </row>
-    <row r="350" spans="1:5">
+      <c r="F349" s="6">
+        <v>1106.8399999999999</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
         <v>500</v>
       </c>
@@ -8569,8 +9616,11 @@
       <c r="E350" s="5">
         <v>790.54</v>
       </c>
-    </row>
-    <row r="351" spans="1:5">
+      <c r="F350" s="5">
+        <v>790.54</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
       <c r="A351" s="2" t="s">
         <v>500</v>
       </c>
@@ -8586,8 +9636,11 @@
       <c r="E351" s="5">
         <v>920.54</v>
       </c>
-    </row>
-    <row r="352" spans="1:5">
+      <c r="F351" s="5">
+        <v>920.54</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
         <v>500</v>
       </c>
@@ -8603,8 +9656,11 @@
       <c r="E352" s="5">
         <v>253.83</v>
       </c>
-    </row>
-    <row r="353" spans="1:5">
+      <c r="F352" s="5">
+        <v>253.83</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
       <c r="A353" s="2" t="s">
         <v>500</v>
       </c>
@@ -8620,8 +9676,11 @@
       <c r="E353" s="5">
         <v>348.09</v>
       </c>
-    </row>
-    <row r="354" spans="1:5">
+      <c r="F353" s="5">
+        <v>348.09</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
         <v>504</v>
       </c>
@@ -8637,8 +9696,11 @@
       <c r="E354" s="5">
         <v>562.69000000000005</v>
       </c>
-    </row>
-    <row r="355" spans="1:5">
+      <c r="F354" s="5">
+        <v>562.69000000000005</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
       <c r="A355" s="2" t="s">
         <v>504</v>
       </c>
@@ -8654,8 +9716,11 @@
       <c r="E355" s="5">
         <v>455.71</v>
       </c>
-    </row>
-    <row r="356" spans="1:5">
+      <c r="F355" s="5">
+        <v>455.71</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
       <c r="A356" s="2" t="s">
         <v>507</v>
       </c>
@@ -8671,8 +9736,11 @@
       <c r="E356" s="6">
         <v>6553.85</v>
       </c>
-    </row>
-    <row r="357" spans="1:5">
+      <c r="F356" s="6">
+        <v>6553.85</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
       <c r="A357" s="2" t="s">
         <v>507</v>
       </c>
@@ -8688,8 +9756,11 @@
       <c r="E357" s="5">
         <v>377.52</v>
       </c>
-    </row>
-    <row r="358" spans="1:5">
+      <c r="F357" s="5">
+        <v>377.52</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
       <c r="A358" s="2" t="s">
         <v>507</v>
       </c>
@@ -8705,8 +9776,11 @@
       <c r="E358" s="5">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="359" spans="1:5">
+      <c r="F358" s="5">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
       <c r="A359" s="2" t="s">
         <v>507</v>
       </c>
@@ -8722,8 +9796,11 @@
       <c r="E359" s="6">
         <v>6789.59</v>
       </c>
-    </row>
-    <row r="360" spans="1:5">
+      <c r="F359" s="6">
+        <v>6789.59</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
         <v>507</v>
       </c>
@@ -8739,8 +9816,11 @@
       <c r="E360" s="6">
         <v>7272.38</v>
       </c>
-    </row>
-    <row r="361" spans="1:5">
+      <c r="F360" s="6">
+        <v>7272.38</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
       <c r="A361" s="2" t="s">
         <v>220</v>
       </c>
@@ -8756,8 +9836,11 @@
       <c r="E361" s="6">
         <v>1551.24</v>
       </c>
-    </row>
-    <row r="362" spans="1:5">
+      <c r="F361" s="6">
+        <v>1551.24</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
       <c r="A362" s="2" t="s">
         <v>220</v>
       </c>
@@ -8773,8 +9856,11 @@
       <c r="E362" s="5">
         <v>685.68</v>
       </c>
-    </row>
-    <row r="363" spans="1:5">
+      <c r="F362" s="5">
+        <v>685.68</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
       <c r="A363" s="2" t="s">
         <v>220</v>
       </c>
@@ -8790,8 +9876,11 @@
       <c r="E363" s="6">
         <v>2524.5100000000002</v>
       </c>
-    </row>
-    <row r="364" spans="1:5">
+      <c r="F363" s="6">
+        <v>2524.5100000000002</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
         <v>515</v>
       </c>
@@ -8807,8 +9896,11 @@
       <c r="E364" s="5">
         <v>631.74</v>
       </c>
-    </row>
-    <row r="365" spans="1:5">
+      <c r="F364" s="5">
+        <v>631.74</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
         <v>515</v>
       </c>
@@ -8824,8 +9916,11 @@
       <c r="E365" s="5">
         <v>692.41</v>
       </c>
-    </row>
-    <row r="366" spans="1:5">
+      <c r="F365" s="5">
+        <v>692.41</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
         <v>515</v>
       </c>
@@ -8841,8 +9936,11 @@
       <c r="E366" s="5">
         <v>-60.79</v>
       </c>
-    </row>
-    <row r="367" spans="1:5">
+      <c r="F366" s="5">
+        <v>-60.79</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
         <v>518</v>
       </c>
@@ -8858,8 +9956,11 @@
       <c r="E367" s="6">
         <v>1062.22</v>
       </c>
-    </row>
-    <row r="368" spans="1:5">
+      <c r="F367" s="6">
+        <v>1062.22</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
       <c r="A368" s="2" t="s">
         <v>518</v>
       </c>
@@ -8875,8 +9976,11 @@
       <c r="E368" s="6">
         <v>1401.95</v>
       </c>
-    </row>
-    <row r="369" spans="1:5">
+      <c r="F368" s="6">
+        <v>1401.95</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
         <v>518</v>
       </c>
@@ -8892,8 +9996,11 @@
       <c r="E369" s="6">
         <v>2527.83</v>
       </c>
-    </row>
-    <row r="370" spans="1:5">
+      <c r="F369" s="6">
+        <v>2527.83</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
       <c r="A370" s="2" t="s">
         <v>521</v>
       </c>
@@ -8909,8 +10016,11 @@
       <c r="E370" s="6">
         <v>1197.98</v>
       </c>
-    </row>
-    <row r="371" spans="1:5">
+      <c r="F370" s="6">
+        <v>1197.98</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
         <v>521</v>
       </c>
@@ -8926,8 +10036,11 @@
       <c r="E371" s="6">
         <v>1893.12</v>
       </c>
-    </row>
-    <row r="372" spans="1:5">
+      <c r="F371" s="6">
+        <v>1893.12</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
       <c r="A372" s="2" t="s">
         <v>521</v>
       </c>
@@ -8943,8 +10056,11 @@
       <c r="E372" s="5">
         <v>473.16</v>
       </c>
-    </row>
-    <row r="373" spans="1:5">
+      <c r="F372" s="5">
+        <v>473.16</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
         <v>521</v>
       </c>
@@ -8960,8 +10076,11 @@
       <c r="E373" s="6">
         <v>1150.99</v>
       </c>
-    </row>
-    <row r="374" spans="1:5">
+      <c r="F373" s="6">
+        <v>1150.99</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
         <v>521</v>
       </c>
@@ -8977,8 +10096,11 @@
       <c r="E374" s="5">
         <v>981.71</v>
       </c>
-    </row>
-    <row r="375" spans="1:5">
+      <c r="F374" s="5">
+        <v>981.71</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
         <v>521</v>
       </c>
@@ -8994,8 +10116,11 @@
       <c r="E375" s="5">
         <v>109.38</v>
       </c>
-    </row>
-    <row r="376" spans="1:5">
+      <c r="F375" s="5">
+        <v>109.38</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
       <c r="A376" s="2" t="s">
         <v>521</v>
       </c>
@@ -9011,8 +10136,11 @@
       <c r="E376" s="5">
         <v>981.71</v>
       </c>
-    </row>
-    <row r="377" spans="1:5">
+      <c r="F376" s="5">
+        <v>981.71</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
       <c r="A377" s="2" t="s">
         <v>530</v>
       </c>
@@ -9028,8 +10156,11 @@
       <c r="E377" s="6">
         <v>16800</v>
       </c>
-    </row>
-    <row r="378" spans="1:5">
+      <c r="F377" s="6">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
         <v>530</v>
       </c>
@@ -9045,8 +10176,11 @@
       <c r="E378" s="5">
         <v>594.21</v>
       </c>
-    </row>
-    <row r="379" spans="1:5">
+      <c r="F378" s="5">
+        <v>594.21</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
         <v>530</v>
       </c>
@@ -9062,8 +10196,11 @@
       <c r="E379" s="5">
         <v>416.84</v>
       </c>
-    </row>
-    <row r="380" spans="1:5">
+      <c r="F379" s="5">
+        <v>416.84</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
       <c r="A380" s="2" t="s">
         <v>530</v>
       </c>
@@ -9079,8 +10216,11 @@
       <c r="E380" s="5">
         <v>729.12</v>
       </c>
-    </row>
-    <row r="381" spans="1:5">
+      <c r="F380" s="5">
+        <v>729.12</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
       <c r="A381" s="2" t="s">
         <v>530</v>
       </c>
@@ -9096,8 +10236,11 @@
       <c r="E381" s="5">
         <v>356.73</v>
       </c>
-    </row>
-    <row r="382" spans="1:5">
+      <c r="F381" s="5">
+        <v>356.73</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
       <c r="A382" s="2" t="s">
         <v>530</v>
       </c>
@@ -9113,8 +10256,11 @@
       <c r="E382" s="5">
         <v>651.4</v>
       </c>
-    </row>
-    <row r="383" spans="1:5">
+      <c r="F382" s="5">
+        <v>651.4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
       <c r="A383" s="2" t="s">
         <v>530</v>
       </c>
@@ -9130,8 +10276,11 @@
       <c r="E383" s="5">
         <v>764.3</v>
       </c>
-    </row>
-    <row r="384" spans="1:5">
+      <c r="F383" s="5">
+        <v>764.3</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
       <c r="A384" s="2" t="s">
         <v>530</v>
       </c>
@@ -9147,8 +10296,11 @@
       <c r="E384" s="5">
         <v>729.12</v>
       </c>
-    </row>
-    <row r="385" spans="1:5">
+      <c r="F384" s="5">
+        <v>729.12</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
       <c r="A385" s="2" t="s">
         <v>530</v>
       </c>
@@ -9164,8 +10316,11 @@
       <c r="E385" s="5">
         <v>216.35</v>
       </c>
-    </row>
-    <row r="386" spans="1:5">
+      <c r="F385" s="5">
+        <v>216.35</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
       <c r="A386" s="2" t="s">
         <v>530</v>
       </c>
@@ -9181,8 +10336,11 @@
       <c r="E386" s="5">
         <v>597.20000000000005</v>
       </c>
-    </row>
-    <row r="387" spans="1:5">
+      <c r="F386" s="5">
+        <v>597.20000000000005</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
       <c r="A387" s="2" t="s">
         <v>530</v>
       </c>
@@ -9198,8 +10356,11 @@
       <c r="E387" s="6">
         <v>5600.79</v>
       </c>
-    </row>
-    <row r="388" spans="1:5">
+      <c r="F387" s="6">
+        <v>5600.79</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
       <c r="A388" s="2" t="s">
         <v>530</v>
       </c>
@@ -9215,8 +10376,11 @@
       <c r="E388" s="5">
         <v>652.29999999999995</v>
       </c>
-    </row>
-    <row r="389" spans="1:5">
+      <c r="F388" s="5">
+        <v>652.29999999999995</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
       <c r="A389" s="2" t="s">
         <v>530</v>
       </c>
@@ -9232,8 +10396,11 @@
       <c r="E389" s="6">
         <v>2042.43</v>
       </c>
-    </row>
-    <row r="390" spans="1:5">
+      <c r="F389" s="6">
+        <v>2042.43</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
       <c r="A390" s="2" t="s">
         <v>530</v>
       </c>
@@ -9249,8 +10416,11 @@
       <c r="E390" s="5">
         <v>870.5</v>
       </c>
-    </row>
-    <row r="391" spans="1:5">
+      <c r="F390" s="5">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
       <c r="A391" s="2" t="s">
         <v>530</v>
       </c>
@@ -9266,8 +10436,11 @@
       <c r="E391" s="6">
         <v>1009.8</v>
       </c>
-    </row>
-    <row r="392" spans="1:5">
+      <c r="F391" s="6">
+        <v>1009.8</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
       <c r="A392" s="2" t="s">
         <v>530</v>
       </c>
@@ -9283,8 +10456,11 @@
       <c r="E392" s="5">
         <v>870.5</v>
       </c>
-    </row>
-    <row r="393" spans="1:5">
+      <c r="F392" s="5">
+        <v>870.5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
       <c r="A393" s="2" t="s">
         <v>530</v>
       </c>
@@ -9300,8 +10476,11 @@
       <c r="E393" s="5">
         <v>596.72</v>
       </c>
-    </row>
-    <row r="394" spans="1:5">
+      <c r="F393" s="5">
+        <v>596.72</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
       <c r="A394" s="2" t="s">
         <v>530</v>
       </c>
@@ -9317,8 +10496,11 @@
       <c r="E394" s="5">
         <v>736.72</v>
       </c>
-    </row>
-    <row r="395" spans="1:5">
+      <c r="F394" s="5">
+        <v>736.72</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
       <c r="A395" s="2" t="s">
         <v>530</v>
       </c>
@@ -9334,8 +10516,11 @@
       <c r="E395" s="5">
         <v>716.1</v>
       </c>
-    </row>
-    <row r="396" spans="1:5">
+      <c r="F395" s="5">
+        <v>716.1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
       <c r="A396" s="2" t="s">
         <v>530</v>
       </c>
@@ -9351,8 +10536,11 @@
       <c r="E396" s="5">
         <v>564.66</v>
       </c>
-    </row>
-    <row r="397" spans="1:5">
+      <c r="F396" s="5">
+        <v>564.66</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
       <c r="A397" s="2" t="s">
         <v>530</v>
       </c>
@@ -9368,8 +10556,11 @@
       <c r="E397" s="5">
         <v>898.02</v>
       </c>
-    </row>
-    <row r="398" spans="1:5">
+      <c r="F397" s="5">
+        <v>898.02</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
       <c r="A398" s="2" t="s">
         <v>530</v>
       </c>
@@ -9385,8 +10576,11 @@
       <c r="E398" s="5">
         <v>898.02</v>
       </c>
-    </row>
-    <row r="399" spans="1:5">
+      <c r="F398" s="5">
+        <v>898.02</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6">
       <c r="A399" s="2" t="s">
         <v>530</v>
       </c>
@@ -9402,8 +10596,11 @@
       <c r="E399" s="5">
         <v>651.29999999999995</v>
       </c>
-    </row>
-    <row r="400" spans="1:5">
+      <c r="F399" s="5">
+        <v>651.29999999999995</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
       <c r="A400" s="2" t="s">
         <v>530</v>
       </c>
@@ -9419,8 +10616,11 @@
       <c r="E400" s="6">
         <v>-36000</v>
       </c>
-    </row>
-    <row r="401" spans="1:5">
+      <c r="F400" s="6">
+        <v>-36000</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
       <c r="A401" s="2" t="s">
         <v>573</v>
       </c>
@@ -9436,8 +10636,11 @@
       <c r="E401" s="5">
         <v>142.72999999999999</v>
       </c>
-    </row>
-    <row r="402" spans="1:5">
+      <c r="F401" s="5">
+        <v>142.72999999999999</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
       <c r="A402" s="2" t="s">
         <v>575</v>
       </c>
@@ -9453,8 +10656,11 @@
       <c r="E402" s="6">
         <v>2107.64</v>
       </c>
-    </row>
-    <row r="403" spans="1:5">
+      <c r="F402" s="6">
+        <v>2107.64</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
       <c r="A403" s="2" t="s">
         <v>575</v>
       </c>
@@ -9470,8 +10676,11 @@
       <c r="E403" s="6">
         <v>6835.49</v>
       </c>
-    </row>
-    <row r="404" spans="1:5">
+      <c r="F403" s="6">
+        <v>6835.49</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
       <c r="A404" s="2" t="s">
         <v>575</v>
       </c>
@@ -9487,8 +10696,11 @@
       <c r="E404" s="5">
         <v>374.52</v>
       </c>
-    </row>
-    <row r="405" spans="1:5">
+      <c r="F404" s="5">
+        <v>374.52</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
       <c r="A405" s="2" t="s">
         <v>575</v>
       </c>
@@ -9504,8 +10716,11 @@
       <c r="E405" s="6">
         <v>10694.76</v>
       </c>
-    </row>
-    <row r="406" spans="1:5">
+      <c r="F405" s="6">
+        <v>10694.76</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
       <c r="A406" s="2" t="s">
         <v>575</v>
       </c>
@@ -9521,8 +10736,11 @@
       <c r="E406" s="5">
         <v>647.5</v>
       </c>
-    </row>
-    <row r="407" spans="1:5">
+      <c r="F406" s="5">
+        <v>647.5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
       <c r="A407" s="2" t="s">
         <v>575</v>
       </c>
@@ -9538,8 +10756,11 @@
       <c r="E407" s="6">
         <v>14078.93</v>
       </c>
-    </row>
-    <row r="408" spans="1:5">
+      <c r="F407" s="6">
+        <v>14078.93</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
       <c r="A408" s="2" t="s">
         <v>583</v>
       </c>
@@ -9555,8 +10776,11 @@
       <c r="E408" s="5">
         <v>337.41</v>
       </c>
-    </row>
-    <row r="409" spans="1:5">
+      <c r="F408" s="5">
+        <v>337.41</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6">
       <c r="A409" s="2" t="s">
         <v>583</v>
       </c>
@@ -9572,8 +10796,11 @@
       <c r="E409" s="5">
         <v>235.95</v>
       </c>
-    </row>
-    <row r="410" spans="1:5">
+      <c r="F409" s="5">
+        <v>235.95</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6">
       <c r="A410" s="2" t="s">
         <v>586</v>
       </c>
@@ -9589,8 +10816,11 @@
       <c r="E410" s="6">
         <v>3879.17</v>
       </c>
-    </row>
-    <row r="411" spans="1:5">
+      <c r="F410" s="6">
+        <v>3879.17</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
       <c r="A411" s="2" t="s">
         <v>586</v>
       </c>
@@ -9606,8 +10836,11 @@
       <c r="E411" s="5">
         <v>589.9</v>
       </c>
-    </row>
-    <row r="412" spans="1:5">
+      <c r="F411" s="5">
+        <v>589.9</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
       <c r="A412" s="2" t="s">
         <v>586</v>
       </c>
@@ -9623,8 +10856,11 @@
       <c r="E412" s="6">
         <v>1565.3</v>
       </c>
-    </row>
-    <row r="413" spans="1:5">
+      <c r="F412" s="6">
+        <v>1565.3</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
       <c r="A413" s="2" t="s">
         <v>586</v>
       </c>
@@ -9640,8 +10876,11 @@
       <c r="E413" s="5">
         <v>752.71</v>
       </c>
-    </row>
-    <row r="414" spans="1:5">
+      <c r="F413" s="5">
+        <v>752.71</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
       <c r="A414" s="2" t="s">
         <v>591</v>
       </c>
@@ -9657,8 +10896,11 @@
       <c r="E414" s="6">
         <v>1146.3599999999999</v>
       </c>
-    </row>
-    <row r="415" spans="1:5">
+      <c r="F414" s="6">
+        <v>1146.3599999999999</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
       <c r="A415" s="2" t="s">
         <v>593</v>
       </c>
@@ -9674,8 +10916,11 @@
       <c r="E415" s="6">
         <v>1009.62</v>
       </c>
-    </row>
-    <row r="416" spans="1:5">
+      <c r="F415" s="6">
+        <v>1009.62</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
       <c r="A416" s="2" t="s">
         <v>593</v>
       </c>
@@ -9691,8 +10936,11 @@
       <c r="E416" s="6">
         <v>2684.64</v>
       </c>
-    </row>
-    <row r="417" spans="1:5">
+      <c r="F416" s="6">
+        <v>2684.64</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
       <c r="A417" s="2" t="s">
         <v>593</v>
       </c>
@@ -9708,8 +10956,11 @@
       <c r="E417" s="5">
         <v>980.1</v>
       </c>
-    </row>
-    <row r="418" spans="1:5">
+      <c r="F417" s="5">
+        <v>980.1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
       <c r="A418" s="2" t="s">
         <v>593</v>
       </c>
@@ -9725,8 +10976,11 @@
       <c r="E418" s="6">
         <v>1837.63</v>
       </c>
-    </row>
-    <row r="419" spans="1:5">
+      <c r="F418" s="6">
+        <v>1837.63</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
       <c r="A419" s="2" t="s">
         <v>593</v>
       </c>
@@ -9742,8 +10996,11 @@
       <c r="E419" s="5">
         <v>270.92</v>
       </c>
-    </row>
-    <row r="420" spans="1:5">
+      <c r="F419" s="5">
+        <v>270.92</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
       <c r="A420" s="2" t="s">
         <v>593</v>
       </c>
@@ -9759,8 +11016,11 @@
       <c r="E420" s="6">
         <v>1830.78</v>
       </c>
-    </row>
-    <row r="421" spans="1:5">
+      <c r="F420" s="6">
+        <v>1830.78</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
       <c r="A421" s="2" t="s">
         <v>599</v>
       </c>
@@ -9776,8 +11036,11 @@
       <c r="E421" s="5">
         <v>264.02999999999997</v>
       </c>
-    </row>
-    <row r="422" spans="1:5">
+      <c r="F421" s="5">
+        <v>264.02999999999997</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
       <c r="A422" s="2" t="s">
         <v>599</v>
       </c>
@@ -9793,8 +11056,11 @@
       <c r="E422" s="5">
         <v>569.84</v>
       </c>
-    </row>
-    <row r="423" spans="1:5">
+      <c r="F422" s="5">
+        <v>569.84</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
       <c r="A423" s="2" t="s">
         <v>599</v>
       </c>
@@ -9810,8 +11076,11 @@
       <c r="E423" s="5">
         <v>211.45</v>
       </c>
-    </row>
-    <row r="424" spans="1:5">
+      <c r="F423" s="5">
+        <v>211.45</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
       <c r="A424" s="2" t="s">
         <v>599</v>
       </c>
@@ -9827,8 +11096,11 @@
       <c r="E424" s="5">
         <v>92.34</v>
       </c>
-    </row>
-    <row r="425" spans="1:5">
+      <c r="F424" s="5">
+        <v>92.34</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
       <c r="A425" s="2" t="s">
         <v>599</v>
       </c>
@@ -9844,8 +11116,11 @@
       <c r="E425" s="5">
         <v>318.69</v>
       </c>
-    </row>
-    <row r="426" spans="1:5">
+      <c r="F425" s="5">
+        <v>318.69</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
       <c r="A426" s="2" t="s">
         <v>599</v>
       </c>
@@ -9861,8 +11136,11 @@
       <c r="E426" s="5">
         <v>501.26</v>
       </c>
-    </row>
-    <row r="427" spans="1:5">
+      <c r="F426" s="5">
+        <v>501.26</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
       <c r="A427" s="2" t="s">
         <v>611</v>
       </c>
@@ -9878,8 +11156,11 @@
       <c r="E427" s="5">
         <v>711.16</v>
       </c>
-    </row>
-    <row r="428" spans="1:5">
+      <c r="F427" s="5">
+        <v>711.16</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
       <c r="A428" s="2" t="s">
         <v>611</v>
       </c>
@@ -9895,8 +11176,11 @@
       <c r="E428" s="6">
         <v>3028.65</v>
       </c>
-    </row>
-    <row r="429" spans="1:5">
+      <c r="F428" s="6">
+        <v>3028.65</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
       <c r="A429" s="2" t="s">
         <v>611</v>
       </c>
@@ -9912,8 +11196,11 @@
       <c r="E429" s="5">
         <v>323.57</v>
       </c>
-    </row>
-    <row r="430" spans="1:5">
+      <c r="F429" s="5">
+        <v>323.57</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
       <c r="A430" s="2" t="s">
         <v>611</v>
       </c>
@@ -9929,8 +11216,11 @@
       <c r="E430" s="5">
         <v>401.14</v>
       </c>
-    </row>
-    <row r="431" spans="1:5">
+      <c r="F430" s="5">
+        <v>401.14</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
       <c r="A431" s="2" t="s">
         <v>611</v>
       </c>
@@ -9946,8 +11236,11 @@
       <c r="E431" s="6">
         <v>1047.43</v>
       </c>
-    </row>
-    <row r="432" spans="1:5">
+      <c r="F431" s="6">
+        <v>1047.43</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
       <c r="A432" s="2" t="s">
         <v>611</v>
       </c>
@@ -9963,8 +11256,11 @@
       <c r="E432" s="5">
         <v>759.09</v>
       </c>
-    </row>
-    <row r="433" spans="1:5">
+      <c r="F432" s="5">
+        <v>759.09</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
       <c r="A433" s="2" t="s">
         <v>611</v>
       </c>
@@ -9980,8 +11276,11 @@
       <c r="E433" s="6">
         <v>2374.58</v>
       </c>
-    </row>
-    <row r="434" spans="1:5">
+      <c r="F433" s="6">
+        <v>2374.58</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
       <c r="A434" s="2" t="s">
         <v>611</v>
       </c>
@@ -9997,8 +11296,11 @@
       <c r="E434" s="5">
         <v>337.92</v>
       </c>
-    </row>
-    <row r="435" spans="1:5">
+      <c r="F434" s="5">
+        <v>337.92</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
       <c r="A435" s="2" t="s">
         <v>621</v>
       </c>
@@ -10014,8 +11316,11 @@
       <c r="E435" s="6">
         <v>3077.12</v>
       </c>
-    </row>
-    <row r="436" spans="1:5">
+      <c r="F435" s="6">
+        <v>3077.12</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
       <c r="A436" s="2" t="s">
         <v>621</v>
       </c>
@@ -10031,8 +11336,11 @@
       <c r="E436" s="6">
         <v>2526.5300000000002</v>
       </c>
-    </row>
-    <row r="437" spans="1:5">
+      <c r="F436" s="6">
+        <v>2526.5300000000002</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
       <c r="A437" s="2" t="s">
         <v>621</v>
       </c>
@@ -10048,8 +11356,11 @@
       <c r="E437" s="6">
         <v>1992.95</v>
       </c>
-    </row>
-    <row r="438" spans="1:5">
+      <c r="F437" s="6">
+        <v>1992.95</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
       <c r="A438" s="2" t="s">
         <v>621</v>
       </c>
@@ -10065,8 +11376,11 @@
       <c r="E438" s="6">
         <v>1550.83</v>
       </c>
-    </row>
-    <row r="439" spans="1:5">
+      <c r="F438" s="6">
+        <v>1550.83</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
       <c r="A439" s="2" t="s">
         <v>621</v>
       </c>
@@ -10082,8 +11396,11 @@
       <c r="E439" s="5">
         <v>188.76</v>
       </c>
-    </row>
-    <row r="440" spans="1:5">
+      <c r="F439" s="5">
+        <v>188.76</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
       <c r="A440" s="2" t="s">
         <v>621</v>
       </c>
@@ -10099,8 +11416,11 @@
       <c r="E440" s="5">
         <v>532.1</v>
       </c>
-    </row>
-    <row r="441" spans="1:5">
+      <c r="F440" s="5">
+        <v>532.1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
       <c r="A441" s="2" t="s">
         <v>621</v>
       </c>
@@ -10116,8 +11436,11 @@
       <c r="E441" s="6">
         <v>2047.91</v>
       </c>
-    </row>
-    <row r="442" spans="1:5">
+      <c r="F441" s="6">
+        <v>2047.91</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
       <c r="A442" s="2" t="s">
         <v>621</v>
       </c>
@@ -10133,8 +11456,11 @@
       <c r="E442" s="6">
         <v>1436.76</v>
       </c>
-    </row>
-    <row r="443" spans="1:5">
+      <c r="F442" s="6">
+        <v>1436.76</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6">
       <c r="A443" s="2" t="s">
         <v>621</v>
       </c>
@@ -10150,8 +11476,11 @@
       <c r="E443" s="6">
         <v>2452.62</v>
       </c>
-    </row>
-    <row r="444" spans="1:5">
+      <c r="F443" s="6">
+        <v>2452.62</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
       <c r="A444" s="2" t="s">
         <v>630</v>
       </c>
@@ -10167,8 +11496,11 @@
       <c r="E444" s="5">
         <v>10.98</v>
       </c>
-    </row>
-    <row r="445" spans="1:5">
+      <c r="F444" s="5">
+        <v>10.98</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
       <c r="A445" s="2" t="s">
         <v>632</v>
       </c>
@@ -10184,8 +11516,11 @@
       <c r="E445" s="5">
         <v>178.53</v>
       </c>
-    </row>
-    <row r="446" spans="1:5">
+      <c r="F445" s="5">
+        <v>178.53</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
       <c r="A446" s="2" t="s">
         <v>632</v>
       </c>
@@ -10201,8 +11536,11 @@
       <c r="E446" s="5">
         <v>963.9</v>
       </c>
-    </row>
-    <row r="447" spans="1:5">
+      <c r="F446" s="5">
+        <v>963.9</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
       <c r="A447" s="2" t="s">
         <v>635</v>
       </c>
@@ -10218,8 +11556,11 @@
       <c r="E447" s="6">
         <v>1732.17</v>
       </c>
-    </row>
-    <row r="448" spans="1:5">
+      <c r="F447" s="6">
+        <v>1732.17</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
       <c r="A448" s="2" t="s">
         <v>635</v>
       </c>
@@ -10235,8 +11576,11 @@
       <c r="E448" s="5">
         <v>956.4</v>
       </c>
-    </row>
-    <row r="449" spans="1:5">
+      <c r="F448" s="5">
+        <v>956.4</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
       <c r="A449" s="2" t="s">
         <v>640</v>
       </c>
@@ -10252,8 +11596,11 @@
       <c r="E449" s="5">
         <v>680.06</v>
       </c>
-    </row>
-    <row r="450" spans="1:5">
+      <c r="F449" s="5">
+        <v>680.06</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
       <c r="A450" s="2" t="s">
         <v>642</v>
       </c>
@@ -10269,8 +11616,11 @@
       <c r="E450" s="6">
         <v>1128.3</v>
       </c>
-    </row>
-    <row r="451" spans="1:5">
+      <c r="F450" s="6">
+        <v>1128.3</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
       <c r="A451" s="2" t="s">
         <v>645</v>
       </c>
@@ -10286,8 +11636,11 @@
       <c r="E451" s="5">
         <v>262.77999999999997</v>
       </c>
-    </row>
-    <row r="452" spans="1:5">
+      <c r="F451" s="5">
+        <v>262.77999999999997</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
       <c r="A452" s="2" t="s">
         <v>279</v>
       </c>
@@ -10303,8 +11656,11 @@
       <c r="E452" s="6">
         <v>2644.48</v>
       </c>
-    </row>
-    <row r="453" spans="1:5">
+      <c r="F452" s="6">
+        <v>2644.48</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
       <c r="A453" s="2" t="s">
         <v>650</v>
       </c>
@@ -10320,8 +11676,11 @@
       <c r="E453" s="5">
         <v>259.06</v>
       </c>
-    </row>
-    <row r="454" spans="1:5">
+      <c r="F453" s="5">
+        <v>259.06</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
       <c r="A454" s="2" t="s">
         <v>37</v>
       </c>
@@ -10337,8 +11696,11 @@
       <c r="E454" s="5">
         <v>317.23</v>
       </c>
-    </row>
-    <row r="455" spans="1:5">
+      <c r="F454" s="5">
+        <v>317.23</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
       <c r="A455" s="2" t="s">
         <v>651</v>
       </c>
@@ -10354,8 +11716,11 @@
       <c r="E455" s="6">
         <v>2486.83</v>
       </c>
-    </row>
-    <row r="456" spans="1:5">
+      <c r="F455" s="6">
+        <v>2486.83</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
       <c r="A456" s="2" t="s">
         <v>651</v>
       </c>
@@ -10371,8 +11736,11 @@
       <c r="E456" s="6">
         <v>4991.01</v>
       </c>
-    </row>
-    <row r="457" spans="1:5">
+      <c r="F456" s="6">
+        <v>4991.01</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
       <c r="A457" s="2" t="s">
         <v>138</v>
       </c>
@@ -10388,8 +11756,11 @@
       <c r="E457" s="6">
         <v>6232.46</v>
       </c>
-    </row>
-    <row r="458" spans="1:5">
+      <c r="F457" s="6">
+        <v>6232.46</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
       <c r="A458" s="2" t="s">
         <v>138</v>
       </c>
@@ -10405,8 +11776,11 @@
       <c r="E458" s="6">
         <v>9370.36</v>
       </c>
-    </row>
-    <row r="459" spans="1:5">
+      <c r="F458" s="6">
+        <v>9370.36</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
       <c r="A459" s="2" t="s">
         <v>279</v>
       </c>
@@ -10422,8 +11796,11 @@
       <c r="E459" s="6">
         <v>2931.2</v>
       </c>
-    </row>
-    <row r="460" spans="1:5">
+      <c r="F459" s="6">
+        <v>2931.2</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
       <c r="A460" s="2" t="s">
         <v>279</v>
       </c>
@@ -10439,8 +11816,11 @@
       <c r="E460" s="6">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="461" spans="1:5">
+      <c r="F460" s="6">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
       <c r="A461" s="2" t="s">
         <v>279</v>
       </c>
@@ -10456,8 +11836,11 @@
       <c r="E461" s="6">
         <v>3087.07</v>
       </c>
-    </row>
-    <row r="462" spans="1:5">
+      <c r="F461" s="6">
+        <v>3087.07</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
       <c r="A462" s="2" t="s">
         <v>279</v>
       </c>
@@ -10473,8 +11856,11 @@
       <c r="E462" s="6">
         <v>2201.4</v>
       </c>
-    </row>
-    <row r="463" spans="1:5">
+      <c r="F462" s="6">
+        <v>2201.4</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
       <c r="A463" s="2" t="s">
         <v>279</v>
       </c>
@@ -10490,8 +11876,11 @@
       <c r="E463" s="6">
         <v>2741.2</v>
       </c>
-    </row>
-    <row r="464" spans="1:5">
+      <c r="F463" s="6">
+        <v>2741.2</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
       <c r="A464" s="2" t="s">
         <v>287</v>
       </c>
@@ -10505,6 +11894,9 @@
         <v>1469.88</v>
       </c>
       <c r="E464" s="6">
+        <v>1469.88</v>
+      </c>
+      <c r="F464" s="6">
         <v>1469.88</v>
       </c>
     </row>

--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -928,9 +928,6 @@
     <t>YAX AUTO S.R.L. ALBA IULIA</t>
   </si>
   <si>
-    <t>Factura</t>
-  </si>
-  <si>
     <t>03.09.26</t>
   </si>
   <si>
@@ -2018,6 +2015,9 @@
   </si>
   <si>
     <t>09.01.26</t>
+  </si>
+  <si>
+    <t>numar Factura</t>
   </si>
 </sst>
 </file>
@@ -2625,13 +2625,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>304</v>
+        <v>667</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -2768,7 +2768,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D8" s="6">
         <v>1825.31</v>
@@ -2788,7 +2788,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" s="5">
         <v>761.15</v>
@@ -2848,7 +2848,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D12" s="6">
         <v>1990.1</v>
@@ -2928,7 +2928,7 @@
         <v>25</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D16" s="6">
         <v>1938.46</v>
@@ -3068,7 +3068,7 @@
         <v>36</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D23" s="5">
         <v>149.44</v>
@@ -3108,7 +3108,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D25" s="5">
         <v>188.7</v>
@@ -3168,7 +3168,7 @@
         <v>44</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D28" s="5">
         <v>109.38</v>
@@ -3188,7 +3188,7 @@
         <v>45</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D29" s="6">
         <v>1961.14</v>
@@ -3208,7 +3208,7 @@
         <v>46</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D30" s="6">
         <v>1140.42</v>
@@ -3228,7 +3228,7 @@
         <v>47</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D31" s="5">
         <v>607.47</v>
@@ -3308,7 +3308,7 @@
         <v>54</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D35" s="6">
         <v>1001.25</v>
@@ -3328,7 +3328,7 @@
         <v>55</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D36" s="6">
         <v>1001.25</v>
@@ -3388,7 +3388,7 @@
         <v>58</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D39" s="5">
         <v>631.30999999999995</v>
@@ -3468,7 +3468,7 @@
         <v>62</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D43" s="6">
         <v>1237.92</v>
@@ -3508,7 +3508,7 @@
         <v>67</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D45" s="6">
         <v>1127.1600000000001</v>
@@ -3528,7 +3528,7 @@
         <v>68</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D46" s="5">
         <v>455.71</v>
@@ -3568,7 +3568,7 @@
         <v>71</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D48" s="5">
         <v>774.25</v>
@@ -3648,7 +3648,7 @@
         <v>75</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D52" s="5">
         <v>768.39</v>
@@ -3668,7 +3668,7 @@
         <v>76</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D53" s="6">
         <v>1084.49</v>
@@ -3728,7 +3728,7 @@
         <v>80</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D56" s="5">
         <v>303.18</v>
@@ -3808,7 +3808,7 @@
         <v>87</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D60" s="5">
         <v>437.08</v>
@@ -3948,7 +3948,7 @@
         <v>97</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D67" s="6">
         <v>1045.26</v>
@@ -4008,7 +4008,7 @@
         <v>103</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D70" s="5">
         <v>334.17</v>
@@ -4028,7 +4028,7 @@
         <v>104</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D71" s="5">
         <v>239.26</v>
@@ -4048,7 +4048,7 @@
         <v>105</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D72" s="5">
         <v>490.77</v>
@@ -4088,7 +4088,7 @@
         <v>108</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D74" s="5">
         <v>541.19000000000005</v>
@@ -4208,7 +4208,7 @@
         <v>120</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D80" s="5">
         <v>842.01</v>
@@ -4328,7 +4328,7 @@
         <v>131</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D86" s="5">
         <v>377.52</v>
@@ -4348,7 +4348,7 @@
         <v>132</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D87" s="6">
         <v>4684.08</v>
@@ -4408,7 +4408,7 @@
         <v>135</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D90" s="5">
         <v>418.2</v>
@@ -4628,7 +4628,7 @@
         <v>154</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D101" s="5">
         <v>551.74</v>
@@ -4688,7 +4688,7 @@
         <v>159</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D104" s="6">
         <v>-10410.31</v>
@@ -4728,7 +4728,7 @@
         <v>163</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D106" s="5">
         <v>684.26</v>
@@ -4788,7 +4788,7 @@
         <v>166</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D109" s="5">
         <v>755.04</v>
@@ -4888,7 +4888,7 @@
         <v>172</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D114" s="6">
         <v>8148.44</v>
@@ -4988,7 +4988,7 @@
         <v>179</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D119" s="5">
         <v>219.43</v>
@@ -5048,7 +5048,7 @@
         <v>182</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D122" s="5">
         <v>711.77</v>
@@ -5208,7 +5208,7 @@
         <v>194</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D130" s="5">
         <v>537.76</v>
@@ -5268,7 +5268,7 @@
         <v>197</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D133" s="5">
         <v>659.82</v>
@@ -5288,7 +5288,7 @@
         <v>199</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D134" s="5">
         <v>341.65</v>
@@ -5348,7 +5348,7 @@
         <v>204</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D137" s="5">
         <v>961.96</v>
@@ -5408,7 +5408,7 @@
         <v>210</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D140" s="5">
         <v>308.08999999999997</v>
@@ -5428,7 +5428,7 @@
         <v>211</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D141" s="6">
         <v>1391.53</v>
@@ -5548,7 +5548,7 @@
         <v>216</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D147" s="5">
         <v>483.88</v>
@@ -5668,7 +5668,7 @@
         <v>223</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D153" s="5">
         <v>576.96</v>
@@ -5708,7 +5708,7 @@
         <v>225</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D155" s="5">
         <v>706.04</v>
@@ -5788,7 +5788,7 @@
         <v>231</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D159" s="5">
         <v>251.63</v>
@@ -5908,7 +5908,7 @@
         <v>239</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D165" s="5">
         <v>163.47</v>
@@ -6048,7 +6048,7 @@
         <v>247</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D172" s="5">
         <v>603.80999999999995</v>
@@ -6068,7 +6068,7 @@
         <v>248</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D173" s="5">
         <v>401.14</v>
@@ -6088,7 +6088,7 @@
         <v>249</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D174" s="5">
         <v>429.91</v>
@@ -6128,7 +6128,7 @@
         <v>254</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D176" s="6">
         <v>10726.46</v>
@@ -6148,7 +6148,7 @@
         <v>255</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D177" s="6">
         <v>2086.77</v>
@@ -6168,7 +6168,7 @@
         <v>256</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D178" s="6">
         <v>1100.7</v>
@@ -6228,7 +6228,7 @@
         <v>259</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D181" s="5">
         <v>295.83</v>
@@ -6248,7 +6248,7 @@
         <v>261</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D182" s="5">
         <v>311.14999999999998</v>
@@ -6348,7 +6348,7 @@
         <v>268</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D187" s="5">
         <v>398.26</v>
@@ -6388,7 +6388,7 @@
         <v>270</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D189" s="5">
         <v>270.98</v>
@@ -6408,7 +6408,7 @@
         <v>271</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D190" s="5">
         <v>430.93</v>
@@ -6468,7 +6468,7 @@
         <v>275</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D193" s="5">
         <v>467.44</v>
@@ -6488,7 +6488,7 @@
         <v>276</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D194" s="5">
         <v>271.20999999999998</v>
@@ -6528,7 +6528,7 @@
         <v>278</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D196" s="5">
         <v>350.72</v>
@@ -6688,7 +6688,7 @@
         <v>288</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D204" s="6">
         <v>10514.78</v>
@@ -6708,7 +6708,7 @@
         <v>289</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D205" s="6">
         <v>1142.45</v>
@@ -6748,7 +6748,7 @@
         <v>292</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D207" s="5">
         <v>376.95</v>
@@ -6848,7 +6848,7 @@
         <v>295</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D212" s="6">
         <v>4165.26</v>
@@ -6908,7 +6908,7 @@
         <v>298</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D215" s="5">
         <v>288.73</v>
@@ -7008,7 +7008,7 @@
         <v>302</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D220" s="5">
         <v>672.42</v>
@@ -7042,13 +7042,13 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B222" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="C222" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>333</v>
       </c>
       <c r="D222" s="6">
         <v>1395.04</v>
@@ -7062,10 +7062,10 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>267</v>
@@ -7082,10 +7082,10 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>189</v>
@@ -7102,13 +7102,13 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B225" s="7">
         <v>9621</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D225" s="6">
         <v>6601.54</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B226" s="3" t="s">
         <v>338</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>114</v>
@@ -7142,13 +7142,13 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B227" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C227" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="D227" s="5">
         <v>222.65</v>
@@ -7162,13 +7162,13 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B228" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C228" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="D228" s="5">
         <v>351.09</v>
@@ -7182,13 +7182,13 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="C229" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="D229" s="6">
         <v>2219.77</v>
@@ -7202,10 +7202,10 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>186</v>
@@ -7222,10 +7222,10 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>186</v>
@@ -7242,13 +7242,13 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B232" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C232" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="D232" s="5">
         <v>353.93</v>
@@ -7262,13 +7262,13 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D233" s="5">
         <v>750.28</v>
@@ -7282,13 +7282,13 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D234" s="5">
         <v>210.36</v>
@@ -7302,10 +7302,10 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>84</v>
@@ -7322,7 +7322,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B236" s="7">
         <v>9602</v>
@@ -7342,10 +7342,10 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B237" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>11</v>
@@ -7362,13 +7362,13 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D238" s="5">
         <v>506.72</v>
@@ -7382,13 +7382,13 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B239" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="C239" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="D239" s="6">
         <v>1017.46</v>
@@ -7402,13 +7402,13 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B240" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C240" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="C240" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="D240" s="5">
         <v>152.68</v>
@@ -7422,13 +7422,13 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B241" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C241" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>363</v>
       </c>
       <c r="D241" s="5">
         <v>163.05000000000001</v>
@@ -7442,13 +7442,13 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B242" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C242" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>365</v>
       </c>
       <c r="D242" s="5">
         <v>220.74</v>
@@ -7462,13 +7462,13 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B243" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C243" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="D243" s="5">
         <v>304.68</v>
@@ -7482,13 +7482,13 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B244" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C244" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="D244" s="5">
         <v>216.59</v>
@@ -7502,10 +7502,10 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B245" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>186</v>
@@ -7522,13 +7522,13 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B246" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B246" s="3" t="s">
+      <c r="C246" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="D246" s="6">
         <v>2924.9</v>
@@ -7542,10 +7542,10 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>84</v>
@@ -7562,13 +7562,13 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B248" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C248" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="D248" s="6">
         <v>1786.76</v>
@@ -7582,13 +7582,13 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B249" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B249" s="3" t="s">
+      <c r="C249" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="C249" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="D249" s="6">
         <v>7246.34</v>
@@ -7602,10 +7602,10 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>186</v>
@@ -7622,13 +7622,13 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D251" s="6">
         <v>1578.01</v>
@@ -7642,13 +7642,13 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C252" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="D252" s="5">
         <v>361.77</v>
@@ -7662,13 +7662,13 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D253" s="6">
         <v>1156.58</v>
@@ -7682,13 +7682,13 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D254" s="5">
         <v>786.5</v>
@@ -7702,13 +7702,13 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B255" s="7">
         <v>9618</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D255" s="6">
         <v>1479.19</v>
@@ -7722,13 +7722,13 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B256" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B256" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="C256" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D256" s="5">
         <v>523.71</v>
@@ -7742,10 +7742,10 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>118</v>
@@ -7762,13 +7762,13 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D258" s="5">
         <v>634.45000000000005</v>
@@ -7782,13 +7782,13 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D259" s="6">
         <v>1258.33</v>
@@ -7802,13 +7802,13 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D260" s="5">
         <v>703.97</v>
@@ -7822,13 +7822,13 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D261" s="5">
         <v>522.53</v>
@@ -7842,13 +7842,13 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D262" s="5">
         <v>268.63</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>130</v>
@@ -7882,13 +7882,13 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D264" s="5">
         <v>598.75</v>
@@ -7902,13 +7902,13 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B265" s="7">
         <v>9619</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D265" s="5">
         <v>609.71</v>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B266" s="7">
         <v>9656</v>
@@ -7942,10 +7942,10 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B267" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>398</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>15</v>
@@ -7962,13 +7962,13 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B268" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C268" s="4" t="s">
         <v>399</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>400</v>
       </c>
       <c r="D268" s="5">
         <v>491.69</v>
@@ -7982,13 +7982,13 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B269" s="7">
         <v>9639</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D269" s="5">
         <v>188.76</v>
@@ -8002,13 +8002,13 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B270" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B270" s="3" t="s">
+      <c r="C270" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>404</v>
       </c>
       <c r="D270" s="6">
         <v>1603.85</v>
@@ -8022,10 +8022,10 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>186</v>
@@ -8042,10 +8042,10 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>53</v>
@@ -8062,13 +8062,13 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D273" s="5">
         <v>188.76</v>
@@ -8082,13 +8082,13 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B274" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B274" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="C274" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D274" s="6">
         <v>1468.04</v>
@@ -8102,13 +8102,13 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D275" s="6">
         <v>3705.98</v>
@@ -8122,13 +8122,13 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D276" s="5">
         <v>261.86</v>
@@ -8142,10 +8142,10 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>192</v>
@@ -8162,13 +8162,13 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B278" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C278" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>414</v>
       </c>
       <c r="D278" s="5">
         <v>731.45</v>
@@ -8182,13 +8182,13 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D279" s="6">
         <v>1310.6199999999999</v>
@@ -8202,10 +8202,10 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>189</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>189</v>
@@ -8242,10 +8242,10 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>82</v>
@@ -8262,10 +8262,10 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>84</v>
@@ -8282,10 +8282,10 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>30</v>
@@ -8302,13 +8302,13 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D285" s="6">
         <v>3358.91</v>
@@ -8322,13 +8322,13 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D286" s="5">
         <v>860.86</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B287" s="7">
         <v>9600</v>
@@ -8362,13 +8362,13 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B288" s="7">
         <v>9614</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D288" s="5">
         <v>268.77999999999997</v>
@@ -8382,13 +8382,13 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B289" s="7">
         <v>9636</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D289" s="5">
         <v>259.04000000000002</v>
@@ -8405,10 +8405,10 @@
         <v>116</v>
       </c>
       <c r="B290" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C290" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>424</v>
       </c>
       <c r="D290" s="5">
         <v>797.4</v>
@@ -8425,7 +8425,7 @@
         <v>116</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>267</v>
@@ -8445,10 +8445,10 @@
         <v>116</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D292" s="5">
         <v>530.57000000000005</v>
@@ -8465,10 +8465,10 @@
         <v>116</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D293" s="6">
         <v>1109.42</v>
@@ -8485,10 +8485,10 @@
         <v>116</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D294" s="5">
         <v>257.98</v>
@@ -8505,10 +8505,10 @@
         <v>116</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D295" s="5">
         <v>246.58</v>
@@ -8528,7 +8528,7 @@
         <v>9617</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D296" s="5">
         <v>553.42999999999995</v>
@@ -8562,13 +8562,13 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B298" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B298" s="3" t="s">
+      <c r="C298" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C298" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="D298" s="6">
         <v>2644.4</v>
@@ -8582,13 +8582,13 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B299" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C299" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="C299" s="3" t="s">
-        <v>434</v>
       </c>
       <c r="D299" s="5">
         <v>403.75</v>
@@ -8602,13 +8602,13 @@
     </row>
     <row r="300" spans="1:6">
       <c r="A300" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B300" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C300" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="D300" s="5">
         <v>326.95</v>
@@ -8622,13 +8622,13 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D301" s="5">
         <v>708.92</v>
@@ -8642,13 +8642,13 @@
     </row>
     <row r="302" spans="1:6">
       <c r="A302" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D302" s="5">
         <v>170.36</v>
@@ -8662,13 +8662,13 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D303" s="5">
         <v>417.37</v>
@@ -8682,13 +8682,13 @@
     </row>
     <row r="304" spans="1:6">
       <c r="A304" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D304" s="5">
         <v>543.71</v>
@@ -8702,7 +8702,7 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B305" s="7">
         <v>9654</v>
@@ -8722,13 +8722,13 @@
     </row>
     <row r="306" spans="1:6">
       <c r="A306" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B306" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B306" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="C306" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D306" s="6">
         <v>1448.37</v>
@@ -8742,13 +8742,13 @@
     </row>
     <row r="307" spans="1:6">
       <c r="A307" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D307" s="6">
         <v>1380.29</v>
@@ -8762,13 +8762,13 @@
     </row>
     <row r="308" spans="1:6">
       <c r="A308" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B308" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B308" s="3" t="s">
+      <c r="C308" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="C308" s="4" t="s">
-        <v>446</v>
       </c>
       <c r="D308" s="6">
         <v>4795.4399999999996</v>
@@ -8782,13 +8782,13 @@
     </row>
     <row r="309" spans="1:6">
       <c r="A309" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D309" s="6">
         <v>1575.72</v>
@@ -8802,13 +8802,13 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B310" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C310" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="C310" s="4" t="s">
-        <v>449</v>
       </c>
       <c r="D310" s="5">
         <v>63.48</v>
@@ -8822,13 +8822,13 @@
     </row>
     <row r="311" spans="1:6">
       <c r="A311" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B311" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C311" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="D311" s="5">
         <v>93.8</v>
@@ -8842,13 +8842,13 @@
     </row>
     <row r="312" spans="1:6">
       <c r="A312" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D312" s="5">
         <v>852.76</v>
@@ -8862,13 +8862,13 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B313" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C313" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="C313" s="3" t="s">
-        <v>454</v>
       </c>
       <c r="D313" s="5">
         <v>119.58</v>
@@ -8882,13 +8882,13 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B314" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C314" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="C314" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="D314" s="5">
         <v>467.32</v>
@@ -8902,13 +8902,13 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B315" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B315" s="3" t="s">
-        <v>458</v>
-      </c>
       <c r="C315" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D315" s="5">
         <v>981.7</v>
@@ -8922,13 +8922,13 @@
     </row>
     <row r="316" spans="1:6">
       <c r="A316" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D316" s="5">
         <v>778.34</v>
@@ -8942,10 +8942,10 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>114</v>
@@ -8962,13 +8962,13 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D318" s="6">
         <v>1352.99</v>
@@ -8982,13 +8982,13 @@
     </row>
     <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D319" s="5">
         <v>164.08</v>
@@ -9002,13 +9002,13 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D320" s="5">
         <v>374.52</v>
@@ -9022,13 +9022,13 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D321" s="6">
         <v>1873.63</v>
@@ -9042,10 +9042,10 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>267</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>118</v>
@@ -9082,13 +9082,13 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D324" s="5">
         <v>910.84</v>
@@ -9102,13 +9102,13 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D325" s="6">
         <v>1313.79</v>
@@ -9122,13 +9122,13 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D326" s="5">
         <v>374.52</v>
@@ -9142,13 +9142,13 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D327" s="5">
         <v>633.09</v>
@@ -9162,10 +9162,10 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>130</v>
@@ -9182,13 +9182,13 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D329" s="6">
         <v>1202.8499999999999</v>
@@ -9202,13 +9202,13 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D330" s="5">
         <v>651.34</v>
@@ -9222,13 +9222,13 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B331" s="7">
         <v>9615</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D331" s="6">
         <v>2250.61</v>
@@ -9242,7 +9242,7 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B332" s="7">
         <v>9657</v>
@@ -9262,13 +9262,13 @@
     </row>
     <row r="333" spans="1:6">
       <c r="A333" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B333" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B333" s="3" t="s">
+      <c r="C333" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="C333" s="4" t="s">
-        <v>476</v>
       </c>
       <c r="D333" s="6">
         <v>1045.79</v>
@@ -9282,13 +9282,13 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B334" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C334" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="C334" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="D334" s="6">
         <v>1170.74</v>
@@ -9302,13 +9302,13 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B335" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C335" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="C335" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="D335" s="6">
         <v>1356.94</v>
@@ -9322,13 +9322,13 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D336" s="6">
         <v>1873.85</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>186</v>
@@ -9362,13 +9362,13 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D338" s="6">
         <v>1565.58</v>
@@ -9382,13 +9382,13 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B339" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B339" s="3" t="s">
-        <v>485</v>
-      </c>
       <c r="C339" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D339" s="5">
         <v>502.35</v>
@@ -9402,13 +9402,13 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D340" s="5">
         <v>117.98</v>
@@ -9422,13 +9422,13 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B341" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B341" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="C341" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D341" s="5">
         <v>360.44</v>
@@ -9442,13 +9442,13 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D342" s="5">
         <v>315.98</v>
@@ -9462,7 +9462,7 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B343" s="7">
         <v>9601</v>
@@ -9482,13 +9482,13 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B344" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B344" s="3" t="s">
+      <c r="C344" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="C344" s="4" t="s">
-        <v>492</v>
       </c>
       <c r="D344" s="6">
         <v>1854.68</v>
@@ -9502,13 +9502,13 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B345" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B345" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="C345" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D345" s="5">
         <v>631.80999999999995</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>30</v>
@@ -9542,10 +9542,10 @@
     </row>
     <row r="347" spans="1:6">
       <c r="A347" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B347" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="B347" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>118</v>
@@ -9562,13 +9562,13 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B348" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B348" s="3" t="s">
-        <v>499</v>
-      </c>
       <c r="C348" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D348" s="5">
         <v>261.86</v>
@@ -9582,10 +9582,10 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B349" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="B349" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>130</v>
@@ -9602,13 +9602,13 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D350" s="5">
         <v>790.54</v>
@@ -9622,13 +9622,13 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D351" s="5">
         <v>920.54</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B352" s="7">
         <v>9607</v>
@@ -9662,13 +9662,13 @@
     </row>
     <row r="353" spans="1:6">
       <c r="A353" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B353" s="7">
         <v>9616</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D353" s="5">
         <v>348.09</v>
@@ -9682,10 +9682,10 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B354" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="B354" s="3" t="s">
-        <v>505</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>189</v>
@@ -9702,10 +9702,10 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>189</v>
@@ -9722,13 +9722,13 @@
     </row>
     <row r="356" spans="1:6">
       <c r="A356" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B356" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B356" s="3" t="s">
-        <v>508</v>
-      </c>
       <c r="C356" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D356" s="6">
         <v>6600.83</v>
@@ -9742,13 +9742,13 @@
     </row>
     <row r="357" spans="1:6">
       <c r="A357" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D357" s="5">
         <v>377.52</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="358" spans="1:6">
       <c r="A358" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>267</v>
@@ -9782,13 +9782,13 @@
     </row>
     <row r="359" spans="1:6">
       <c r="A359" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D359" s="6">
         <v>6789.59</v>
@@ -9802,7 +9802,7 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B360" s="7">
         <v>9597</v>
@@ -9825,7 +9825,7 @@
         <v>220</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>114</v>
@@ -9845,10 +9845,10 @@
         <v>220</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D362" s="5">
         <v>685.68</v>
@@ -9865,10 +9865,10 @@
         <v>220</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D363" s="6">
         <v>2524.5100000000002</v>
@@ -9882,13 +9882,13 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B364" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B364" s="3" t="s">
-        <v>516</v>
-      </c>
       <c r="C364" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D364" s="5">
         <v>631.74</v>
@@ -9902,13 +9902,13 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D365" s="5">
         <v>692.41</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B366" s="7">
         <v>9606</v>
@@ -9942,13 +9942,13 @@
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B367" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B367" s="3" t="s">
-        <v>519</v>
-      </c>
       <c r="C367" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D367" s="6">
         <v>1062.22</v>
@@ -9962,10 +9962,10 @@
     </row>
     <row r="368" spans="1:6">
       <c r="A368" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>84</v>
@@ -9982,13 +9982,13 @@
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B369" s="7">
         <v>9640</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D369" s="6">
         <v>2527.83</v>
@@ -10002,13 +10002,13 @@
     </row>
     <row r="370" spans="1:6">
       <c r="A370" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B370" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B370" s="3" t="s">
+      <c r="C370" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="C370" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="D370" s="6">
         <v>4118.0200000000004</v>
@@ -10022,13 +10022,13 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D371" s="6">
         <v>1893.12</v>
@@ -10042,10 +10042,10 @@
     </row>
     <row r="372" spans="1:6">
       <c r="A372" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>7</v>
@@ -10062,10 +10062,10 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>118</v>
@@ -10082,10 +10082,10 @@
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>118</v>
@@ -10102,13 +10102,13 @@
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D375" s="5">
         <v>109.38</v>
@@ -10122,13 +10122,13 @@
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D376" s="5">
         <v>981.71</v>
@@ -10142,13 +10142,13 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B377" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B377" s="3" t="s">
+      <c r="C377" s="4" t="s">
         <v>531</v>
-      </c>
-      <c r="C377" s="4" t="s">
-        <v>532</v>
       </c>
       <c r="D377" s="6">
         <v>36000</v>
@@ -10162,13 +10162,13 @@
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B378" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C378" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="C378" s="3" t="s">
-        <v>534</v>
       </c>
       <c r="D378" s="6">
         <v>1072.2</v>
@@ -10182,13 +10182,13 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D379" s="5">
         <v>416.84</v>
@@ -10202,13 +10202,13 @@
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B380" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C380" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="C380" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="D380" s="5">
         <v>729.12</v>
@@ -10222,13 +10222,13 @@
     </row>
     <row r="381" spans="1:6">
       <c r="A381" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D381" s="5">
         <v>356.73</v>
@@ -10242,13 +10242,13 @@
     </row>
     <row r="382" spans="1:6">
       <c r="A382" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B382" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C382" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C382" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="D382" s="5">
         <v>651.4</v>
@@ -10262,13 +10262,13 @@
     </row>
     <row r="383" spans="1:6">
       <c r="A383" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D383" s="5">
         <v>764.3</v>
@@ -10282,13 +10282,13 @@
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B384" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="C384" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C384" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="D384" s="5">
         <v>729.12</v>
@@ -10302,13 +10302,13 @@
     </row>
     <row r="385" spans="1:6">
       <c r="A385" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D385" s="5">
         <v>216.35</v>
@@ -10322,13 +10322,13 @@
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B386" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C386" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="C386" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="D386" s="5">
         <v>597.20000000000005</v>
@@ -10342,13 +10342,13 @@
     </row>
     <row r="387" spans="1:6">
       <c r="A387" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B387" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C387" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="C387" s="3" t="s">
-        <v>548</v>
       </c>
       <c r="D387" s="6">
         <v>5600.79</v>
@@ -10362,13 +10362,13 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B388" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C388" s="4" t="s">
         <v>549</v>
-      </c>
-      <c r="C388" s="4" t="s">
-        <v>550</v>
       </c>
       <c r="D388" s="5">
         <v>652.29999999999995</v>
@@ -10382,13 +10382,13 @@
     </row>
     <row r="389" spans="1:6">
       <c r="A389" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B389" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="C389" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="C389" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="D389" s="6">
         <v>2042.43</v>
@@ -10402,13 +10402,13 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B390" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C390" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="C390" s="4" t="s">
-        <v>554</v>
       </c>
       <c r="D390" s="5">
         <v>870.5</v>
@@ -10422,13 +10422,13 @@
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D391" s="6">
         <v>1009.8</v>
@@ -10442,13 +10442,13 @@
     </row>
     <row r="392" spans="1:6">
       <c r="A392" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B392" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C392" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="C392" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="D392" s="5">
         <v>870.5</v>
@@ -10462,13 +10462,13 @@
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B393" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C393" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="C393" s="4" t="s">
-        <v>559</v>
       </c>
       <c r="D393" s="5">
         <v>596.72</v>
@@ -10482,13 +10482,13 @@
     </row>
     <row r="394" spans="1:6">
       <c r="A394" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B394" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C394" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="C394" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="D394" s="5">
         <v>736.72</v>
@@ -10502,13 +10502,13 @@
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B395" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C395" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="C395" s="3" t="s">
-        <v>563</v>
       </c>
       <c r="D395" s="5">
         <v>716.1</v>
@@ -10522,13 +10522,13 @@
     </row>
     <row r="396" spans="1:6">
       <c r="A396" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B396" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C396" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>565</v>
       </c>
       <c r="D396" s="5">
         <v>564.66</v>
@@ -10542,13 +10542,13 @@
     </row>
     <row r="397" spans="1:6">
       <c r="A397" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B397" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C397" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="D397" s="5">
         <v>898.02</v>
@@ -10562,13 +10562,13 @@
     </row>
     <row r="398" spans="1:6">
       <c r="A398" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B398" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C398" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="C398" s="3" t="s">
-        <v>569</v>
       </c>
       <c r="D398" s="5">
         <v>898.02</v>
@@ -10582,13 +10582,13 @@
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B399" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C399" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="C399" s="3" t="s">
-        <v>571</v>
       </c>
       <c r="D399" s="5">
         <v>651.29999999999995</v>
@@ -10602,10 +10602,10 @@
     </row>
     <row r="400" spans="1:6">
       <c r="A400" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>7</v>
@@ -10622,13 +10622,13 @@
     </row>
     <row r="401" spans="1:6">
       <c r="A401" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B401" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B401" s="3" t="s">
-        <v>574</v>
-      </c>
       <c r="C401" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D401" s="5">
         <v>235.95</v>
@@ -10642,13 +10642,13 @@
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B402" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B402" s="3" t="s">
+      <c r="C402" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="C402" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="D402" s="6">
         <v>9512.7099999999991</v>
@@ -10662,13 +10662,13 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B403" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C403" s="4" t="s">
         <v>578</v>
-      </c>
-      <c r="C403" s="4" t="s">
-        <v>579</v>
       </c>
       <c r="D403" s="6">
         <v>6835.49</v>
@@ -10682,13 +10682,13 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B404" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C404" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="C404" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="D404" s="5">
         <v>374.52</v>
@@ -10702,13 +10702,13 @@
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D405" s="6">
         <v>10694.76</v>
@@ -10722,7 +10722,7 @@
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B406" s="7">
         <v>9603</v>
@@ -10742,7 +10742,7 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B407" s="7">
         <v>9604</v>
@@ -10762,10 +10762,10 @@
     </row>
     <row r="408" spans="1:6">
       <c r="A408" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B408" s="3" t="s">
         <v>583</v>
-      </c>
-      <c r="B408" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>267</v>
@@ -10782,13 +10782,13 @@
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D409" s="5">
         <v>235.95</v>
@@ -10802,13 +10802,13 @@
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B410" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B410" s="3" t="s">
-        <v>587</v>
-      </c>
       <c r="C410" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D410" s="6">
         <v>10808.11</v>
@@ -10822,13 +10822,13 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D411" s="5">
         <v>589.9</v>
@@ -10842,10 +10842,10 @@
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>118</v>
@@ -10862,13 +10862,13 @@
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D413" s="5">
         <v>752.71</v>
@@ -10882,10 +10882,10 @@
     </row>
     <row r="414" spans="1:6">
       <c r="A414" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B414" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="B414" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>114</v>
@@ -10902,10 +10902,10 @@
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B415" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="B415" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>189</v>
@@ -10922,10 +10922,10 @@
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>84</v>
@@ -10942,10 +10942,10 @@
     </row>
     <row r="417" spans="1:6">
       <c r="A417" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>130</v>
@@ -10962,13 +10962,13 @@
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D418" s="6">
         <v>1837.63</v>
@@ -10982,13 +10982,13 @@
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D419" s="5">
         <v>270.92</v>
@@ -11002,13 +11002,13 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B420" s="7">
         <v>9638</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D420" s="6">
         <v>1830.78</v>
@@ -11022,13 +11022,13 @@
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B421" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B421" s="3" t="s">
+      <c r="C421" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="C421" s="4" t="s">
-        <v>601</v>
       </c>
       <c r="D421" s="5">
         <v>829.15</v>
@@ -11042,13 +11042,13 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B422" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C422" s="3" t="s">
         <v>602</v>
-      </c>
-      <c r="C422" s="3" t="s">
-        <v>603</v>
       </c>
       <c r="D422" s="5">
         <v>569.84</v>
@@ -11062,13 +11062,13 @@
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B423" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C423" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="C423" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="D423" s="5">
         <v>211.45</v>
@@ -11082,13 +11082,13 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B424" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C424" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="D424" s="5">
         <v>92.34</v>
@@ -11102,13 +11102,13 @@
     </row>
     <row r="425" spans="1:6">
       <c r="A425" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B425" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C425" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="C425" s="3" t="s">
-        <v>609</v>
       </c>
       <c r="D425" s="5">
         <v>318.69</v>
@@ -11122,13 +11122,13 @@
     </row>
     <row r="426" spans="1:6">
       <c r="A426" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D426" s="5">
         <v>501.26</v>
@@ -11142,13 +11142,13 @@
     </row>
     <row r="427" spans="1:6">
       <c r="A427" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B427" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B427" s="3" t="s">
+      <c r="C427" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="C427" s="4" t="s">
-        <v>613</v>
       </c>
       <c r="D427" s="5">
         <v>798.91</v>
@@ -11162,13 +11162,13 @@
     </row>
     <row r="428" spans="1:6">
       <c r="A428" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D428" s="6">
         <v>3028.65</v>
@@ -11182,10 +11182,10 @@
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C429" s="3" t="s">
         <v>114</v>
@@ -11202,13 +11202,13 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D430" s="5">
         <v>401.14</v>
@@ -11222,13 +11222,13 @@
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D431" s="6">
         <v>1047.43</v>
@@ -11242,10 +11242,10 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>79</v>
@@ -11262,13 +11262,13 @@
     </row>
     <row r="433" spans="1:6">
       <c r="A433" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D433" s="6">
         <v>2374.58</v>
@@ -11282,13 +11282,13 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D434" s="5">
         <v>337.92</v>
@@ -11302,13 +11302,13 @@
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B435" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B435" s="3" t="s">
-        <v>622</v>
-      </c>
       <c r="C435" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D435" s="6">
         <v>5995.83</v>
@@ -11322,13 +11322,13 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D436" s="6">
         <v>2526.5300000000002</v>
@@ -11342,10 +11342,10 @@
     </row>
     <row r="437" spans="1:6">
       <c r="A437" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C437" s="3" t="s">
         <v>267</v>
@@ -11362,13 +11362,13 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D438" s="6">
         <v>1550.83</v>
@@ -11382,13 +11382,13 @@
     </row>
     <row r="439" spans="1:6">
       <c r="A439" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D439" s="5">
         <v>188.76</v>
@@ -11402,10 +11402,10 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C440" s="3" t="s">
         <v>130</v>
@@ -11422,13 +11422,13 @@
     </row>
     <row r="441" spans="1:6">
       <c r="A441" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D441" s="6">
         <v>2047.91</v>
@@ -11442,13 +11442,13 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D442" s="6">
         <v>1436.76</v>
@@ -11462,13 +11462,13 @@
     </row>
     <row r="443" spans="1:6">
       <c r="A443" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B443" s="7">
         <v>9620</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D443" s="6">
         <v>2452.62</v>
@@ -11482,13 +11482,13 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B444" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="B444" s="3" t="s">
-        <v>631</v>
-      </c>
       <c r="C444" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D444" s="6">
         <v>3470.57</v>
@@ -11502,10 +11502,10 @@
     </row>
     <row r="445" spans="1:6">
       <c r="A445" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B445" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="B445" s="3" t="s">
-        <v>633</v>
       </c>
       <c r="C445" s="3" t="s">
         <v>186</v>
@@ -11522,13 +11522,13 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D446" s="5">
         <v>963.9</v>
@@ -11542,13 +11542,13 @@
     </row>
     <row r="447" spans="1:6">
       <c r="A447" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B447" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B447" s="3" t="s">
+      <c r="C447" s="4" t="s">
         <v>636</v>
-      </c>
-      <c r="C447" s="4" t="s">
-        <v>637</v>
       </c>
       <c r="D447" s="6">
         <v>2732.17</v>
@@ -11562,13 +11562,13 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B448" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C448" s="3" t="s">
         <v>638</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>639</v>
       </c>
       <c r="D448" s="5">
         <v>956.4</v>
@@ -11582,10 +11582,10 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B449" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="B449" s="3" t="s">
-        <v>641</v>
       </c>
       <c r="C449" s="3" t="s">
         <v>189</v>
@@ -11602,13 +11602,13 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B450" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="B450" s="3" t="s">
+      <c r="C450" s="4" t="s">
         <v>643</v>
-      </c>
-      <c r="C450" s="4" t="s">
-        <v>644</v>
       </c>
       <c r="D450" s="6">
         <v>1128.3</v>
@@ -11622,13 +11622,13 @@
     </row>
     <row r="451" spans="1:6">
       <c r="A451" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B451" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="B451" s="3" t="s">
+      <c r="C451" s="3" t="s">
         <v>646</v>
-      </c>
-      <c r="C451" s="3" t="s">
-        <v>647</v>
       </c>
       <c r="D451" s="5">
         <v>628.79999999999995</v>
@@ -11645,10 +11645,10 @@
         <v>279</v>
       </c>
       <c r="B452" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="C452" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>649</v>
       </c>
       <c r="D452" s="6">
         <v>2644.48</v>
@@ -11662,13 +11662,13 @@
     </row>
     <row r="453" spans="1:6">
       <c r="A453" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B453" s="7">
         <v>9622</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D453" s="5">
         <v>259.06</v>
@@ -11702,10 +11702,10 @@
     </row>
     <row r="455" spans="1:6">
       <c r="A455" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B455" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="B455" s="3" t="s">
-        <v>652</v>
       </c>
       <c r="C455" s="3" t="s">
         <v>162</v>
@@ -11722,10 +11722,10 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C456" s="3" t="s">
         <v>192</v>
@@ -11745,10 +11745,10 @@
         <v>138</v>
       </c>
       <c r="B457" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C457" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="C457" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="D457" s="6">
         <v>6232.46</v>
@@ -11765,10 +11765,10 @@
         <v>138</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D458" s="6">
         <v>9370.36</v>
@@ -11785,10 +11785,10 @@
         <v>279</v>
       </c>
       <c r="B459" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="C459" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="C459" s="3" t="s">
-        <v>658</v>
       </c>
       <c r="D459" s="6">
         <v>2931.2</v>
@@ -11805,10 +11805,10 @@
         <v>279</v>
       </c>
       <c r="B460" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C460" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="C460" s="3" t="s">
-        <v>660</v>
       </c>
       <c r="D460" s="6">
         <v>2741.2</v>
@@ -11825,10 +11825,10 @@
         <v>279</v>
       </c>
       <c r="B461" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C461" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="C461" s="3" t="s">
-        <v>662</v>
       </c>
       <c r="D461" s="6">
         <v>3087.07</v>
@@ -11845,10 +11845,10 @@
         <v>279</v>
       </c>
       <c r="B462" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C462" s="4" t="s">
         <v>663</v>
-      </c>
-      <c r="C462" s="4" t="s">
-        <v>664</v>
       </c>
       <c r="D462" s="6">
         <v>2201.4</v>
@@ -11865,10 +11865,10 @@
         <v>279</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D463" s="6">
         <v>2741.2</v>
@@ -11885,10 +11885,10 @@
         <v>287</v>
       </c>
       <c r="B464" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C464" s="4" t="s">
         <v>666</v>
-      </c>
-      <c r="C464" s="4" t="s">
-        <v>667</v>
       </c>
       <c r="D464" s="6">
         <v>1469.88</v>

--- a/Facturi_Neincasate.xlsx
+++ b/Facturi_Neincasate.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="645">
   <si>
     <t>Denumire client</t>
   </si>
@@ -866,9 +866,6 @@
   </si>
   <si>
     <t>TOTAL FOCUS TRADE SRL ALBA IULIA</t>
-  </si>
-  <si>
-    <t>DMEG 9575</t>
   </si>
   <si>
     <t>TRIFO AUTO SRL STREMT</t>
@@ -1959,9 +1956,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="168" formatCode="########0"/>
-    <numFmt numFmtId="169" formatCode="###,###,##0.00"/>
-    <numFmt numFmtId="170" formatCode="########0.00"/>
+    <numFmt numFmtId="164" formatCode="########0"/>
+    <numFmt numFmtId="165" formatCode="###,###,##0.00"/>
+    <numFmt numFmtId="166" formatCode="########0.00"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -2208,13 +2205,13 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2546,7 +2543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F480"/>
+  <dimension ref="A1:F479"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42.7109375" style="1" customWidth="1"/>
@@ -2560,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
@@ -2683,7 +2680,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D7" s="5">
         <v>1825.31</v>
@@ -2703,7 +2700,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D8" s="6">
         <v>761.15</v>
@@ -2783,7 +2780,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D12" s="5">
         <v>1990.1</v>
@@ -2883,7 +2880,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D17" s="5">
         <v>1938.46</v>
@@ -3043,7 +3040,7 @@
         <v>38</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D25" s="6">
         <v>149.44</v>
@@ -3123,7 +3120,7 @@
         <v>42</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D29" s="6">
         <v>109.38</v>
@@ -3143,7 +3140,7 @@
         <v>43</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D30" s="5">
         <v>1961.14</v>
@@ -3163,7 +3160,7 @@
         <v>44</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D31" s="5">
         <v>1140.42</v>
@@ -3183,7 +3180,7 @@
         <v>45</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D32" s="6">
         <v>607.47</v>
@@ -3263,7 +3260,7 @@
         <v>52</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D36" s="5">
         <v>1001.25</v>
@@ -3283,7 +3280,7 @@
         <v>53</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D37" s="5">
         <v>1001.25</v>
@@ -3363,7 +3360,7 @@
         <v>56</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D41" s="6">
         <v>631.30999999999995</v>
@@ -3443,7 +3440,7 @@
         <v>60</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D45" s="5">
         <v>1237.92</v>
@@ -3483,7 +3480,7 @@
         <v>65</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D47" s="5">
         <v>1127.1600000000001</v>
@@ -3503,7 +3500,7 @@
         <v>66</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D48" s="6">
         <v>455.71</v>
@@ -3583,7 +3580,7 @@
         <v>69</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D52" s="6">
         <v>774.25</v>
@@ -3663,7 +3660,7 @@
         <v>73</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D56" s="6">
         <v>768.39</v>
@@ -3683,7 +3680,7 @@
         <v>74</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D57" s="5">
         <v>1084.49</v>
@@ -3763,7 +3760,7 @@
         <v>78</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D61" s="6">
         <v>303.18</v>
@@ -3843,7 +3840,7 @@
         <v>85</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D65" s="6">
         <v>437.08</v>
@@ -3983,7 +3980,7 @@
         <v>95</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D72" s="5">
         <v>1045.26</v>
@@ -4043,7 +4040,7 @@
         <v>101</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D75" s="6">
         <v>334.17</v>
@@ -4063,7 +4060,7 @@
         <v>102</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D76" s="6">
         <v>239.26</v>
@@ -4083,7 +4080,7 @@
         <v>103</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D77" s="6">
         <v>490.77</v>
@@ -4123,7 +4120,7 @@
         <v>106</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D79" s="6">
         <v>541.19000000000005</v>
@@ -4243,7 +4240,7 @@
         <v>118</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D85" s="6">
         <v>842.01</v>
@@ -4363,7 +4360,7 @@
         <v>130</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D91" s="6">
         <v>377.52</v>
@@ -4383,7 +4380,7 @@
         <v>131</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D92" s="5">
         <v>4684.08</v>
@@ -4423,7 +4420,7 @@
         <v>9703</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D94" s="5">
         <v>2319.4499999999998</v>
@@ -4463,7 +4460,7 @@
         <v>135</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D96" s="6">
         <v>418.2</v>
@@ -4563,7 +4560,7 @@
         <v>9704</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D101" s="5">
         <v>6814.94</v>
@@ -4703,7 +4700,7 @@
         <v>154</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D108" s="6">
         <v>551.74</v>
@@ -4763,7 +4760,7 @@
         <v>159</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D111" s="5">
         <v>-10410.31</v>
@@ -4803,7 +4800,7 @@
         <v>163</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D113" s="6">
         <v>684.26</v>
@@ -4863,7 +4860,7 @@
         <v>166</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D116" s="6">
         <v>755.04</v>
@@ -4963,7 +4960,7 @@
         <v>172</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D121" s="5">
         <v>8148.44</v>
@@ -5043,7 +5040,7 @@
         <v>178</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D125" s="6">
         <v>219.43</v>
@@ -5103,7 +5100,7 @@
         <v>181</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D128" s="6">
         <v>711.77</v>
@@ -5303,7 +5300,7 @@
         <v>193</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D138" s="6">
         <v>537.76</v>
@@ -5363,7 +5360,7 @@
         <v>196</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D141" s="6">
         <v>659.82</v>
@@ -5403,7 +5400,7 @@
         <v>198</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D143" s="6">
         <v>341.65</v>
@@ -5483,7 +5480,7 @@
         <v>9697</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D147" s="6">
         <v>389.91</v>
@@ -5523,7 +5520,7 @@
         <v>207</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D149" s="5">
         <v>1391.53</v>
@@ -5643,7 +5640,7 @@
         <v>9701</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D155" s="6">
         <v>432.58</v>
@@ -5683,7 +5680,7 @@
         <v>212</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D157" s="6">
         <v>483.88</v>
@@ -5843,7 +5840,7 @@
         <v>220</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D165" s="6">
         <v>706.04</v>
@@ -5943,7 +5940,7 @@
         <v>226</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D170" s="6">
         <v>251.63</v>
@@ -6063,7 +6060,7 @@
         <v>234</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D176" s="6">
         <v>163.47</v>
@@ -6163,7 +6160,7 @@
         <v>9702</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D181" s="5">
         <v>2375.2800000000002</v>
@@ -6203,7 +6200,7 @@
         <v>241</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D183" s="6">
         <v>603.80999999999995</v>
@@ -6223,7 +6220,7 @@
         <v>242</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D184" s="6">
         <v>401.14</v>
@@ -6243,7 +6240,7 @@
         <v>243</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D185" s="6">
         <v>429.91</v>
@@ -6303,7 +6300,7 @@
         <v>248</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D188" s="5">
         <v>2086.77</v>
@@ -6323,7 +6320,7 @@
         <v>249</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D189" s="5">
         <v>1100.7</v>
@@ -6383,7 +6380,7 @@
         <v>252</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D192" s="6">
         <v>295.83</v>
@@ -6423,7 +6420,7 @@
         <v>9699</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D194" s="6">
         <v>768.48</v>
@@ -6443,7 +6440,7 @@
         <v>254</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D195" s="6">
         <v>311.14999999999998</v>
@@ -6543,7 +6540,7 @@
         <v>261</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D200" s="6">
         <v>398.26</v>
@@ -6583,7 +6580,7 @@
         <v>263</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D202" s="6">
         <v>270.98</v>
@@ -6603,7 +6600,7 @@
         <v>264</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D203" s="6">
         <v>430.93</v>
@@ -6663,7 +6660,7 @@
         <v>268</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D206" s="6">
         <v>467.44</v>
@@ -6683,7 +6680,7 @@
         <v>269</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D207" s="6">
         <v>271.20999999999998</v>
@@ -6723,7 +6720,7 @@
         <v>271</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D209" s="6">
         <v>350.72</v>
@@ -6883,7 +6880,7 @@
         <v>281</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D217" s="5">
         <v>10514.78</v>
@@ -6903,7 +6900,7 @@
         <v>282</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D218" s="5">
         <v>1142.45</v>
@@ -6919,20 +6916,20 @@
       <c r="A219" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B219" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>297</v>
+      <c r="B219" s="7">
+        <v>9599</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D219" s="6">
         <v>376.95</v>
       </c>
       <c r="E219" s="6">
-        <v>24.5</v>
+        <v>51.54</v>
       </c>
       <c r="F219" s="6">
-        <v>24.5</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -6940,19 +6937,19 @@
         <v>283</v>
       </c>
       <c r="B220" s="7">
-        <v>9599</v>
+        <v>9612</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D220" s="6">
-        <v>376.95</v>
+        <v>325.68</v>
       </c>
       <c r="E220" s="6">
-        <v>376.95</v>
+        <v>325.68</v>
       </c>
       <c r="F220" s="6">
-        <v>376.95</v>
+        <v>325.68</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -6960,19 +6957,19 @@
         <v>283</v>
       </c>
       <c r="B221" s="7">
-        <v>9612</v>
+        <v>9629</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D221" s="6">
-        <v>325.68</v>
+        <v>270.98</v>
       </c>
       <c r="E221" s="6">
-        <v>325.68</v>
+        <v>270.98</v>
       </c>
       <c r="F221" s="6">
-        <v>325.68</v>
+        <v>270.98</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -6980,19 +6977,19 @@
         <v>283</v>
       </c>
       <c r="B222" s="7">
-        <v>9629</v>
+        <v>9661</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D222" s="6">
-        <v>270.98</v>
+        <v>154.04</v>
       </c>
       <c r="E222" s="6">
-        <v>270.98</v>
+        <v>154.04</v>
       </c>
       <c r="F222" s="6">
-        <v>270.98</v>
+        <v>154.04</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -7000,19 +6997,19 @@
         <v>283</v>
       </c>
       <c r="B223" s="7">
-        <v>9661</v>
+        <v>9668</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D223" s="6">
-        <v>154.04</v>
+        <v>259.04000000000002</v>
       </c>
       <c r="E223" s="6">
-        <v>154.04</v>
+        <v>259.04000000000002</v>
       </c>
       <c r="F223" s="6">
-        <v>154.04</v>
+        <v>259.04000000000002</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -7020,464 +7017,464 @@
         <v>283</v>
       </c>
       <c r="B224" s="7">
-        <v>9668</v>
+        <v>9688</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D224" s="6">
-        <v>259.04000000000002</v>
+        <v>333.19</v>
       </c>
       <c r="E224" s="6">
-        <v>259.04000000000002</v>
+        <v>333.19</v>
       </c>
       <c r="F224" s="6">
-        <v>259.04000000000002</v>
+        <v>333.19</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B225" s="7">
-        <v>9688</v>
+        <v>9669</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D225" s="6">
-        <v>333.19</v>
+        <v>432.07</v>
       </c>
       <c r="E225" s="6">
-        <v>333.19</v>
+        <v>432.07</v>
       </c>
       <c r="F225" s="6">
-        <v>333.19</v>
+        <v>432.07</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B226" s="7">
-        <v>9669</v>
+        <v>9680</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D226" s="6">
-        <v>432.07</v>
-      </c>
-      <c r="E226" s="6">
-        <v>432.07</v>
-      </c>
-      <c r="F226" s="6">
-        <v>432.07</v>
+        <v>18</v>
+      </c>
+      <c r="D226" s="5">
+        <v>1853.6</v>
+      </c>
+      <c r="E226" s="5">
+        <v>1853.6</v>
+      </c>
+      <c r="F226" s="5">
+        <v>1853.6</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="B227" s="7">
-        <v>9680</v>
+      <c r="B227" s="3" t="s">
+        <v>286</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="D227" s="5">
-        <v>1853.6</v>
+        <v>4007.37</v>
       </c>
       <c r="E227" s="5">
-        <v>1853.6</v>
+        <v>4007.37</v>
       </c>
       <c r="F227" s="5">
-        <v>1853.6</v>
+        <v>4007.37</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C228" s="3" t="s">
-        <v>129</v>
+      <c r="C228" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="D228" s="5">
-        <v>4007.37</v>
+        <v>4165.26</v>
       </c>
       <c r="E228" s="5">
-        <v>4007.37</v>
+        <v>4165.26</v>
       </c>
       <c r="F228" s="5">
-        <v>4007.37</v>
+        <v>4165.26</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D229" s="5">
-        <v>4165.26</v>
-      </c>
-      <c r="E229" s="5">
-        <v>4165.26</v>
-      </c>
-      <c r="F229" s="5">
-        <v>4165.26</v>
+        <v>285</v>
+      </c>
+      <c r="B229" s="7">
+        <v>9653</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D229" s="6">
+        <v>572.52</v>
+      </c>
+      <c r="E229" s="6">
+        <v>572.52</v>
+      </c>
+      <c r="F229" s="6">
+        <v>572.52</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B230" s="7">
-        <v>9653</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>186</v>
+        <v>9700</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="D230" s="6">
-        <v>572.52</v>
+        <v>942.68</v>
       </c>
       <c r="E230" s="6">
-        <v>572.52</v>
+        <v>942.68</v>
       </c>
       <c r="F230" s="6">
-        <v>572.52</v>
+        <v>942.68</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B231" s="7">
-        <v>9700</v>
+        <v>288</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="D231" s="6">
-        <v>942.68</v>
+        <v>288.73</v>
       </c>
       <c r="E231" s="6">
-        <v>942.68</v>
+        <v>288.73</v>
       </c>
       <c r="F231" s="6">
-        <v>942.68</v>
+        <v>288.73</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>296</v>
+        <v>288</v>
+      </c>
+      <c r="B232" s="7">
+        <v>9611</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D232" s="6">
-        <v>288.73</v>
+        <v>272.25</v>
       </c>
       <c r="E232" s="6">
-        <v>288.73</v>
+        <v>272.25</v>
       </c>
       <c r="F232" s="6">
-        <v>288.73</v>
+        <v>272.25</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B233" s="7">
-        <v>9611</v>
+        <v>9649</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D233" s="6">
-        <v>272.25</v>
+        <v>188.76</v>
       </c>
       <c r="E233" s="6">
-        <v>272.25</v>
+        <v>188.76</v>
       </c>
       <c r="F233" s="6">
-        <v>272.25</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B234" s="7">
-        <v>9649</v>
+        <v>290</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D234" s="6">
-        <v>188.76</v>
-      </c>
-      <c r="E234" s="6">
-        <v>188.76</v>
-      </c>
-      <c r="F234" s="6">
-        <v>188.76</v>
+        <v>5</v>
+      </c>
+      <c r="D234" s="5">
+        <v>1548.06</v>
+      </c>
+      <c r="E234" s="5">
+        <v>1218.0899999999999</v>
+      </c>
+      <c r="F234" s="5">
+        <v>1218.0899999999999</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>292</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D235" s="5">
-        <v>1548.06</v>
-      </c>
-      <c r="E235" s="5">
-        <v>1218.0899999999999</v>
-      </c>
-      <c r="F235" s="5">
-        <v>1218.0899999999999</v>
+        <v>11</v>
+      </c>
+      <c r="D235" s="6">
+        <v>162.1</v>
+      </c>
+      <c r="E235" s="6">
+        <v>162.1</v>
+      </c>
+      <c r="F235" s="6">
+        <v>162.1</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C236" s="3" t="s">
-        <v>11</v>
+      <c r="C236" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="D236" s="6">
-        <v>162.1</v>
+        <v>672.42</v>
       </c>
       <c r="E236" s="6">
-        <v>162.1</v>
+        <v>672.42</v>
       </c>
       <c r="F236" s="6">
-        <v>162.1</v>
+        <v>672.42</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B237" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="C237" s="4" t="s">
-        <v>296</v>
+      <c r="B237" s="7">
+        <v>9641</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D237" s="6">
-        <v>672.42</v>
+        <v>916</v>
       </c>
       <c r="E237" s="6">
-        <v>672.42</v>
+        <v>916</v>
       </c>
       <c r="F237" s="6">
-        <v>672.42</v>
+        <v>916</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B238" s="7">
-        <v>9641</v>
+        <v>323</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D238" s="6">
-        <v>916</v>
+        <v>325</v>
+      </c>
+      <c r="D238" s="5">
+        <v>1395.04</v>
       </c>
       <c r="E238" s="6">
-        <v>916</v>
+        <v>911.88</v>
       </c>
       <c r="F238" s="6">
-        <v>916</v>
+        <v>911.88</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D239" s="5">
-        <v>1395.04</v>
+        <v>260</v>
+      </c>
+      <c r="D239" s="6">
+        <v>222.3</v>
       </c>
       <c r="E239" s="6">
-        <v>911.88</v>
+        <v>222.3</v>
       </c>
       <c r="F239" s="6">
-        <v>911.88</v>
+        <v>222.3</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>327</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>260</v>
+        <v>188</v>
       </c>
       <c r="D240" s="6">
-        <v>222.3</v>
+        <v>589.88</v>
       </c>
       <c r="E240" s="6">
-        <v>222.3</v>
+        <v>589.88</v>
       </c>
       <c r="F240" s="6">
-        <v>222.3</v>
+        <v>589.88</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B241" s="3" t="s">
         <v>328</v>
       </c>
+      <c r="B241" s="7">
+        <v>9621</v>
+      </c>
       <c r="C241" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D241" s="6">
-        <v>589.88</v>
-      </c>
-      <c r="E241" s="6">
-        <v>589.88</v>
-      </c>
-      <c r="F241" s="6">
-        <v>589.88</v>
+        <v>329</v>
+      </c>
+      <c r="D241" s="5">
+        <v>6601.54</v>
+      </c>
+      <c r="E241" s="5">
+        <v>6601.54</v>
+      </c>
+      <c r="F241" s="5">
+        <v>6601.54</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B242" s="7">
-        <v>9621</v>
+        <v>330</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D242" s="5">
-        <v>6601.54</v>
-      </c>
-      <c r="E242" s="5">
-        <v>6601.54</v>
-      </c>
-      <c r="F242" s="5">
-        <v>6601.54</v>
+        <v>112</v>
+      </c>
+      <c r="D242" s="6">
+        <v>421.28</v>
+      </c>
+      <c r="E242" s="6">
+        <v>17.61</v>
+      </c>
+      <c r="F242" s="6">
+        <v>17.61</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C243" s="3" t="s">
-        <v>112</v>
+      <c r="C243" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="D243" s="6">
-        <v>421.28</v>
+        <v>222.65</v>
       </c>
       <c r="E243" s="6">
-        <v>17.61</v>
+        <v>222.65</v>
       </c>
       <c r="F243" s="6">
-        <v>17.61</v>
+        <v>222.65</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C244" s="4" t="s">
-        <v>319</v>
+      <c r="C244" s="3" t="s">
+        <v>334</v>
       </c>
       <c r="D244" s="6">
-        <v>222.65</v>
+        <v>351.09</v>
       </c>
       <c r="E244" s="6">
-        <v>222.65</v>
+        <v>351.09</v>
       </c>
       <c r="F244" s="6">
-        <v>222.65</v>
+        <v>351.09</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D245" s="6">
-        <v>351.09</v>
+        <v>337</v>
+      </c>
+      <c r="D245" s="5">
+        <v>2219.77</v>
       </c>
       <c r="E245" s="6">
-        <v>351.09</v>
+        <v>219.77</v>
       </c>
       <c r="F245" s="6">
-        <v>351.09</v>
+        <v>219.77</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D246" s="5">
-        <v>2219.77</v>
+        <v>185</v>
+      </c>
+      <c r="D246" s="6">
+        <v>838.68</v>
       </c>
       <c r="E246" s="6">
-        <v>219.77</v>
+        <v>838.68</v>
       </c>
       <c r="F246" s="6">
-        <v>219.77</v>
+        <v>838.68</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>339</v>
@@ -7485,959 +7482,959 @@
       <c r="C247" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D247" s="6">
-        <v>838.68</v>
-      </c>
-      <c r="E247" s="6">
-        <v>838.68</v>
-      </c>
-      <c r="F247" s="6">
-        <v>838.68</v>
+      <c r="D247" s="5">
+        <v>3440.81</v>
+      </c>
+      <c r="E247" s="5">
+        <v>3440.81</v>
+      </c>
+      <c r="F247" s="5">
+        <v>3440.81</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>340</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D248" s="5">
-        <v>3440.81</v>
-      </c>
-      <c r="E248" s="5">
-        <v>3440.81</v>
-      </c>
-      <c r="F248" s="5">
-        <v>3440.81</v>
+        <v>341</v>
+      </c>
+      <c r="D248" s="6">
+        <v>353.93</v>
+      </c>
+      <c r="E248" s="6">
+        <v>353.93</v>
+      </c>
+      <c r="F248" s="6">
+        <v>353.93</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C249" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="D249" s="6">
-        <v>353.93</v>
+        <v>750.28</v>
       </c>
       <c r="E249" s="6">
-        <v>353.93</v>
+        <v>750.28</v>
       </c>
       <c r="F249" s="6">
-        <v>353.93</v>
+        <v>750.28</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C250" s="3" t="s">
-        <v>342</v>
+      <c r="C250" s="4" t="s">
+        <v>301</v>
       </c>
       <c r="D250" s="6">
-        <v>750.28</v>
+        <v>210.36</v>
       </c>
       <c r="E250" s="6">
-        <v>750.28</v>
+        <v>210.36</v>
       </c>
       <c r="F250" s="6">
-        <v>750.28</v>
+        <v>210.36</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C251" s="4" t="s">
-        <v>302</v>
+      <c r="C251" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="D251" s="6">
-        <v>210.36</v>
+        <v>810.63</v>
       </c>
       <c r="E251" s="6">
-        <v>210.36</v>
+        <v>810.63</v>
       </c>
       <c r="F251" s="6">
-        <v>210.36</v>
+        <v>810.63</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
+      </c>
+      <c r="B252" s="7">
+        <v>9602</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D252" s="6">
-        <v>810.63</v>
-      </c>
-      <c r="E252" s="6">
-        <v>810.63</v>
-      </c>
-      <c r="F252" s="6">
-        <v>810.63</v>
+        <v>64</v>
+      </c>
+      <c r="D252" s="5">
+        <v>1305.2</v>
+      </c>
+      <c r="E252" s="5">
+        <v>1305.2</v>
+      </c>
+      <c r="F252" s="5">
+        <v>1305.2</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B253" s="7">
-        <v>9602</v>
+        <v>345</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D253" s="5">
-        <v>1305.2</v>
-      </c>
-      <c r="E253" s="5">
-        <v>1305.2</v>
-      </c>
-      <c r="F253" s="5">
-        <v>1305.2</v>
+        <v>9</v>
+      </c>
+      <c r="D253" s="6">
+        <v>377.52</v>
+      </c>
+      <c r="E253" s="6">
+        <v>377.52</v>
+      </c>
+      <c r="F253" s="6">
+        <v>377.52</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="C254" s="3" t="s">
-        <v>9</v>
+      <c r="C254" s="4" t="s">
+        <v>298</v>
       </c>
       <c r="D254" s="6">
-        <v>377.52</v>
+        <v>506.72</v>
       </c>
       <c r="E254" s="6">
-        <v>377.52</v>
+        <v>506.72</v>
       </c>
       <c r="F254" s="6">
-        <v>377.52</v>
+        <v>506.72</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D255" s="6">
-        <v>506.72</v>
+        <v>350</v>
+      </c>
+      <c r="D255" s="5">
+        <v>1017.46</v>
       </c>
       <c r="E255" s="6">
-        <v>506.72</v>
+        <v>132.46</v>
       </c>
       <c r="F255" s="6">
-        <v>506.72</v>
+        <v>132.46</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C256" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D256" s="5">
-        <v>1017.46</v>
+      <c r="C256" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D256" s="6">
+        <v>152.68</v>
       </c>
       <c r="E256" s="6">
-        <v>132.46</v>
+        <v>152.68</v>
       </c>
       <c r="F256" s="6">
-        <v>132.46</v>
+        <v>152.68</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D257" s="6">
-        <v>152.68</v>
+        <v>163.05000000000001</v>
       </c>
       <c r="E257" s="6">
-        <v>152.68</v>
+        <v>163.05000000000001</v>
       </c>
       <c r="F257" s="6">
-        <v>152.68</v>
+        <v>163.05000000000001</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C258" s="3" t="s">
         <v>355</v>
       </c>
+      <c r="C258" s="4" t="s">
+        <v>356</v>
+      </c>
       <c r="D258" s="6">
-        <v>163.05000000000001</v>
+        <v>220.74</v>
       </c>
       <c r="E258" s="6">
-        <v>163.05000000000001</v>
+        <v>220.74</v>
       </c>
       <c r="F258" s="6">
-        <v>163.05000000000001</v>
+        <v>220.74</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D259" s="6">
-        <v>220.74</v>
+        <v>304.68</v>
       </c>
       <c r="E259" s="6">
-        <v>220.74</v>
+        <v>304.68</v>
       </c>
       <c r="F259" s="6">
-        <v>220.74</v>
+        <v>304.68</v>
       </c>
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D260" s="6">
-        <v>304.68</v>
+        <v>216.59</v>
       </c>
       <c r="E260" s="6">
-        <v>304.68</v>
+        <v>216.59</v>
       </c>
       <c r="F260" s="6">
-        <v>304.68</v>
+        <v>216.59</v>
       </c>
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="2" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="D261" s="6">
-        <v>216.59</v>
-      </c>
-      <c r="E261" s="6">
-        <v>216.59</v>
-      </c>
-      <c r="F261" s="6">
-        <v>216.59</v>
+        <v>362</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D261" s="5">
+        <v>3826.5</v>
+      </c>
+      <c r="E261" s="5">
+        <v>2826.5</v>
+      </c>
+      <c r="F261" s="5">
+        <v>2826.5</v>
       </c>
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
+      </c>
+      <c r="B262" s="7">
+        <v>9677</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="D262" s="5">
-        <v>3826.5</v>
+        <v>7204.92</v>
       </c>
       <c r="E262" s="5">
-        <v>2826.5</v>
+        <v>7204.92</v>
       </c>
       <c r="F262" s="5">
-        <v>2826.5</v>
+        <v>7204.92</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B263" s="7">
-        <v>9677</v>
+        <v>363</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>364</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>18</v>
+        <v>365</v>
       </c>
       <c r="D263" s="5">
-        <v>7204.92</v>
-      </c>
-      <c r="E263" s="5">
-        <v>7204.92</v>
-      </c>
-      <c r="F263" s="5">
-        <v>7204.92</v>
+        <v>2924.9</v>
+      </c>
+      <c r="E263" s="6">
+        <v>327.32</v>
+      </c>
+      <c r="F263" s="6">
+        <v>327.32</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D264" s="5">
-        <v>2924.9</v>
+        <v>82</v>
+      </c>
+      <c r="D264" s="6">
+        <v>506.52</v>
       </c>
       <c r="E264" s="6">
-        <v>327.32</v>
+        <v>506.52</v>
       </c>
       <c r="F264" s="6">
-        <v>327.32</v>
+        <v>506.52</v>
       </c>
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C265" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D265" s="6">
-        <v>506.52</v>
-      </c>
-      <c r="E265" s="6">
-        <v>506.52</v>
-      </c>
-      <c r="F265" s="6">
-        <v>506.52</v>
+      <c r="C265" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D265" s="5">
+        <v>1786.76</v>
+      </c>
+      <c r="E265" s="5">
+        <v>1786.76</v>
+      </c>
+      <c r="F265" s="5">
+        <v>1786.76</v>
       </c>
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="D266" s="5">
-        <v>1786.76</v>
+        <v>1578.01</v>
       </c>
       <c r="E266" s="5">
-        <v>1786.76</v>
+        <v>1578.01</v>
       </c>
       <c r="F266" s="5">
-        <v>1786.76</v>
+        <v>1578.01</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>371</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D267" s="5">
-        <v>1578.01</v>
-      </c>
-      <c r="E267" s="5">
-        <v>1578.01</v>
-      </c>
-      <c r="F267" s="5">
-        <v>1578.01</v>
+        <v>372</v>
+      </c>
+      <c r="D267" s="6">
+        <v>361.77</v>
+      </c>
+      <c r="E267" s="6">
+        <v>361.77</v>
+      </c>
+      <c r="F267" s="6">
+        <v>361.77</v>
       </c>
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D268" s="6">
-        <v>361.77</v>
-      </c>
-      <c r="E268" s="6">
-        <v>361.77</v>
-      </c>
-      <c r="F268" s="6">
-        <v>361.77</v>
+        <v>365</v>
+      </c>
+      <c r="D268" s="5">
+        <v>1156.58</v>
+      </c>
+      <c r="E268" s="5">
+        <v>1156.58</v>
+      </c>
+      <c r="F268" s="5">
+        <v>1156.58</v>
       </c>
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C269" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D269" s="5">
-        <v>1156.58</v>
-      </c>
-      <c r="E269" s="5">
-        <v>1156.58</v>
-      </c>
-      <c r="F269" s="5">
-        <v>1156.58</v>
+      <c r="C269" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D269" s="6">
+        <v>786.5</v>
+      </c>
+      <c r="E269" s="6">
+        <v>786.5</v>
+      </c>
+      <c r="F269" s="6">
+        <v>786.5</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D270" s="6">
-        <v>786.5</v>
-      </c>
-      <c r="E270" s="6">
-        <v>786.5</v>
-      </c>
-      <c r="F270" s="6">
-        <v>786.5</v>
+        <v>369</v>
+      </c>
+      <c r="B270" s="7">
+        <v>9618</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D270" s="5">
+        <v>1479.19</v>
+      </c>
+      <c r="E270" s="5">
+        <v>1479.19</v>
+      </c>
+      <c r="F270" s="5">
+        <v>1479.19</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B271" s="7">
-        <v>9618</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D271" s="5">
-        <v>1479.19</v>
-      </c>
-      <c r="E271" s="5">
-        <v>1479.19</v>
-      </c>
-      <c r="F271" s="5">
-        <v>1479.19</v>
+        <v>375</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D271" s="6">
+        <v>634.45000000000005</v>
+      </c>
+      <c r="E271" s="6">
+        <v>343.16</v>
+      </c>
+      <c r="F271" s="6">
+        <v>343.16</v>
       </c>
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>377</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D272" s="6">
-        <v>634.45000000000005</v>
-      </c>
-      <c r="E272" s="6">
-        <v>343.16</v>
-      </c>
-      <c r="F272" s="6">
-        <v>343.16</v>
+        <v>317</v>
+      </c>
+      <c r="D272" s="5">
+        <v>1258.33</v>
+      </c>
+      <c r="E272" s="5">
+        <v>1258.33</v>
+      </c>
+      <c r="F272" s="5">
+        <v>1258.33</v>
       </c>
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C273" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D273" s="5">
-        <v>1258.33</v>
-      </c>
-      <c r="E273" s="5">
-        <v>1258.33</v>
-      </c>
-      <c r="F273" s="5">
-        <v>1258.33</v>
+      <c r="C273" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D273" s="6">
+        <v>703.97</v>
+      </c>
+      <c r="E273" s="6">
+        <v>703.97</v>
+      </c>
+      <c r="F273" s="6">
+        <v>703.97</v>
       </c>
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>379</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="D274" s="6">
-        <v>703.97</v>
+        <v>522.53</v>
       </c>
       <c r="E274" s="6">
-        <v>703.97</v>
+        <v>522.53</v>
       </c>
       <c r="F274" s="6">
-        <v>703.97</v>
+        <v>522.53</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>380</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D275" s="6">
-        <v>522.53</v>
+        <v>268.63</v>
       </c>
       <c r="E275" s="6">
-        <v>522.53</v>
+        <v>268.63</v>
       </c>
       <c r="F275" s="6">
-        <v>522.53</v>
+        <v>268.63</v>
       </c>
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>381</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>366</v>
+        <v>129</v>
       </c>
       <c r="D276" s="6">
-        <v>268.63</v>
+        <v>110.33</v>
       </c>
       <c r="E276" s="6">
-        <v>268.63</v>
+        <v>110.33</v>
       </c>
       <c r="F276" s="6">
-        <v>268.63</v>
+        <v>110.33</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C277" s="3" t="s">
-        <v>129</v>
+      <c r="C277" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="D277" s="6">
-        <v>110.33</v>
+        <v>598.75</v>
       </c>
       <c r="E277" s="6">
-        <v>110.33</v>
+        <v>598.75</v>
       </c>
       <c r="F277" s="6">
-        <v>110.33</v>
+        <v>598.75</v>
       </c>
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>309</v>
+        <v>375</v>
+      </c>
+      <c r="B278" s="7">
+        <v>9619</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="D278" s="6">
-        <v>598.75</v>
+        <v>609.71</v>
       </c>
       <c r="E278" s="6">
-        <v>598.75</v>
+        <v>609.71</v>
       </c>
       <c r="F278" s="6">
-        <v>598.75</v>
+        <v>609.71</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B279" s="7">
-        <v>9619</v>
+        <v>9656</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>330</v>
+        <v>186</v>
       </c>
       <c r="D279" s="6">
-        <v>609.71</v>
+        <v>136.43</v>
       </c>
       <c r="E279" s="6">
-        <v>609.71</v>
+        <v>136.43</v>
       </c>
       <c r="F279" s="6">
-        <v>609.71</v>
+        <v>136.43</v>
       </c>
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="B280" s="7">
-        <v>9656</v>
+        <v>383</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D280" s="6">
-        <v>136.43</v>
-      </c>
-      <c r="E280" s="6">
-        <v>136.43</v>
-      </c>
-      <c r="F280" s="6">
-        <v>136.43</v>
+        <v>13</v>
+      </c>
+      <c r="D280" s="5">
+        <v>1368.51</v>
+      </c>
+      <c r="E280" s="5">
+        <v>1222.1600000000001</v>
+      </c>
+      <c r="F280" s="5">
+        <v>1222.1600000000001</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C281" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D281" s="5">
-        <v>1368.51</v>
-      </c>
-      <c r="E281" s="5">
-        <v>1222.1600000000001</v>
-      </c>
-      <c r="F281" s="5">
-        <v>1222.1600000000001</v>
+      <c r="C281" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D281" s="6">
+        <v>491.69</v>
+      </c>
+      <c r="E281" s="6">
+        <v>491.69</v>
+      </c>
+      <c r="F281" s="6">
+        <v>491.69</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C282" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B282" s="7">
+        <v>9639</v>
+      </c>
+      <c r="C282" s="3" t="s">
         <v>387</v>
       </c>
       <c r="D282" s="6">
-        <v>491.69</v>
+        <v>188.76</v>
       </c>
       <c r="E282" s="6">
-        <v>491.69</v>
+        <v>188.76</v>
       </c>
       <c r="F282" s="6">
-        <v>491.69</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B283" s="7">
-        <v>9639</v>
+        <v>9678</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="D283" s="6">
-        <v>188.76</v>
+        <v>362.8</v>
       </c>
       <c r="E283" s="6">
-        <v>188.76</v>
+        <v>362.8</v>
       </c>
       <c r="F283" s="6">
-        <v>188.76</v>
+        <v>362.8</v>
       </c>
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B284" s="7">
-        <v>9678</v>
+        <v>388</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>389</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D284" s="6">
-        <v>362.8</v>
+        <v>390</v>
+      </c>
+      <c r="D284" s="5">
+        <v>1603.85</v>
       </c>
       <c r="E284" s="6">
-        <v>362.8</v>
+        <v>653.74</v>
       </c>
       <c r="F284" s="6">
-        <v>362.8</v>
+        <v>653.74</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D285" s="5">
-        <v>1603.85</v>
+        <v>185</v>
+      </c>
+      <c r="D285" s="6">
+        <v>607.19000000000005</v>
       </c>
       <c r="E285" s="6">
-        <v>653.74</v>
+        <v>607.19000000000005</v>
       </c>
       <c r="F285" s="6">
-        <v>653.74</v>
+        <v>607.19000000000005</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>392</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="D286" s="6">
-        <v>607.19000000000005</v>
+        <v>250.31</v>
       </c>
       <c r="E286" s="6">
-        <v>607.19000000000005</v>
+        <v>250.31</v>
       </c>
       <c r="F286" s="6">
-        <v>607.19000000000005</v>
+        <v>250.31</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>393</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="D287" s="6">
-        <v>250.31</v>
+        <v>188.76</v>
       </c>
       <c r="E287" s="6">
-        <v>250.31</v>
+        <v>188.76</v>
       </c>
       <c r="F287" s="6">
-        <v>250.31</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D288" s="6">
-        <v>188.76</v>
+        <v>341</v>
+      </c>
+      <c r="D288" s="5">
+        <v>1468.04</v>
       </c>
       <c r="E288" s="6">
-        <v>188.76</v>
+        <v>91.86</v>
       </c>
       <c r="F288" s="6">
-        <v>188.76</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>396</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D289" s="5">
-        <v>1468.04</v>
-      </c>
-      <c r="E289" s="6">
-        <v>91.86</v>
-      </c>
-      <c r="F289" s="6">
-        <v>91.86</v>
+        <v>3705.98</v>
+      </c>
+      <c r="E289" s="5">
+        <v>3705.98</v>
+      </c>
+      <c r="F289" s="5">
+        <v>3705.98</v>
       </c>
     </row>
     <row r="290" spans="1:6">
       <c r="A290" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>397</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D290" s="5">
-        <v>3705.98</v>
-      </c>
-      <c r="E290" s="5">
-        <v>3705.98</v>
-      </c>
-      <c r="F290" s="5">
-        <v>3705.98</v>
+        <v>372</v>
+      </c>
+      <c r="D290" s="6">
+        <v>261.86</v>
+      </c>
+      <c r="E290" s="6">
+        <v>261.86</v>
+      </c>
+      <c r="F290" s="6">
+        <v>261.86</v>
       </c>
     </row>
     <row r="291" spans="1:6">
       <c r="A291" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>398</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>373</v>
+        <v>191</v>
       </c>
       <c r="D291" s="6">
-        <v>261.86</v>
+        <v>772.98</v>
       </c>
       <c r="E291" s="6">
-        <v>261.86</v>
+        <v>772.98</v>
       </c>
       <c r="F291" s="6">
-        <v>261.86</v>
+        <v>772.98</v>
       </c>
     </row>
     <row r="292" spans="1:6">
       <c r="A292" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C292" s="3" t="s">
-        <v>191</v>
+      <c r="C292" s="4" t="s">
+        <v>400</v>
       </c>
       <c r="D292" s="6">
-        <v>772.98</v>
+        <v>731.45</v>
       </c>
       <c r="E292" s="6">
-        <v>772.98</v>
+        <v>731.45</v>
       </c>
       <c r="F292" s="6">
-        <v>772.98</v>
+        <v>731.45</v>
       </c>
     </row>
     <row r="293" spans="1:6">
       <c r="A293" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="D293" s="6">
-        <v>731.45</v>
-      </c>
-      <c r="E293" s="6">
-        <v>731.45</v>
-      </c>
-      <c r="F293" s="6">
-        <v>731.45</v>
+        <v>301</v>
+      </c>
+      <c r="D293" s="5">
+        <v>1310.6199999999999</v>
+      </c>
+      <c r="E293" s="5">
+        <v>1310.6199999999999</v>
+      </c>
+      <c r="F293" s="5">
+        <v>1310.6199999999999</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C294" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D294" s="5">
-        <v>1310.6199999999999</v>
-      </c>
-      <c r="E294" s="5">
-        <v>1310.6199999999999</v>
-      </c>
-      <c r="F294" s="5">
-        <v>1310.6199999999999</v>
+      <c r="C294" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D294" s="6">
+        <v>749.9</v>
+      </c>
+      <c r="E294" s="6">
+        <v>749.9</v>
+      </c>
+      <c r="F294" s="6">
+        <v>749.9</v>
       </c>
     </row>
     <row r="295" spans="1:6">
       <c r="A295" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>403</v>
@@ -8445,214 +8442,214 @@
       <c r="C295" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D295" s="6">
-        <v>749.9</v>
-      </c>
-      <c r="E295" s="6">
-        <v>749.9</v>
-      </c>
-      <c r="F295" s="6">
-        <v>749.9</v>
+      <c r="D295" s="5">
+        <v>1994.85</v>
+      </c>
+      <c r="E295" s="5">
+        <v>1994.85</v>
+      </c>
+      <c r="F295" s="5">
+        <v>1994.85</v>
       </c>
     </row>
     <row r="296" spans="1:6">
       <c r="A296" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>404</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D296" s="5">
-        <v>1994.85</v>
-      </c>
-      <c r="E296" s="5">
-        <v>1994.85</v>
-      </c>
-      <c r="F296" s="5">
-        <v>1994.85</v>
+        <v>80</v>
+      </c>
+      <c r="D296" s="6">
+        <v>648.86</v>
+      </c>
+      <c r="E296" s="6">
+        <v>648.86</v>
+      </c>
+      <c r="F296" s="6">
+        <v>648.86</v>
       </c>
     </row>
     <row r="297" spans="1:6">
       <c r="A297" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>405</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D297" s="6">
-        <v>648.86</v>
-      </c>
-      <c r="E297" s="6">
-        <v>648.86</v>
-      </c>
-      <c r="F297" s="6">
-        <v>648.86</v>
+        <v>82</v>
+      </c>
+      <c r="D297" s="5">
+        <v>1620.7</v>
+      </c>
+      <c r="E297" s="5">
+        <v>1620.7</v>
+      </c>
+      <c r="F297" s="5">
+        <v>1620.7</v>
       </c>
     </row>
     <row r="298" spans="1:6">
       <c r="A298" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>406</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D298" s="5">
-        <v>1620.7</v>
-      </c>
-      <c r="E298" s="5">
-        <v>1620.7</v>
-      </c>
-      <c r="F298" s="5">
-        <v>1620.7</v>
+        <v>30</v>
+      </c>
+      <c r="D298" s="6">
+        <v>259.98</v>
+      </c>
+      <c r="E298" s="6">
+        <v>259.98</v>
+      </c>
+      <c r="F298" s="6">
+        <v>259.98</v>
       </c>
     </row>
     <row r="299" spans="1:6">
       <c r="A299" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C299" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D299" s="6">
-        <v>259.98</v>
-      </c>
-      <c r="E299" s="6">
-        <v>259.98</v>
-      </c>
-      <c r="F299" s="6">
-        <v>259.98</v>
+      <c r="C299" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D299" s="5">
+        <v>3358.91</v>
+      </c>
+      <c r="E299" s="5">
+        <v>3358.91</v>
+      </c>
+      <c r="F299" s="5">
+        <v>3358.91</v>
       </c>
     </row>
     <row r="300" spans="1:6">
       <c r="A300" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>408</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D300" s="5">
-        <v>3358.91</v>
-      </c>
-      <c r="E300" s="5">
-        <v>3358.91</v>
-      </c>
-      <c r="F300" s="5">
-        <v>3358.91</v>
+        <v>386</v>
+      </c>
+      <c r="D300" s="6">
+        <v>860.86</v>
+      </c>
+      <c r="E300" s="6">
+        <v>860.86</v>
+      </c>
+      <c r="F300" s="6">
+        <v>860.86</v>
       </c>
     </row>
     <row r="301" spans="1:6">
       <c r="A301" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="C301" s="4" t="s">
-        <v>387</v>
+        <v>394</v>
+      </c>
+      <c r="B301" s="7">
+        <v>9600</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D301" s="6">
-        <v>860.86</v>
+        <v>986.83</v>
       </c>
       <c r="E301" s="6">
-        <v>860.86</v>
+        <v>986.83</v>
       </c>
       <c r="F301" s="6">
-        <v>860.86</v>
+        <v>986.83</v>
       </c>
     </row>
     <row r="302" spans="1:6">
       <c r="A302" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B302" s="7">
-        <v>9600</v>
+        <v>9614</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>64</v>
+        <v>329</v>
       </c>
       <c r="D302" s="6">
-        <v>986.83</v>
+        <v>268.77999999999997</v>
       </c>
       <c r="E302" s="6">
-        <v>986.83</v>
+        <v>268.77999999999997</v>
       </c>
       <c r="F302" s="6">
-        <v>986.83</v>
+        <v>268.77999999999997</v>
       </c>
     </row>
     <row r="303" spans="1:6">
       <c r="A303" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B303" s="7">
-        <v>9614</v>
+        <v>9636</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="D303" s="6">
-        <v>268.77999999999997</v>
+        <v>259.04000000000002</v>
       </c>
       <c r="E303" s="6">
-        <v>268.77999999999997</v>
+        <v>259.04000000000002</v>
       </c>
       <c r="F303" s="6">
-        <v>268.77999999999997</v>
+        <v>259.04000000000002</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B304" s="7">
-        <v>9636</v>
+        <v>9676</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D304" s="6">
-        <v>259.04000000000002</v>
-      </c>
-      <c r="E304" s="6">
-        <v>259.04000000000002</v>
-      </c>
-      <c r="F304" s="6">
-        <v>259.04000000000002</v>
+        <v>18</v>
+      </c>
+      <c r="D304" s="5">
+        <v>6751.52</v>
+      </c>
+      <c r="E304" s="5">
+        <v>6751.52</v>
+      </c>
+      <c r="F304" s="5">
+        <v>6751.52</v>
       </c>
     </row>
     <row r="305" spans="1:6">
       <c r="A305" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B305" s="7">
-        <v>9676</v>
-      </c>
-      <c r="C305" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D305" s="5">
-        <v>6751.52</v>
-      </c>
-      <c r="E305" s="5">
-        <v>6751.52</v>
-      </c>
-      <c r="F305" s="5">
-        <v>6751.52</v>
+        <v>114</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D305" s="6">
+        <v>797.4</v>
+      </c>
+      <c r="E305" s="6">
+        <v>329.63</v>
+      </c>
+      <c r="F305" s="6">
+        <v>329.63</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -8660,19 +8657,19 @@
         <v>114</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C306" s="4" t="s">
         <v>411</v>
       </c>
+      <c r="C306" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="D306" s="6">
-        <v>797.4</v>
+        <v>349.33</v>
       </c>
       <c r="E306" s="6">
-        <v>329.63</v>
+        <v>349.33</v>
       </c>
       <c r="F306" s="6">
-        <v>329.63</v>
+        <v>349.33</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -8682,17 +8679,17 @@
       <c r="B307" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C307" s="3" t="s">
-        <v>260</v>
+      <c r="C307" s="4" t="s">
+        <v>317</v>
       </c>
       <c r="D307" s="6">
-        <v>349.33</v>
+        <v>530.57000000000005</v>
       </c>
       <c r="E307" s="6">
-        <v>349.33</v>
+        <v>530.57000000000005</v>
       </c>
       <c r="F307" s="6">
-        <v>349.33</v>
+        <v>530.57000000000005</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -8702,17 +8699,17 @@
       <c r="B308" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C308" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D308" s="6">
-        <v>530.57000000000005</v>
-      </c>
-      <c r="E308" s="6">
-        <v>530.57000000000005</v>
-      </c>
-      <c r="F308" s="6">
-        <v>530.57000000000005</v>
+      <c r="C308" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D308" s="5">
+        <v>1109.42</v>
+      </c>
+      <c r="E308" s="5">
+        <v>1109.42</v>
+      </c>
+      <c r="F308" s="5">
+        <v>1109.42</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -8723,16 +8720,16 @@
         <v>414</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D309" s="5">
-        <v>1109.42</v>
-      </c>
-      <c r="E309" s="5">
-        <v>1109.42</v>
-      </c>
-      <c r="F309" s="5">
-        <v>1109.42</v>
+        <v>365</v>
+      </c>
+      <c r="D309" s="6">
+        <v>257.98</v>
+      </c>
+      <c r="E309" s="6">
+        <v>257.98</v>
+      </c>
+      <c r="F309" s="6">
+        <v>257.98</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -8742,37 +8739,37 @@
       <c r="B310" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C310" s="3" t="s">
-        <v>366</v>
+      <c r="C310" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="D310" s="6">
-        <v>257.98</v>
+        <v>246.58</v>
       </c>
       <c r="E310" s="6">
-        <v>257.98</v>
+        <v>246.58</v>
       </c>
       <c r="F310" s="6">
-        <v>257.98</v>
+        <v>246.58</v>
       </c>
     </row>
     <row r="311" spans="1:6">
       <c r="A311" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B311" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>309</v>
+      <c r="B311" s="7">
+        <v>9617</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="D311" s="6">
-        <v>246.58</v>
+        <v>553.42999999999995</v>
       </c>
       <c r="E311" s="6">
-        <v>246.58</v>
+        <v>553.42999999999995</v>
       </c>
       <c r="F311" s="6">
-        <v>246.58</v>
+        <v>553.42999999999995</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -8780,1299 +8777,1299 @@
         <v>114</v>
       </c>
       <c r="B312" s="7">
-        <v>9617</v>
+        <v>9655</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>330</v>
+        <v>186</v>
       </c>
       <c r="D312" s="6">
-        <v>553.42999999999995</v>
+        <v>519.86</v>
       </c>
       <c r="E312" s="6">
-        <v>553.42999999999995</v>
+        <v>519.86</v>
       </c>
       <c r="F312" s="6">
-        <v>553.42999999999995</v>
+        <v>519.86</v>
       </c>
     </row>
     <row r="313" spans="1:6">
       <c r="A313" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B313" s="7">
-        <v>9655</v>
+        <v>416</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D313" s="6">
-        <v>519.86</v>
-      </c>
-      <c r="E313" s="6">
-        <v>519.86</v>
-      </c>
-      <c r="F313" s="6">
-        <v>519.86</v>
+        <v>418</v>
+      </c>
+      <c r="D313" s="5">
+        <v>2644.4</v>
+      </c>
+      <c r="E313" s="5">
+        <v>1437.29</v>
+      </c>
+      <c r="F313" s="5">
+        <v>1437.29</v>
       </c>
     </row>
     <row r="314" spans="1:6">
       <c r="A314" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="D314" s="5">
-        <v>2644.4</v>
-      </c>
-      <c r="E314" s="5">
-        <v>1437.29</v>
-      </c>
-      <c r="F314" s="5">
-        <v>1437.29</v>
+        <v>420</v>
+      </c>
+      <c r="D314" s="6">
+        <v>403.75</v>
+      </c>
+      <c r="E314" s="6">
+        <v>403.75</v>
+      </c>
+      <c r="F314" s="6">
+        <v>403.75</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C315" s="3" t="s">
         <v>421</v>
       </c>
+      <c r="C315" s="4" t="s">
+        <v>422</v>
+      </c>
       <c r="D315" s="6">
-        <v>403.75</v>
+        <v>326.95</v>
       </c>
       <c r="E315" s="6">
-        <v>403.75</v>
+        <v>326.95</v>
       </c>
       <c r="F315" s="6">
-        <v>403.75</v>
+        <v>326.95</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C316" s="4" t="s">
         <v>423</v>
       </c>
+      <c r="C316" s="3" t="s">
+        <v>424</v>
+      </c>
       <c r="D316" s="6">
-        <v>326.95</v>
+        <v>708.92</v>
       </c>
       <c r="E316" s="6">
-        <v>326.95</v>
+        <v>708.92</v>
       </c>
       <c r="F316" s="6">
-        <v>326.95</v>
+        <v>708.92</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C317" s="3" t="s">
         <v>425</v>
       </c>
+      <c r="C317" s="4" t="s">
+        <v>410</v>
+      </c>
       <c r="D317" s="6">
-        <v>708.92</v>
+        <v>170.36</v>
       </c>
       <c r="E317" s="6">
-        <v>708.92</v>
+        <v>170.36</v>
       </c>
       <c r="F317" s="6">
-        <v>708.92</v>
+        <v>170.36</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C318" s="4" t="s">
-        <v>411</v>
+      <c r="C318" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="D318" s="6">
-        <v>170.36</v>
+        <v>417.37</v>
       </c>
       <c r="E318" s="6">
-        <v>170.36</v>
+        <v>417.37</v>
       </c>
       <c r="F318" s="6">
-        <v>170.36</v>
+        <v>417.37</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="C319" s="3" t="s">
-        <v>326</v>
+      <c r="C319" s="4" t="s">
+        <v>298</v>
       </c>
       <c r="D319" s="6">
-        <v>417.37</v>
+        <v>543.71</v>
       </c>
       <c r="E319" s="6">
-        <v>417.37</v>
+        <v>543.71</v>
       </c>
       <c r="F319" s="6">
-        <v>417.37</v>
+        <v>543.71</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>299</v>
+        <v>416</v>
+      </c>
+      <c r="B320" s="7">
+        <v>9654</v>
+      </c>
+      <c r="C320" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="D320" s="6">
-        <v>543.71</v>
+        <v>351.53</v>
       </c>
       <c r="E320" s="6">
-        <v>543.71</v>
+        <v>351.53</v>
       </c>
       <c r="F320" s="6">
-        <v>543.71</v>
+        <v>351.53</v>
       </c>
     </row>
     <row r="321" spans="1:6">
       <c r="A321" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B321" s="7">
-        <v>9654</v>
-      </c>
-      <c r="C321" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D321" s="6">
-        <v>351.53</v>
-      </c>
-      <c r="E321" s="6">
-        <v>351.53</v>
-      </c>
-      <c r="F321" s="6">
-        <v>351.53</v>
+        <v>428</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D321" s="5">
+        <v>1448.37</v>
+      </c>
+      <c r="E321" s="5">
+        <v>1448.37</v>
+      </c>
+      <c r="F321" s="5">
+        <v>1448.37</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>430</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="D322" s="5">
-        <v>1448.37</v>
+        <v>1380.29</v>
       </c>
       <c r="E322" s="5">
-        <v>1448.37</v>
+        <v>1380.29</v>
       </c>
       <c r="F322" s="5">
-        <v>1448.37</v>
+        <v>1380.29</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B323" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
+      </c>
+      <c r="B323" s="7">
+        <v>9690</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D323" s="5">
-        <v>1380.29</v>
-      </c>
-      <c r="E323" s="5">
-        <v>1380.29</v>
-      </c>
-      <c r="F323" s="5">
-        <v>1380.29</v>
+        <v>315</v>
+      </c>
+      <c r="D323" s="6">
+        <v>794.89</v>
+      </c>
+      <c r="E323" s="6">
+        <v>794.89</v>
+      </c>
+      <c r="F323" s="6">
+        <v>794.89</v>
       </c>
     </row>
     <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B324" s="7">
-        <v>9690</v>
+        <v>431</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>432</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D324" s="6">
-        <v>794.89</v>
+        <v>433</v>
+      </c>
+      <c r="D324" s="5">
+        <v>4795.4399999999996</v>
       </c>
       <c r="E324" s="6">
-        <v>794.89</v>
+        <v>498.17</v>
       </c>
       <c r="F324" s="6">
-        <v>794.89</v>
+        <v>498.17</v>
       </c>
     </row>
     <row r="325" spans="1:6">
       <c r="A325" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B325" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C325" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C325" s="4" t="s">
-        <v>434</v>
-      </c>
       <c r="D325" s="5">
-        <v>4795.4399999999996</v>
-      </c>
-      <c r="E325" s="6">
-        <v>498.17</v>
-      </c>
-      <c r="F325" s="6">
-        <v>498.17</v>
+        <v>1575.72</v>
+      </c>
+      <c r="E325" s="5">
+        <v>1575.72</v>
+      </c>
+      <c r="F325" s="5">
+        <v>1575.72</v>
       </c>
     </row>
     <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>435</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D326" s="5">
-        <v>1575.72</v>
-      </c>
-      <c r="E326" s="5">
-        <v>1575.72</v>
-      </c>
-      <c r="F326" s="5">
-        <v>1575.72</v>
+        <v>436</v>
+      </c>
+      <c r="D326" s="6">
+        <v>63.48</v>
+      </c>
+      <c r="E326" s="6">
+        <v>63.48</v>
+      </c>
+      <c r="F326" s="6">
+        <v>63.48</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D327" s="6">
-        <v>63.48</v>
+        <v>93.8</v>
       </c>
       <c r="E327" s="6">
-        <v>63.48</v>
+        <v>93.8</v>
       </c>
       <c r="F327" s="6">
-        <v>63.48</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B328" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="C328" s="4" t="s">
-        <v>439</v>
-      </c>
       <c r="D328" s="6">
-        <v>93.8</v>
+        <v>852.76</v>
       </c>
       <c r="E328" s="6">
-        <v>93.8</v>
+        <v>852.76</v>
       </c>
       <c r="F328" s="6">
-        <v>93.8</v>
+        <v>852.76</v>
       </c>
     </row>
     <row r="329" spans="1:6">
       <c r="A329" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C329" s="4" t="s">
-        <v>439</v>
+      <c r="C329" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="D329" s="6">
-        <v>852.76</v>
+        <v>119.58</v>
       </c>
       <c r="E329" s="6">
-        <v>852.76</v>
+        <v>119.58</v>
       </c>
       <c r="F329" s="6">
-        <v>852.76</v>
+        <v>119.58</v>
       </c>
     </row>
     <row r="330" spans="1:6">
       <c r="A330" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D330" s="6">
-        <v>119.58</v>
+        <v>467.32</v>
       </c>
       <c r="E330" s="6">
-        <v>119.58</v>
+        <v>467.32</v>
       </c>
       <c r="F330" s="6">
-        <v>119.58</v>
+        <v>467.32</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B331" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
+      </c>
+      <c r="B331" s="7">
+        <v>9673</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>444</v>
+        <v>18</v>
       </c>
       <c r="D331" s="6">
-        <v>467.32</v>
+        <v>954.34</v>
       </c>
       <c r="E331" s="6">
-        <v>467.32</v>
+        <v>954.34</v>
       </c>
       <c r="F331" s="6">
-        <v>467.32</v>
+        <v>954.34</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B332" s="7">
-        <v>9673</v>
+      <c r="B332" s="3" t="s">
+        <v>446</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>18</v>
+        <v>424</v>
       </c>
       <c r="D332" s="6">
-        <v>954.34</v>
+        <v>778.34</v>
       </c>
       <c r="E332" s="6">
-        <v>954.34</v>
+        <v>547.01</v>
       </c>
       <c r="F332" s="6">
-        <v>954.34</v>
+        <v>547.01</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>447</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D333" s="6">
-        <v>778.34</v>
-      </c>
-      <c r="E333" s="6">
-        <v>547.01</v>
-      </c>
-      <c r="F333" s="6">
-        <v>547.01</v>
+        <v>112</v>
+      </c>
+      <c r="D333" s="5">
+        <v>1052.3699999999999</v>
+      </c>
+      <c r="E333" s="5">
+        <v>1052.3699999999999</v>
+      </c>
+      <c r="F333" s="5">
+        <v>1052.3699999999999</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C334" s="3" t="s">
-        <v>112</v>
+      <c r="C334" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="D334" s="5">
-        <v>1052.3699999999999</v>
+        <v>1352.99</v>
       </c>
       <c r="E334" s="5">
-        <v>1052.3699999999999</v>
+        <v>1352.99</v>
       </c>
       <c r="F334" s="5">
-        <v>1052.3699999999999</v>
+        <v>1352.99</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>449</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D335" s="5">
-        <v>1352.99</v>
-      </c>
-      <c r="E335" s="5">
-        <v>1352.99</v>
-      </c>
-      <c r="F335" s="5">
-        <v>1352.99</v>
+        <v>319</v>
+      </c>
+      <c r="D335" s="6">
+        <v>164.08</v>
+      </c>
+      <c r="E335" s="6">
+        <v>164.08</v>
+      </c>
+      <c r="F335" s="6">
+        <v>164.08</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>450</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D336" s="6">
-        <v>164.08</v>
+        <v>374.52</v>
       </c>
       <c r="E336" s="6">
-        <v>164.08</v>
+        <v>374.52</v>
       </c>
       <c r="F336" s="6">
-        <v>164.08</v>
+        <v>374.52</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C337" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D337" s="6">
-        <v>374.52</v>
-      </c>
-      <c r="E337" s="6">
-        <v>374.52</v>
-      </c>
-      <c r="F337" s="6">
-        <v>374.52</v>
+      <c r="C337" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D337" s="5">
+        <v>1873.63</v>
+      </c>
+      <c r="E337" s="5">
+        <v>1873.63</v>
+      </c>
+      <c r="F337" s="5">
+        <v>1873.63</v>
       </c>
     </row>
     <row r="338" spans="1:6">
       <c r="A338" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>452</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D338" s="5">
-        <v>1873.63</v>
-      </c>
-      <c r="E338" s="5">
-        <v>1873.63</v>
-      </c>
-      <c r="F338" s="5">
-        <v>1873.63</v>
+        <v>260</v>
+      </c>
+      <c r="D338" s="6">
+        <v>397.56</v>
+      </c>
+      <c r="E338" s="6">
+        <v>397.56</v>
+      </c>
+      <c r="F338" s="6">
+        <v>397.56</v>
       </c>
     </row>
     <row r="339" spans="1:6">
       <c r="A339" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>453</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D339" s="6">
-        <v>397.56</v>
-      </c>
-      <c r="E339" s="6">
-        <v>397.56</v>
-      </c>
-      <c r="F339" s="6">
-        <v>397.56</v>
+        <v>116</v>
+      </c>
+      <c r="D339" s="5">
+        <v>1135.22</v>
+      </c>
+      <c r="E339" s="5">
+        <v>1135.22</v>
+      </c>
+      <c r="F339" s="5">
+        <v>1135.22</v>
       </c>
     </row>
     <row r="340" spans="1:6">
       <c r="A340" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C340" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D340" s="5">
-        <v>1135.22</v>
-      </c>
-      <c r="E340" s="5">
-        <v>1135.22</v>
-      </c>
-      <c r="F340" s="5">
-        <v>1135.22</v>
+      <c r="C340" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D340" s="6">
+        <v>910.84</v>
+      </c>
+      <c r="E340" s="6">
+        <v>910.84</v>
+      </c>
+      <c r="F340" s="6">
+        <v>910.84</v>
       </c>
     </row>
     <row r="341" spans="1:6">
       <c r="A341" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C341" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D341" s="6">
-        <v>910.84</v>
-      </c>
-      <c r="E341" s="6">
-        <v>910.84</v>
-      </c>
-      <c r="F341" s="6">
-        <v>910.84</v>
+      <c r="C341" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D341" s="5">
+        <v>1313.79</v>
+      </c>
+      <c r="E341" s="5">
+        <v>1313.79</v>
+      </c>
+      <c r="F341" s="5">
+        <v>1313.79</v>
       </c>
     </row>
     <row r="342" spans="1:6">
       <c r="A342" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>456</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D342" s="5">
-        <v>1313.79</v>
-      </c>
-      <c r="E342" s="5">
-        <v>1313.79</v>
-      </c>
-      <c r="F342" s="5">
-        <v>1313.79</v>
+        <v>334</v>
+      </c>
+      <c r="D342" s="6">
+        <v>374.52</v>
+      </c>
+      <c r="E342" s="6">
+        <v>374.52</v>
+      </c>
+      <c r="F342" s="6">
+        <v>374.52</v>
       </c>
     </row>
     <row r="343" spans="1:6">
       <c r="A343" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>457</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="D343" s="6">
-        <v>374.52</v>
+        <v>633.09</v>
       </c>
       <c r="E343" s="6">
-        <v>374.52</v>
+        <v>633.09</v>
       </c>
       <c r="F343" s="6">
-        <v>374.52</v>
+        <v>633.09</v>
       </c>
     </row>
     <row r="344" spans="1:6">
       <c r="A344" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D344" s="6">
-        <v>633.09</v>
-      </c>
-      <c r="E344" s="6">
-        <v>633.09</v>
-      </c>
-      <c r="F344" s="6">
-        <v>633.09</v>
+        <v>129</v>
+      </c>
+      <c r="D344" s="5">
+        <v>1120.5</v>
+      </c>
+      <c r="E344" s="5">
+        <v>1120.5</v>
+      </c>
+      <c r="F344" s="5">
+        <v>1120.5</v>
       </c>
     </row>
     <row r="345" spans="1:6">
       <c r="A345" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C345" s="3" t="s">
-        <v>129</v>
+      <c r="C345" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="D345" s="5">
-        <v>1120.5</v>
+        <v>1202.8499999999999</v>
       </c>
       <c r="E345" s="5">
-        <v>1120.5</v>
+        <v>1202.8499999999999</v>
       </c>
       <c r="F345" s="5">
-        <v>1120.5</v>
+        <v>1202.8499999999999</v>
       </c>
     </row>
     <row r="346" spans="1:6">
       <c r="A346" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>460</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D346" s="5">
-        <v>1202.8499999999999</v>
-      </c>
-      <c r="E346" s="5">
-        <v>1202.8499999999999</v>
-      </c>
-      <c r="F346" s="5">
-        <v>1202.8499999999999</v>
+        <v>298</v>
+      </c>
+      <c r="D346" s="6">
+        <v>651.34</v>
+      </c>
+      <c r="E346" s="6">
+        <v>651.34</v>
+      </c>
+      <c r="F346" s="6">
+        <v>651.34</v>
       </c>
     </row>
     <row r="347" spans="1:6">
       <c r="A347" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B347" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="C347" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D347" s="6">
-        <v>651.34</v>
-      </c>
-      <c r="E347" s="6">
-        <v>651.34</v>
-      </c>
-      <c r="F347" s="6">
-        <v>651.34</v>
+        <v>445</v>
+      </c>
+      <c r="B347" s="7">
+        <v>9615</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D347" s="5">
+        <v>2250.61</v>
+      </c>
+      <c r="E347" s="5">
+        <v>2250.61</v>
+      </c>
+      <c r="F347" s="5">
+        <v>2250.61</v>
       </c>
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B348" s="7">
-        <v>9615</v>
+        <v>9657</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D348" s="5">
-        <v>2250.61</v>
-      </c>
-      <c r="E348" s="5">
-        <v>2250.61</v>
-      </c>
-      <c r="F348" s="5">
-        <v>2250.61</v>
+        <v>186</v>
+      </c>
+      <c r="D348" s="6">
+        <v>303.25</v>
+      </c>
+      <c r="E348" s="6">
+        <v>303.25</v>
+      </c>
+      <c r="F348" s="6">
+        <v>303.25</v>
       </c>
     </row>
     <row r="349" spans="1:6">
       <c r="A349" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B349" s="7">
-        <v>9657</v>
-      </c>
-      <c r="C349" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D349" s="6">
-        <v>303.25</v>
-      </c>
-      <c r="E349" s="6">
-        <v>303.25</v>
-      </c>
-      <c r="F349" s="6">
-        <v>303.25</v>
+        <v>461</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="D349" s="5">
+        <v>1170.74</v>
+      </c>
+      <c r="E349" s="5">
+        <v>1006.83</v>
+      </c>
+      <c r="F349" s="5">
+        <v>1006.83</v>
       </c>
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C350" s="4" t="s">
         <v>464</v>
       </c>
+      <c r="C350" s="3" t="s">
+        <v>465</v>
+      </c>
       <c r="D350" s="5">
-        <v>1170.74</v>
+        <v>1356.94</v>
       </c>
       <c r="E350" s="5">
-        <v>1006.83</v>
+        <v>1356.94</v>
       </c>
       <c r="F350" s="5">
-        <v>1006.83</v>
+        <v>1356.94</v>
       </c>
     </row>
     <row r="351" spans="1:6">
       <c r="A351" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>466</v>
+        <v>390</v>
       </c>
       <c r="D351" s="5">
-        <v>1356.94</v>
+        <v>1873.85</v>
       </c>
       <c r="E351" s="5">
-        <v>1356.94</v>
+        <v>1873.85</v>
       </c>
       <c r="F351" s="5">
-        <v>1356.94</v>
+        <v>1873.85</v>
       </c>
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>467</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D352" s="5">
-        <v>1873.85</v>
-      </c>
-      <c r="E352" s="5">
-        <v>1873.85</v>
-      </c>
-      <c r="F352" s="5">
-        <v>1873.85</v>
+        <v>185</v>
+      </c>
+      <c r="D352" s="6">
+        <v>188.76</v>
+      </c>
+      <c r="E352" s="6">
+        <v>188.76</v>
+      </c>
+      <c r="F352" s="6">
+        <v>188.76</v>
       </c>
     </row>
     <row r="353" spans="1:6">
       <c r="A353" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>468</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D353" s="6">
-        <v>188.76</v>
-      </c>
-      <c r="E353" s="6">
-        <v>188.76</v>
-      </c>
-      <c r="F353" s="6">
-        <v>188.76</v>
+        <v>372</v>
+      </c>
+      <c r="D353" s="5">
+        <v>1565.58</v>
+      </c>
+      <c r="E353" s="5">
+        <v>1565.58</v>
+      </c>
+      <c r="F353" s="5">
+        <v>1565.58</v>
       </c>
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C354" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="D354" s="5">
-        <v>1565.58</v>
-      </c>
-      <c r="E354" s="5">
-        <v>1565.58</v>
-      </c>
-      <c r="F354" s="5">
-        <v>1565.58</v>
+        <v>470</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D354" s="6">
+        <v>502.35</v>
+      </c>
+      <c r="E354" s="6">
+        <v>359.26</v>
+      </c>
+      <c r="F354" s="6">
+        <v>359.26</v>
       </c>
     </row>
     <row r="355" spans="1:6">
       <c r="A355" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>471</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>369</v>
+        <v>308</v>
       </c>
       <c r="D355" s="6">
-        <v>502.35</v>
+        <v>117.98</v>
       </c>
       <c r="E355" s="6">
-        <v>359.26</v>
+        <v>117.98</v>
       </c>
       <c r="F355" s="6">
-        <v>359.26</v>
+        <v>117.98</v>
       </c>
     </row>
     <row r="356" spans="1:6">
       <c r="A356" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>309</v>
+        <v>368</v>
       </c>
       <c r="D356" s="6">
-        <v>117.98</v>
+        <v>360.44</v>
       </c>
       <c r="E356" s="6">
-        <v>117.98</v>
+        <v>360.44</v>
       </c>
       <c r="F356" s="6">
-        <v>117.98</v>
+        <v>360.44</v>
       </c>
     </row>
     <row r="357" spans="1:6">
       <c r="A357" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>474</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="D357" s="6">
-        <v>360.44</v>
+        <v>315.98</v>
       </c>
       <c r="E357" s="6">
-        <v>360.44</v>
+        <v>315.98</v>
       </c>
       <c r="F357" s="6">
-        <v>360.44</v>
+        <v>315.98</v>
       </c>
     </row>
     <row r="358" spans="1:6">
       <c r="A358" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B358" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="C358" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="D358" s="6">
-        <v>315.98</v>
-      </c>
-      <c r="E358" s="6">
-        <v>315.98</v>
-      </c>
-      <c r="F358" s="6">
-        <v>315.98</v>
+        <v>472</v>
+      </c>
+      <c r="B358" s="7">
+        <v>9601</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D358" s="5">
+        <v>1012.32</v>
+      </c>
+      <c r="E358" s="5">
+        <v>1012.32</v>
+      </c>
+      <c r="F358" s="5">
+        <v>1012.32</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="A359" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B359" s="7">
-        <v>9601</v>
-      </c>
-      <c r="C359" s="3" t="s">
-        <v>64</v>
+        <v>475</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="D359" s="5">
-        <v>1012.32</v>
-      </c>
-      <c r="E359" s="5">
-        <v>1012.32</v>
-      </c>
-      <c r="F359" s="5">
-        <v>1012.32</v>
+        <v>1854.68</v>
+      </c>
+      <c r="E359" s="6">
+        <v>598.82000000000005</v>
+      </c>
+      <c r="F359" s="6">
+        <v>598.82000000000005</v>
       </c>
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="D360" s="5">
-        <v>1854.68</v>
+        <v>479</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D360" s="6">
+        <v>631.80999999999995</v>
       </c>
       <c r="E360" s="6">
-        <v>598.82000000000005</v>
+        <v>631.80999999999995</v>
       </c>
       <c r="F360" s="6">
-        <v>598.82000000000005</v>
+        <v>631.80999999999995</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>480</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D361" s="6">
-        <v>631.80999999999995</v>
-      </c>
-      <c r="E361" s="6">
-        <v>631.80999999999995</v>
-      </c>
-      <c r="F361" s="6">
-        <v>631.80999999999995</v>
+        <v>30</v>
+      </c>
+      <c r="D361" s="5">
+        <v>1167.58</v>
+      </c>
+      <c r="E361" s="5">
+        <v>1167.58</v>
+      </c>
+      <c r="F361" s="5">
+        <v>1167.58</v>
       </c>
     </row>
     <row r="362" spans="1:6">
       <c r="A362" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B362" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
+      </c>
+      <c r="B362" s="7">
+        <v>9679</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D362" s="5">
-        <v>1167.58</v>
-      </c>
-      <c r="E362" s="5">
-        <v>1167.58</v>
-      </c>
-      <c r="F362" s="5">
-        <v>1167.58</v>
+        <v>18</v>
+      </c>
+      <c r="D362" s="6">
+        <v>599.91</v>
+      </c>
+      <c r="E362" s="6">
+        <v>599.91</v>
+      </c>
+      <c r="F362" s="6">
+        <v>599.91</v>
       </c>
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B363" s="7">
-        <v>9679</v>
+        <v>481</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>482</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D363" s="6">
-        <v>599.91</v>
-      </c>
-      <c r="E363" s="6">
-        <v>599.91</v>
-      </c>
-      <c r="F363" s="6">
-        <v>599.91</v>
+        <v>116</v>
+      </c>
+      <c r="D363" s="5">
+        <v>7003.29</v>
+      </c>
+      <c r="E363" s="5">
+        <v>5000</v>
+      </c>
+      <c r="F363" s="5">
+        <v>5000</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B364" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="C364" s="3" t="s">
-        <v>116</v>
+        <v>481</v>
+      </c>
+      <c r="B364" s="7">
+        <v>9692</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>315</v>
       </c>
       <c r="D364" s="5">
-        <v>7003.29</v>
+        <v>7482.55</v>
       </c>
       <c r="E364" s="5">
-        <v>5000</v>
+        <v>7482.55</v>
       </c>
       <c r="F364" s="5">
-        <v>5000</v>
+        <v>7482.55</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B365" s="7">
-        <v>9692</v>
-      </c>
-      <c r="C365" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D365" s="5">
-        <v>7482.55</v>
-      </c>
-      <c r="E365" s="5">
-        <v>7482.55</v>
-      </c>
-      <c r="F365" s="5">
-        <v>7482.55</v>
+        <v>483</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C365" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D365" s="6">
+        <v>261.86</v>
+      </c>
+      <c r="E365" s="6">
+        <v>-848.73</v>
+      </c>
+      <c r="F365" s="6">
+        <v>-848.73</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B366" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C366" s="3" t="s">
-        <v>373</v>
+        <v>483</v>
+      </c>
+      <c r="B366" s="7">
+        <v>9691</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>315</v>
       </c>
       <c r="D366" s="6">
-        <v>261.86</v>
+        <v>444.05</v>
       </c>
       <c r="E366" s="6">
-        <v>-848.73</v>
+        <v>444.05</v>
       </c>
       <c r="F366" s="6">
-        <v>-848.73</v>
+        <v>444.05</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B367" s="7">
-        <v>9691</v>
+        <v>485</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>486</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="D367" s="6">
-        <v>444.05</v>
+        <v>920.54</v>
       </c>
       <c r="E367" s="6">
-        <v>444.05</v>
+        <v>817.92</v>
       </c>
       <c r="F367" s="6">
-        <v>444.05</v>
+        <v>817.92</v>
       </c>
     </row>
     <row r="368" spans="1:6">
       <c r="A368" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B368" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>299</v>
+        <v>485</v>
+      </c>
+      <c r="B368" s="7">
+        <v>9607</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D368" s="6">
-        <v>920.54</v>
+        <v>253.83</v>
       </c>
       <c r="E368" s="6">
-        <v>817.92</v>
+        <v>253.83</v>
       </c>
       <c r="F368" s="6">
-        <v>817.92</v>
+        <v>253.83</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B369" s="7">
-        <v>9607</v>
+        <v>9616</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>16</v>
+        <v>329</v>
       </c>
       <c r="D369" s="6">
-        <v>253.83</v>
+        <v>348.09</v>
       </c>
       <c r="E369" s="6">
-        <v>253.83</v>
+        <v>348.09</v>
       </c>
       <c r="F369" s="6">
-        <v>253.83</v>
+        <v>348.09</v>
       </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B370" s="7">
-        <v>9616</v>
-      </c>
-      <c r="C370" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D370" s="6">
-        <v>348.09</v>
-      </c>
-      <c r="E370" s="6">
-        <v>348.09</v>
-      </c>
-      <c r="F370" s="6">
-        <v>348.09</v>
+        <v>9693</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D370" s="5">
+        <v>1647.63</v>
+      </c>
+      <c r="E370" s="5">
+        <v>1647.63</v>
+      </c>
+      <c r="F370" s="5">
+        <v>1647.63</v>
       </c>
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B371" s="7">
-        <v>9693</v>
-      </c>
-      <c r="C371" s="4" t="s">
-        <v>316</v>
+        <v>487</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="D371" s="5">
-        <v>1647.63</v>
+        <v>6600.83</v>
       </c>
       <c r="E371" s="5">
-        <v>1647.63</v>
+        <v>6553.85</v>
       </c>
       <c r="F371" s="5">
-        <v>1647.63</v>
+        <v>6553.85</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C372" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D372" s="5">
-        <v>6600.83</v>
-      </c>
-      <c r="E372" s="5">
-        <v>6553.85</v>
-      </c>
-      <c r="F372" s="5">
-        <v>6553.85</v>
+      <c r="C372" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D372" s="6">
+        <v>377.52</v>
+      </c>
+      <c r="E372" s="6">
+        <v>377.52</v>
+      </c>
+      <c r="F372" s="6">
+        <v>377.52</v>
       </c>
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C373" s="4" t="s">
-        <v>411</v>
+      <c r="C373" s="3" t="s">
+        <v>260</v>
       </c>
       <c r="D373" s="6">
-        <v>377.52</v>
+        <v>188.76</v>
       </c>
       <c r="E373" s="6">
-        <v>377.52</v>
+        <v>188.76</v>
       </c>
       <c r="F373" s="6">
-        <v>377.52</v>
+        <v>188.76</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C374" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D374" s="6">
-        <v>188.76</v>
-      </c>
-      <c r="E374" s="6">
-        <v>188.76</v>
-      </c>
-      <c r="F374" s="6">
-        <v>188.76</v>
+      <c r="C374" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D374" s="5">
+        <v>6789.59</v>
+      </c>
+      <c r="E374" s="5">
+        <v>6789.59</v>
+      </c>
+      <c r="F374" s="5">
+        <v>6789.59</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B375" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C375" s="4" t="s">
-        <v>318</v>
+        <v>487</v>
+      </c>
+      <c r="B375" s="7">
+        <v>9597</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="D375" s="5">
-        <v>6789.59</v>
+        <v>7272.38</v>
       </c>
       <c r="E375" s="5">
-        <v>6789.59</v>
+        <v>7272.38</v>
       </c>
       <c r="F375" s="5">
-        <v>6789.59</v>
+        <v>7272.38</v>
       </c>
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B376" s="7">
-        <v>9597</v>
+        <v>216</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="D376" s="5">
-        <v>7272.38</v>
+        <v>1551.24</v>
       </c>
       <c r="E376" s="5">
-        <v>7272.38</v>
+        <v>1551.24</v>
       </c>
       <c r="F376" s="5">
-        <v>7272.38</v>
+        <v>1551.24</v>
       </c>
     </row>
     <row r="377" spans="1:6">
@@ -10082,17 +10079,17 @@
       <c r="B377" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C377" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D377" s="5">
-        <v>1551.24</v>
-      </c>
-      <c r="E377" s="5">
-        <v>1551.24</v>
-      </c>
-      <c r="F377" s="5">
-        <v>1551.24</v>
+      <c r="C377" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D377" s="6">
+        <v>685.68</v>
+      </c>
+      <c r="E377" s="6">
+        <v>685.68</v>
+      </c>
+      <c r="F377" s="6">
+        <v>685.68</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -10103,201 +10100,201 @@
         <v>494</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D378" s="6">
-        <v>685.68</v>
-      </c>
-      <c r="E378" s="6">
-        <v>685.68</v>
-      </c>
-      <c r="F378" s="6">
-        <v>685.68</v>
+        <v>298</v>
+      </c>
+      <c r="D378" s="5">
+        <v>2524.5100000000002</v>
+      </c>
+      <c r="E378" s="5">
+        <v>2524.5100000000002</v>
+      </c>
+      <c r="F378" s="5">
+        <v>2524.5100000000002</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
-        <v>216</v>
+        <v>495</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D379" s="5">
-        <v>2524.5100000000002</v>
-      </c>
-      <c r="E379" s="5">
-        <v>2524.5100000000002</v>
-      </c>
-      <c r="F379" s="5">
-        <v>2524.5100000000002</v>
+        <v>368</v>
+      </c>
+      <c r="D379" s="6">
+        <v>631.74</v>
+      </c>
+      <c r="E379" s="6">
+        <v>631.74</v>
+      </c>
+      <c r="F379" s="6">
+        <v>631.74</v>
       </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>497</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="D380" s="6">
-        <v>631.74</v>
+        <v>692.41</v>
       </c>
       <c r="E380" s="6">
-        <v>631.74</v>
+        <v>692.41</v>
       </c>
       <c r="F380" s="6">
-        <v>631.74</v>
+        <v>692.41</v>
       </c>
     </row>
     <row r="381" spans="1:6">
       <c r="A381" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B381" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C381" s="4" t="s">
-        <v>387</v>
+        <v>495</v>
+      </c>
+      <c r="B381" s="7">
+        <v>9606</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="D381" s="6">
-        <v>692.41</v>
+        <v>-60.79</v>
       </c>
       <c r="E381" s="6">
-        <v>692.41</v>
+        <v>-60.79</v>
       </c>
       <c r="F381" s="6">
-        <v>692.41</v>
+        <v>-60.79</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B382" s="7">
-        <v>9606</v>
+        <v>498</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D382" s="6">
-        <v>-60.79</v>
-      </c>
-      <c r="E382" s="6">
-        <v>-60.79</v>
-      </c>
-      <c r="F382" s="6">
-        <v>-60.79</v>
+        <v>82</v>
+      </c>
+      <c r="D382" s="5">
+        <v>1401.95</v>
+      </c>
+      <c r="E382" s="5">
+        <v>1401.95</v>
+      </c>
+      <c r="F382" s="5">
+        <v>1401.95</v>
       </c>
     </row>
     <row r="383" spans="1:6">
       <c r="A383" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="B383" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
+      </c>
+      <c r="B383" s="7">
+        <v>9640</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="D383" s="5">
-        <v>1401.95</v>
+        <v>2527.83</v>
       </c>
       <c r="E383" s="5">
-        <v>1401.95</v>
+        <v>2527.83</v>
       </c>
       <c r="F383" s="5">
-        <v>1401.95</v>
+        <v>2527.83</v>
       </c>
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="B384" s="7">
-        <v>9640</v>
+        <v>500</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>501</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>388</v>
+        <v>502</v>
       </c>
       <c r="D384" s="5">
-        <v>2527.83</v>
-      </c>
-      <c r="E384" s="5">
-        <v>2527.83</v>
-      </c>
-      <c r="F384" s="5">
-        <v>2527.83</v>
+        <v>4118.0200000000004</v>
+      </c>
+      <c r="E384" s="6">
+        <v>697.98</v>
+      </c>
+      <c r="F384" s="6">
+        <v>697.98</v>
       </c>
     </row>
     <row r="385" spans="1:6">
       <c r="A385" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>503</v>
+        <v>424</v>
       </c>
       <c r="D385" s="5">
-        <v>4118.0200000000004</v>
-      </c>
-      <c r="E385" s="6">
-        <v>697.98</v>
-      </c>
-      <c r="F385" s="6">
-        <v>697.98</v>
+        <v>1893.12</v>
+      </c>
+      <c r="E385" s="5">
+        <v>1893.12</v>
+      </c>
+      <c r="F385" s="5">
+        <v>1893.12</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>504</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D386" s="5">
-        <v>1893.12</v>
-      </c>
-      <c r="E386" s="5">
-        <v>1893.12</v>
-      </c>
-      <c r="F386" s="5">
-        <v>1893.12</v>
+        <v>5</v>
+      </c>
+      <c r="D386" s="6">
+        <v>473.16</v>
+      </c>
+      <c r="E386" s="6">
+        <v>473.16</v>
+      </c>
+      <c r="F386" s="6">
+        <v>473.16</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>505</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D387" s="6">
-        <v>473.16</v>
-      </c>
-      <c r="E387" s="6">
-        <v>473.16</v>
-      </c>
-      <c r="F387" s="6">
-        <v>473.16</v>
+        <v>116</v>
+      </c>
+      <c r="D387" s="5">
+        <v>1150.99</v>
+      </c>
+      <c r="E387" s="5">
+        <v>1150.99</v>
+      </c>
+      <c r="F387" s="5">
+        <v>1150.99</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>506</v>
@@ -10305,485 +10302,485 @@
       <c r="C388" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D388" s="5">
-        <v>1150.99</v>
-      </c>
-      <c r="E388" s="5">
-        <v>1150.99</v>
-      </c>
-      <c r="F388" s="5">
-        <v>1150.99</v>
+      <c r="D388" s="6">
+        <v>981.71</v>
+      </c>
+      <c r="E388" s="6">
+        <v>981.71</v>
+      </c>
+      <c r="F388" s="6">
+        <v>981.71</v>
       </c>
     </row>
     <row r="389" spans="1:6">
       <c r="A389" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C389" s="3" t="s">
-        <v>116</v>
+      <c r="C389" s="4" t="s">
+        <v>317</v>
       </c>
       <c r="D389" s="6">
-        <v>981.71</v>
+        <v>109.38</v>
       </c>
       <c r="E389" s="6">
-        <v>981.71</v>
+        <v>109.38</v>
       </c>
       <c r="F389" s="6">
-        <v>981.71</v>
+        <v>109.38</v>
       </c>
     </row>
     <row r="390" spans="1:6">
       <c r="A390" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>508</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D390" s="6">
-        <v>109.38</v>
+        <v>981.71</v>
       </c>
       <c r="E390" s="6">
-        <v>109.38</v>
+        <v>981.71</v>
       </c>
       <c r="F390" s="6">
-        <v>109.38</v>
+        <v>981.71</v>
       </c>
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="2" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D391" s="6">
-        <v>981.71</v>
-      </c>
-      <c r="E391" s="6">
-        <v>981.71</v>
-      </c>
-      <c r="F391" s="6">
-        <v>981.71</v>
+        <v>511</v>
+      </c>
+      <c r="D391" s="5">
+        <v>36000</v>
+      </c>
+      <c r="E391" s="5">
+        <v>16800</v>
+      </c>
+      <c r="F391" s="5">
+        <v>16800</v>
       </c>
     </row>
     <row r="392" spans="1:6">
       <c r="A392" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="C392" s="4" t="s">
         <v>512</v>
       </c>
+      <c r="C392" s="3" t="s">
+        <v>513</v>
+      </c>
       <c r="D392" s="5">
-        <v>36000</v>
-      </c>
-      <c r="E392" s="5">
-        <v>16800</v>
-      </c>
-      <c r="F392" s="5">
-        <v>16800</v>
+        <v>1072.2</v>
+      </c>
+      <c r="E392" s="6">
+        <v>594.21</v>
+      </c>
+      <c r="F392" s="6">
+        <v>594.21</v>
       </c>
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B393" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C393" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C393" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D393" s="5">
-        <v>1072.2</v>
+      <c r="D393" s="6">
+        <v>416.84</v>
       </c>
       <c r="E393" s="6">
-        <v>594.21</v>
+        <v>416.84</v>
       </c>
       <c r="F393" s="6">
-        <v>594.21</v>
+        <v>416.84</v>
       </c>
     </row>
     <row r="394" spans="1:6">
       <c r="A394" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>515</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D394" s="6">
-        <v>416.84</v>
+        <v>729.12</v>
       </c>
       <c r="E394" s="6">
-        <v>416.84</v>
+        <v>729.12</v>
       </c>
       <c r="F394" s="6">
-        <v>416.84</v>
+        <v>729.12</v>
       </c>
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>517</v>
+        <v>352</v>
       </c>
       <c r="D395" s="6">
-        <v>729.12</v>
+        <v>356.73</v>
       </c>
       <c r="E395" s="6">
-        <v>729.12</v>
+        <v>356.73</v>
       </c>
       <c r="F395" s="6">
-        <v>729.12</v>
+        <v>356.73</v>
       </c>
     </row>
     <row r="396" spans="1:6">
       <c r="A396" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>518</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>353</v>
+        <v>519</v>
       </c>
       <c r="D396" s="6">
-        <v>356.73</v>
+        <v>651.4</v>
       </c>
       <c r="E396" s="6">
-        <v>356.73</v>
+        <v>651.4</v>
       </c>
       <c r="F396" s="6">
-        <v>356.73</v>
+        <v>651.4</v>
       </c>
     </row>
     <row r="397" spans="1:6">
       <c r="A397" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="C397" s="3" t="s">
         <v>520</v>
       </c>
+      <c r="C397" s="4" t="s">
+        <v>358</v>
+      </c>
       <c r="D397" s="6">
-        <v>651.4</v>
+        <v>764.3</v>
       </c>
       <c r="E397" s="6">
-        <v>651.4</v>
+        <v>764.3</v>
       </c>
       <c r="F397" s="6">
-        <v>651.4</v>
+        <v>764.3</v>
       </c>
     </row>
     <row r="398" spans="1:6">
       <c r="A398" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="C398" s="4" t="s">
-        <v>359</v>
+      <c r="C398" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="D398" s="6">
-        <v>764.3</v>
+        <v>729.12</v>
       </c>
       <c r="E398" s="6">
-        <v>764.3</v>
+        <v>729.12</v>
       </c>
       <c r="F398" s="6">
-        <v>764.3</v>
+        <v>729.12</v>
       </c>
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B399" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C399" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C399" s="3" t="s">
-        <v>523</v>
-      </c>
       <c r="D399" s="6">
-        <v>729.12</v>
+        <v>216.35</v>
       </c>
       <c r="E399" s="6">
-        <v>729.12</v>
+        <v>216.35</v>
       </c>
       <c r="F399" s="6">
-        <v>729.12</v>
+        <v>216.35</v>
       </c>
     </row>
     <row r="400" spans="1:6">
       <c r="A400" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>524</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D400" s="6">
-        <v>216.35</v>
+        <v>597.20000000000005</v>
       </c>
       <c r="E400" s="6">
-        <v>216.35</v>
+        <v>597.20000000000005</v>
       </c>
       <c r="F400" s="6">
-        <v>216.35</v>
+        <v>597.20000000000005</v>
       </c>
     </row>
     <row r="401" spans="1:6">
       <c r="A401" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="D401" s="6">
-        <v>597.20000000000005</v>
-      </c>
-      <c r="E401" s="6">
-        <v>597.20000000000005</v>
-      </c>
-      <c r="F401" s="6">
-        <v>597.20000000000005</v>
+        <v>527</v>
+      </c>
+      <c r="D401" s="5">
+        <v>5600.79</v>
+      </c>
+      <c r="E401" s="5">
+        <v>5600.79</v>
+      </c>
+      <c r="F401" s="5">
+        <v>5600.79</v>
       </c>
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C402" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D402" s="5">
-        <v>5600.79</v>
-      </c>
-      <c r="E402" s="5">
-        <v>5600.79</v>
-      </c>
-      <c r="F402" s="5">
-        <v>5600.79</v>
+      <c r="C402" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D402" s="6">
+        <v>652.29999999999995</v>
+      </c>
+      <c r="E402" s="6">
+        <v>652.29999999999995</v>
+      </c>
+      <c r="F402" s="6">
+        <v>652.29999999999995</v>
       </c>
     </row>
     <row r="403" spans="1:6">
       <c r="A403" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C403" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D403" s="6">
-        <v>652.29999999999995</v>
-      </c>
-      <c r="E403" s="6">
-        <v>652.29999999999995</v>
-      </c>
-      <c r="F403" s="6">
-        <v>652.29999999999995</v>
+      <c r="C403" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D403" s="5">
+        <v>2042.43</v>
+      </c>
+      <c r="E403" s="5">
+        <v>2042.43</v>
+      </c>
+      <c r="F403" s="5">
+        <v>2042.43</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C404" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D404" s="5">
-        <v>2042.43</v>
-      </c>
-      <c r="E404" s="5">
-        <v>2042.43</v>
-      </c>
-      <c r="F404" s="5">
-        <v>2042.43</v>
+      <c r="C404" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="D404" s="6">
+        <v>870.5</v>
+      </c>
+      <c r="E404" s="6">
+        <v>870.5</v>
+      </c>
+      <c r="F404" s="6">
+        <v>870.5</v>
       </c>
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B405" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C405" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C405" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="D405" s="6">
-        <v>870.5</v>
-      </c>
-      <c r="E405" s="6">
-        <v>870.5</v>
-      </c>
-      <c r="F405" s="6">
-        <v>870.5</v>
+      <c r="D405" s="5">
+        <v>1009.8</v>
+      </c>
+      <c r="E405" s="5">
+        <v>1009.8</v>
+      </c>
+      <c r="F405" s="5">
+        <v>1009.8</v>
       </c>
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C406" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="D406" s="5">
-        <v>1009.8</v>
-      </c>
-      <c r="E406" s="5">
-        <v>1009.8</v>
-      </c>
-      <c r="F406" s="5">
-        <v>1009.8</v>
+      <c r="C406" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D406" s="6">
+        <v>870.5</v>
+      </c>
+      <c r="E406" s="6">
+        <v>870.5</v>
+      </c>
+      <c r="F406" s="6">
+        <v>870.5</v>
       </c>
     </row>
     <row r="407" spans="1:6">
       <c r="A407" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C407" s="3" t="s">
         <v>537</v>
       </c>
+      <c r="C407" s="4" t="s">
+        <v>538</v>
+      </c>
       <c r="D407" s="6">
-        <v>870.5</v>
+        <v>596.72</v>
       </c>
       <c r="E407" s="6">
-        <v>870.5</v>
+        <v>596.72</v>
       </c>
       <c r="F407" s="6">
-        <v>870.5</v>
+        <v>596.72</v>
       </c>
     </row>
     <row r="408" spans="1:6">
       <c r="A408" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C408" s="4" t="s">
         <v>539</v>
       </c>
+      <c r="C408" s="3" t="s">
+        <v>540</v>
+      </c>
       <c r="D408" s="6">
-        <v>596.72</v>
+        <v>736.72</v>
       </c>
       <c r="E408" s="6">
-        <v>596.72</v>
+        <v>736.72</v>
       </c>
       <c r="F408" s="6">
-        <v>596.72</v>
+        <v>736.72</v>
       </c>
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D409" s="6">
-        <v>736.72</v>
+        <v>716.1</v>
       </c>
       <c r="E409" s="6">
-        <v>736.72</v>
+        <v>716.1</v>
       </c>
       <c r="F409" s="6">
-        <v>736.72</v>
+        <v>716.1</v>
       </c>
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="C410" s="3" t="s">
         <v>543</v>
       </c>
+      <c r="C410" s="4" t="s">
+        <v>544</v>
+      </c>
       <c r="D410" s="6">
-        <v>716.1</v>
+        <v>564.66</v>
       </c>
       <c r="E410" s="6">
-        <v>716.1</v>
+        <v>564.66</v>
       </c>
       <c r="F410" s="6">
-        <v>716.1</v>
+        <v>564.66</v>
       </c>
     </row>
     <row r="411" spans="1:6">
       <c r="A411" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C411" s="4" t="s">
         <v>545</v>
       </c>
+      <c r="C411" s="3" t="s">
+        <v>546</v>
+      </c>
       <c r="D411" s="6">
-        <v>564.66</v>
+        <v>898.02</v>
       </c>
       <c r="E411" s="6">
-        <v>564.66</v>
+        <v>898.02</v>
       </c>
       <c r="F411" s="6">
-        <v>564.66</v>
+        <v>898.02</v>
       </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D412" s="6">
         <v>898.02</v>
@@ -10797,1142 +10794,1142 @@
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C413" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D413" s="6">
-        <v>898.02</v>
+        <v>651.29999999999995</v>
       </c>
       <c r="E413" s="6">
-        <v>898.02</v>
+        <v>651.29999999999995</v>
       </c>
       <c r="F413" s="6">
-        <v>898.02</v>
+        <v>651.29999999999995</v>
       </c>
     </row>
     <row r="414" spans="1:6">
       <c r="A414" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="D414" s="6">
-        <v>651.29999999999995</v>
-      </c>
-      <c r="E414" s="6">
-        <v>651.29999999999995</v>
-      </c>
-      <c r="F414" s="6">
-        <v>651.29999999999995</v>
+        <v>5</v>
+      </c>
+      <c r="D414" s="5">
+        <v>-36000</v>
+      </c>
+      <c r="E414" s="5">
+        <v>-36000</v>
+      </c>
+      <c r="F414" s="5">
+        <v>-36000</v>
       </c>
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="2" t="s">
-        <v>510</v>
+        <v>552</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D415" s="5">
-        <v>-36000</v>
-      </c>
-      <c r="E415" s="5">
-        <v>-36000</v>
-      </c>
-      <c r="F415" s="5">
-        <v>-36000</v>
+        <v>325</v>
+      </c>
+      <c r="D415" s="6">
+        <v>235.95</v>
+      </c>
+      <c r="E415" s="6">
+        <v>142.72999999999999</v>
+      </c>
+      <c r="F415" s="6">
+        <v>142.72999999999999</v>
       </c>
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C416" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D416" s="6">
-        <v>235.95</v>
-      </c>
-      <c r="E416" s="6">
-        <v>142.72999999999999</v>
-      </c>
-      <c r="F416" s="6">
-        <v>142.72999999999999</v>
+        <v>556</v>
+      </c>
+      <c r="D416" s="5">
+        <v>9512.7099999999991</v>
+      </c>
+      <c r="E416" s="5">
+        <v>1107.6400000000001</v>
+      </c>
+      <c r="F416" s="5">
+        <v>1107.6400000000001</v>
       </c>
     </row>
     <row r="417" spans="1:6">
       <c r="A417" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C417" s="3" t="s">
         <v>557</v>
       </c>
+      <c r="C417" s="4" t="s">
+        <v>558</v>
+      </c>
       <c r="D417" s="5">
-        <v>9512.7099999999991</v>
+        <v>6835.49</v>
       </c>
       <c r="E417" s="5">
-        <v>1107.6400000000001</v>
+        <v>6835.49</v>
       </c>
       <c r="F417" s="5">
-        <v>1107.6400000000001</v>
+        <v>6835.49</v>
       </c>
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="C418" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="D418" s="5">
-        <v>6835.49</v>
-      </c>
-      <c r="E418" s="5">
-        <v>6835.49</v>
-      </c>
-      <c r="F418" s="5">
-        <v>6835.49</v>
+      <c r="C418" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D418" s="6">
+        <v>374.52</v>
+      </c>
+      <c r="E418" s="6">
+        <v>374.52</v>
+      </c>
+      <c r="F418" s="6">
+        <v>374.52</v>
       </c>
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C419" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="D419" s="6">
-        <v>374.52</v>
-      </c>
-      <c r="E419" s="6">
-        <v>374.52</v>
-      </c>
-      <c r="F419" s="6">
-        <v>374.52</v>
+      <c r="C419" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D419" s="5">
+        <v>10694.76</v>
+      </c>
+      <c r="E419" s="5">
+        <v>10694.76</v>
+      </c>
+      <c r="F419" s="5">
+        <v>10694.76</v>
       </c>
     </row>
     <row r="420" spans="1:6">
       <c r="A420" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B420" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="C420" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="D420" s="5">
-        <v>10694.76</v>
-      </c>
-      <c r="E420" s="5">
-        <v>10694.76</v>
-      </c>
-      <c r="F420" s="5">
-        <v>10694.76</v>
+        <v>554</v>
+      </c>
+      <c r="B420" s="7">
+        <v>9603</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D420" s="6">
+        <v>647.5</v>
+      </c>
+      <c r="E420" s="6">
+        <v>647.5</v>
+      </c>
+      <c r="F420" s="6">
+        <v>647.5</v>
       </c>
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B421" s="7">
-        <v>9603</v>
+        <v>9604</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D421" s="6">
-        <v>647.5</v>
-      </c>
-      <c r="E421" s="6">
-        <v>647.5</v>
-      </c>
-      <c r="F421" s="6">
-        <v>647.5</v>
+      <c r="D421" s="5">
+        <v>14078.93</v>
+      </c>
+      <c r="E421" s="5">
+        <v>14078.93</v>
+      </c>
+      <c r="F421" s="5">
+        <v>14078.93</v>
       </c>
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B422" s="7">
-        <v>9604</v>
+        <v>563</v>
+      </c>
+      <c r="B422" s="3" t="s">
+        <v>564</v>
       </c>
       <c r="C422" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D422" s="5">
-        <v>14078.93</v>
-      </c>
-      <c r="E422" s="5">
-        <v>14078.93</v>
-      </c>
-      <c r="F422" s="5">
-        <v>14078.93</v>
+        <v>260</v>
+      </c>
+      <c r="D422" s="6">
+        <v>337.41</v>
+      </c>
+      <c r="E422" s="6">
+        <v>337.41</v>
+      </c>
+      <c r="F422" s="6">
+        <v>337.41</v>
       </c>
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="C423" s="3" t="s">
-        <v>260</v>
+      <c r="C423" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="D423" s="6">
-        <v>337.41</v>
+        <v>235.95</v>
       </c>
       <c r="E423" s="6">
-        <v>337.41</v>
+        <v>235.95</v>
       </c>
       <c r="F423" s="6">
-        <v>337.41</v>
+        <v>235.95</v>
       </c>
     </row>
     <row r="424" spans="1:6">
       <c r="A424" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="C424" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D424" s="6">
-        <v>235.95</v>
-      </c>
-      <c r="E424" s="6">
-        <v>235.95</v>
-      </c>
-      <c r="F424" s="6">
-        <v>235.95</v>
+        <v>567</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D424" s="5">
+        <v>10808.11</v>
+      </c>
+      <c r="E424" s="5">
+        <v>3879.17</v>
+      </c>
+      <c r="F424" s="5">
+        <v>3879.17</v>
       </c>
     </row>
     <row r="425" spans="1:6">
       <c r="A425" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="C425" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="D425" s="5">
-        <v>10808.11</v>
-      </c>
-      <c r="E425" s="5">
-        <v>3879.17</v>
-      </c>
-      <c r="F425" s="5">
-        <v>3879.17</v>
+      <c r="C425" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D425" s="6">
+        <v>589.9</v>
+      </c>
+      <c r="E425" s="6">
+        <v>589.9</v>
+      </c>
+      <c r="F425" s="6">
+        <v>589.9</v>
       </c>
     </row>
     <row r="426" spans="1:6">
       <c r="A426" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="C426" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D426" s="6">
-        <v>589.9</v>
-      </c>
-      <c r="E426" s="6">
-        <v>589.9</v>
-      </c>
-      <c r="F426" s="6">
-        <v>589.9</v>
+      <c r="C426" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D426" s="5">
+        <v>1565.3</v>
+      </c>
+      <c r="E426" s="5">
+        <v>1565.3</v>
+      </c>
+      <c r="F426" s="5">
+        <v>1565.3</v>
       </c>
     </row>
     <row r="427" spans="1:6">
       <c r="A427" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>570</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D427" s="5">
-        <v>1565.3</v>
-      </c>
-      <c r="E427" s="5">
-        <v>1565.3</v>
-      </c>
-      <c r="F427" s="5">
-        <v>1565.3</v>
+        <v>365</v>
+      </c>
+      <c r="D427" s="6">
+        <v>752.71</v>
+      </c>
+      <c r="E427" s="6">
+        <v>752.71</v>
+      </c>
+      <c r="F427" s="6">
+        <v>752.71</v>
       </c>
     </row>
     <row r="428" spans="1:6">
       <c r="A428" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B428" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="C428" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D428" s="6">
-        <v>752.71</v>
-      </c>
-      <c r="E428" s="6">
-        <v>752.71</v>
-      </c>
-      <c r="F428" s="6">
-        <v>752.71</v>
+        <v>566</v>
+      </c>
+      <c r="B428" s="7">
+        <v>9695</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D428" s="5">
+        <v>9180.86</v>
+      </c>
+      <c r="E428" s="5">
+        <v>9180.86</v>
+      </c>
+      <c r="F428" s="5">
+        <v>9180.86</v>
       </c>
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B429" s="7">
-        <v>9695</v>
-      </c>
-      <c r="C429" s="4" t="s">
-        <v>316</v>
+        <v>571</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="D429" s="5">
-        <v>9180.86</v>
+        <v>2956.69</v>
       </c>
       <c r="E429" s="5">
-        <v>9180.86</v>
+        <v>1146.3599999999999</v>
       </c>
       <c r="F429" s="5">
-        <v>9180.86</v>
+        <v>1146.3599999999999</v>
       </c>
     </row>
     <row r="430" spans="1:6">
       <c r="A430" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D430" s="5">
-        <v>2956.69</v>
+        <v>2684.64</v>
       </c>
       <c r="E430" s="5">
-        <v>1146.3599999999999</v>
+        <v>2684.64</v>
       </c>
       <c r="F430" s="5">
-        <v>1146.3599999999999</v>
+        <v>2684.64</v>
       </c>
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>575</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D431" s="5">
-        <v>2684.64</v>
-      </c>
-      <c r="E431" s="5">
-        <v>2684.64</v>
-      </c>
-      <c r="F431" s="5">
-        <v>2684.64</v>
+        <v>129</v>
+      </c>
+      <c r="D431" s="6">
+        <v>980.1</v>
+      </c>
+      <c r="E431" s="6">
+        <v>980.1</v>
+      </c>
+      <c r="F431" s="6">
+        <v>980.1</v>
       </c>
     </row>
     <row r="432" spans="1:6">
       <c r="A432" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="C432" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D432" s="6">
-        <v>980.1</v>
-      </c>
-      <c r="E432" s="6">
-        <v>980.1</v>
-      </c>
-      <c r="F432" s="6">
-        <v>980.1</v>
+      <c r="C432" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D432" s="5">
+        <v>1837.63</v>
+      </c>
+      <c r="E432" s="5">
+        <v>1837.63</v>
+      </c>
+      <c r="F432" s="5">
+        <v>1837.63</v>
       </c>
     </row>
     <row r="433" spans="1:6">
       <c r="A433" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>577</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D433" s="5">
-        <v>1837.63</v>
-      </c>
-      <c r="E433" s="5">
-        <v>1837.63</v>
-      </c>
-      <c r="F433" s="5">
-        <v>1837.63</v>
+        <v>386</v>
+      </c>
+      <c r="D433" s="6">
+        <v>270.92</v>
+      </c>
+      <c r="E433" s="6">
+        <v>270.92</v>
+      </c>
+      <c r="F433" s="6">
+        <v>270.92</v>
       </c>
     </row>
     <row r="434" spans="1:6">
       <c r="A434" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="B434" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="C434" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B434" s="7">
+        <v>9638</v>
+      </c>
+      <c r="C434" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D434" s="6">
-        <v>270.92</v>
-      </c>
-      <c r="E434" s="6">
-        <v>270.92</v>
-      </c>
-      <c r="F434" s="6">
-        <v>270.92</v>
+      <c r="D434" s="5">
+        <v>1830.78</v>
+      </c>
+      <c r="E434" s="5">
+        <v>1830.78</v>
+      </c>
+      <c r="F434" s="5">
+        <v>1830.78</v>
       </c>
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B435" s="7">
-        <v>9638</v>
+        <v>9675</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>388</v>
+        <v>18</v>
       </c>
       <c r="D435" s="5">
-        <v>1830.78</v>
+        <v>3221.21</v>
       </c>
       <c r="E435" s="5">
-        <v>1830.78</v>
+        <v>3221.21</v>
       </c>
       <c r="F435" s="5">
-        <v>1830.78</v>
+        <v>3221.21</v>
       </c>
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="B436" s="7">
-        <v>9675</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D436" s="5">
-        <v>3221.21</v>
-      </c>
-      <c r="E436" s="5">
-        <v>3221.21</v>
-      </c>
-      <c r="F436" s="5">
-        <v>3221.21</v>
+        <v>578</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D436" s="6">
+        <v>829.15</v>
+      </c>
+      <c r="E436" s="6">
+        <v>264.02999999999997</v>
+      </c>
+      <c r="F436" s="6">
+        <v>264.02999999999997</v>
       </c>
     </row>
     <row r="437" spans="1:6">
       <c r="A437" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="C437" s="4" t="s">
         <v>581</v>
       </c>
+      <c r="C437" s="3" t="s">
+        <v>582</v>
+      </c>
       <c r="D437" s="6">
-        <v>829.15</v>
+        <v>569.84</v>
       </c>
       <c r="E437" s="6">
-        <v>264.02999999999997</v>
+        <v>569.84</v>
       </c>
       <c r="F437" s="6">
-        <v>264.02999999999997</v>
+        <v>569.84</v>
       </c>
     </row>
     <row r="438" spans="1:6">
       <c r="A438" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C438" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D438" s="6">
-        <v>569.84</v>
+        <v>211.45</v>
       </c>
       <c r="E438" s="6">
-        <v>569.84</v>
+        <v>211.45</v>
       </c>
       <c r="F438" s="6">
-        <v>569.84</v>
+        <v>211.45</v>
       </c>
     </row>
     <row r="439" spans="1:6">
       <c r="A439" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D439" s="6">
-        <v>211.45</v>
+        <v>92.34</v>
       </c>
       <c r="E439" s="6">
-        <v>211.45</v>
+        <v>92.34</v>
       </c>
       <c r="F439" s="6">
-        <v>211.45</v>
+        <v>92.34</v>
       </c>
     </row>
     <row r="440" spans="1:6">
       <c r="A440" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D440" s="6">
-        <v>92.34</v>
+        <v>318.69</v>
       </c>
       <c r="E440" s="6">
-        <v>92.34</v>
+        <v>318.69</v>
       </c>
       <c r="F440" s="6">
-        <v>92.34</v>
+        <v>318.69</v>
       </c>
     </row>
     <row r="441" spans="1:6">
       <c r="A441" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B441" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C441" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="C441" s="3" t="s">
-        <v>589</v>
-      </c>
       <c r="D441" s="6">
-        <v>318.69</v>
+        <v>501.26</v>
       </c>
       <c r="E441" s="6">
-        <v>318.69</v>
+        <v>501.26</v>
       </c>
       <c r="F441" s="6">
-        <v>318.69</v>
+        <v>501.26</v>
       </c>
     </row>
     <row r="442" spans="1:6">
       <c r="A442" s="2" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>592</v>
       </c>
       <c r="D442" s="6">
-        <v>501.26</v>
+        <v>798.91</v>
       </c>
       <c r="E442" s="6">
-        <v>501.26</v>
+        <v>711.16</v>
       </c>
       <c r="F442" s="6">
-        <v>501.26</v>
+        <v>711.16</v>
       </c>
     </row>
     <row r="443" spans="1:6">
       <c r="A443" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C443" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="D443" s="6">
-        <v>798.91</v>
-      </c>
-      <c r="E443" s="6">
-        <v>711.16</v>
-      </c>
-      <c r="F443" s="6">
-        <v>711.16</v>
+      <c r="C443" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D443" s="5">
+        <v>3028.65</v>
+      </c>
+      <c r="E443" s="5">
+        <v>3028.65</v>
+      </c>
+      <c r="F443" s="5">
+        <v>3028.65</v>
       </c>
     </row>
     <row r="444" spans="1:6">
       <c r="A444" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>594</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D444" s="5">
-        <v>3028.65</v>
-      </c>
-      <c r="E444" s="5">
-        <v>3028.65</v>
-      </c>
-      <c r="F444" s="5">
-        <v>3028.65</v>
+        <v>112</v>
+      </c>
+      <c r="D444" s="6">
+        <v>323.57</v>
+      </c>
+      <c r="E444" s="6">
+        <v>323.57</v>
+      </c>
+      <c r="F444" s="6">
+        <v>323.57</v>
       </c>
     </row>
     <row r="445" spans="1:6">
       <c r="A445" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C445" s="3" t="s">
-        <v>112</v>
+      <c r="C445" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="D445" s="6">
-        <v>323.57</v>
+        <v>401.14</v>
       </c>
       <c r="E445" s="6">
-        <v>323.57</v>
+        <v>401.14</v>
       </c>
       <c r="F445" s="6">
-        <v>323.57</v>
+        <v>401.14</v>
       </c>
     </row>
     <row r="446" spans="1:6">
       <c r="A446" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="C446" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="D446" s="6">
-        <v>401.14</v>
-      </c>
-      <c r="E446" s="6">
-        <v>401.14</v>
-      </c>
-      <c r="F446" s="6">
-        <v>401.14</v>
+      <c r="C446" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D446" s="5">
+        <v>1047.43</v>
+      </c>
+      <c r="E446" s="5">
+        <v>1047.43</v>
+      </c>
+      <c r="F446" s="5">
+        <v>1047.43</v>
       </c>
     </row>
     <row r="447" spans="1:6">
       <c r="A447" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>597</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="D447" s="5">
-        <v>1047.43</v>
-      </c>
-      <c r="E447" s="5">
-        <v>1047.43</v>
-      </c>
-      <c r="F447" s="5">
-        <v>1047.43</v>
+        <v>77</v>
+      </c>
+      <c r="D447" s="6">
+        <v>759.09</v>
+      </c>
+      <c r="E447" s="6">
+        <v>759.09</v>
+      </c>
+      <c r="F447" s="6">
+        <v>759.09</v>
       </c>
     </row>
     <row r="448" spans="1:6">
       <c r="A448" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>598</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D448" s="6">
-        <v>759.09</v>
-      </c>
-      <c r="E448" s="6">
-        <v>759.09</v>
-      </c>
-      <c r="F448" s="6">
-        <v>759.09</v>
+        <v>334</v>
+      </c>
+      <c r="D448" s="5">
+        <v>2374.58</v>
+      </c>
+      <c r="E448" s="5">
+        <v>2374.58</v>
+      </c>
+      <c r="F448" s="5">
+        <v>2374.58</v>
       </c>
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="C449" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D449" s="5">
-        <v>2374.58</v>
-      </c>
-      <c r="E449" s="5">
-        <v>2374.58</v>
-      </c>
-      <c r="F449" s="5">
-        <v>2374.58</v>
+      <c r="C449" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="D449" s="6">
+        <v>337.92</v>
+      </c>
+      <c r="E449" s="6">
+        <v>337.92</v>
+      </c>
+      <c r="F449" s="6">
+        <v>337.92</v>
       </c>
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="B450" s="3" t="s">
-        <v>600</v>
+        <v>590</v>
+      </c>
+      <c r="B450" s="7">
+        <v>9694</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D450" s="6">
-        <v>337.92</v>
-      </c>
-      <c r="E450" s="6">
-        <v>337.92</v>
-      </c>
-      <c r="F450" s="6">
-        <v>337.92</v>
+        <v>315</v>
+      </c>
+      <c r="D450" s="5">
+        <v>1420.5</v>
+      </c>
+      <c r="E450" s="5">
+        <v>1420.5</v>
+      </c>
+      <c r="F450" s="5">
+        <v>1420.5</v>
       </c>
     </row>
     <row r="451" spans="1:6">
       <c r="A451" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="B451" s="7">
-        <v>9694</v>
+        <v>600</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D451" s="5">
-        <v>1420.5</v>
+        <v>5995.83</v>
       </c>
       <c r="E451" s="5">
-        <v>1420.5</v>
+        <v>2477.12</v>
       </c>
       <c r="F451" s="5">
-        <v>1420.5</v>
+        <v>2477.12</v>
       </c>
     </row>
     <row r="452" spans="1:6">
       <c r="A452" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C452" s="4" t="s">
-        <v>320</v>
+      <c r="C452" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="D452" s="5">
-        <v>5995.83</v>
+        <v>2526.5300000000002</v>
       </c>
       <c r="E452" s="5">
-        <v>2477.12</v>
+        <v>2526.5300000000002</v>
       </c>
       <c r="F452" s="5">
-        <v>2477.12</v>
+        <v>2526.5300000000002</v>
       </c>
     </row>
     <row r="453" spans="1:6">
       <c r="A453" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>603</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>326</v>
+        <v>260</v>
       </c>
       <c r="D453" s="5">
-        <v>2526.5300000000002</v>
+        <v>1992.95</v>
       </c>
       <c r="E453" s="5">
-        <v>2526.5300000000002</v>
+        <v>1992.95</v>
       </c>
       <c r="F453" s="5">
-        <v>2526.5300000000002</v>
+        <v>1992.95</v>
       </c>
     </row>
     <row r="454" spans="1:6">
       <c r="A454" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>604</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>260</v>
+        <v>334</v>
       </c>
       <c r="D454" s="5">
-        <v>1992.95</v>
+        <v>1550.83</v>
       </c>
       <c r="E454" s="5">
-        <v>1992.95</v>
+        <v>1550.83</v>
       </c>
       <c r="F454" s="5">
-        <v>1992.95</v>
+        <v>1550.83</v>
       </c>
     </row>
     <row r="455" spans="1:6">
       <c r="A455" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>605</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D455" s="5">
-        <v>1550.83</v>
-      </c>
-      <c r="E455" s="5">
-        <v>1550.83</v>
-      </c>
-      <c r="F455" s="5">
-        <v>1550.83</v>
+        <v>365</v>
+      </c>
+      <c r="D455" s="6">
+        <v>188.76</v>
+      </c>
+      <c r="E455" s="6">
+        <v>188.76</v>
+      </c>
+      <c r="F455" s="6">
+        <v>188.76</v>
       </c>
     </row>
     <row r="456" spans="1:6">
       <c r="A456" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>606</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>366</v>
+        <v>129</v>
       </c>
       <c r="D456" s="6">
-        <v>188.76</v>
+        <v>532.1</v>
       </c>
       <c r="E456" s="6">
-        <v>188.76</v>
+        <v>532.1</v>
       </c>
       <c r="F456" s="6">
-        <v>188.76</v>
+        <v>532.1</v>
       </c>
     </row>
     <row r="457" spans="1:6">
       <c r="A457" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C457" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D457" s="6">
-        <v>532.1</v>
-      </c>
-      <c r="E457" s="6">
-        <v>532.1</v>
-      </c>
-      <c r="F457" s="6">
-        <v>532.1</v>
+      <c r="C457" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D457" s="5">
+        <v>2047.91</v>
+      </c>
+      <c r="E457" s="5">
+        <v>2047.91</v>
+      </c>
+      <c r="F457" s="5">
+        <v>2047.91</v>
       </c>
     </row>
     <row r="458" spans="1:6">
       <c r="A458" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>608</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D458" s="5">
-        <v>2047.91</v>
+        <v>1436.76</v>
       </c>
       <c r="E458" s="5">
-        <v>2047.91</v>
+        <v>1436.76</v>
       </c>
       <c r="F458" s="5">
-        <v>2047.91</v>
+        <v>1436.76</v>
       </c>
     </row>
     <row r="459" spans="1:6">
       <c r="A459" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B459" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="C459" s="4" t="s">
-        <v>299</v>
+        <v>600</v>
+      </c>
+      <c r="B459" s="7">
+        <v>9620</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="D459" s="5">
-        <v>1436.76</v>
+        <v>2452.62</v>
       </c>
       <c r="E459" s="5">
-        <v>1436.76</v>
+        <v>2452.62</v>
       </c>
       <c r="F459" s="5">
-        <v>1436.76</v>
+        <v>2452.62</v>
       </c>
     </row>
     <row r="460" spans="1:6">
       <c r="A460" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B460" s="7">
-        <v>9620</v>
-      </c>
-      <c r="C460" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D460" s="5">
-        <v>2452.62</v>
-      </c>
-      <c r="E460" s="5">
-        <v>2452.62</v>
-      </c>
-      <c r="F460" s="5">
-        <v>2452.62</v>
+        <v>9698</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D460" s="6">
+        <v>802.82</v>
+      </c>
+      <c r="E460" s="6">
+        <v>802.82</v>
+      </c>
+      <c r="F460" s="6">
+        <v>802.82</v>
       </c>
     </row>
     <row r="461" spans="1:6">
       <c r="A461" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B461" s="7">
-        <v>9698</v>
+        <v>609</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>610</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D461" s="6">
-        <v>802.82</v>
+        <v>580</v>
+      </c>
+      <c r="D461" s="5">
+        <v>3470.57</v>
       </c>
       <c r="E461" s="6">
-        <v>802.82</v>
+        <v>10.98</v>
       </c>
       <c r="F461" s="6">
-        <v>802.82</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="462" spans="1:6">
       <c r="A462" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="D462" s="5">
-        <v>3470.57</v>
+        <v>562</v>
+      </c>
+      <c r="D462" s="6">
+        <v>963.9</v>
       </c>
       <c r="E462" s="6">
-        <v>10.98</v>
+        <v>842.43</v>
       </c>
       <c r="F462" s="6">
-        <v>10.98</v>
+        <v>842.43</v>
       </c>
     </row>
     <row r="463" spans="1:6">
       <c r="A463" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="D463" s="6">
-        <v>963.9</v>
-      </c>
-      <c r="E463" s="6">
-        <v>842.43</v>
-      </c>
-      <c r="F463" s="6">
-        <v>842.43</v>
+        <v>615</v>
+      </c>
+      <c r="D463" s="5">
+        <v>2732.17</v>
+      </c>
+      <c r="E463" s="5">
+        <v>1732.17</v>
+      </c>
+      <c r="F463" s="5">
+        <v>1732.17</v>
       </c>
     </row>
     <row r="464" spans="1:6">
       <c r="A464" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="C464" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="D464" s="5">
-        <v>2732.17</v>
-      </c>
-      <c r="E464" s="5">
-        <v>1732.17</v>
-      </c>
-      <c r="F464" s="5">
-        <v>1732.17</v>
+      <c r="C464" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D464" s="6">
+        <v>956.4</v>
+      </c>
+      <c r="E464" s="6">
+        <v>956.4</v>
+      </c>
+      <c r="F464" s="6">
+        <v>956.4</v>
       </c>
     </row>
     <row r="465" spans="1:6">
       <c r="A465" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C465" s="3" t="s">
-        <v>618</v>
+        <v>188</v>
       </c>
       <c r="D465" s="6">
-        <v>956.4</v>
+        <v>680.06</v>
       </c>
       <c r="E465" s="6">
-        <v>956.4</v>
+        <v>680.06</v>
       </c>
       <c r="F465" s="6">
-        <v>956.4</v>
+        <v>680.06</v>
       </c>
     </row>
     <row r="466" spans="1:6">
       <c r="A466" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B466" s="3" t="s">
-        <v>620</v>
+        <v>39</v>
+      </c>
+      <c r="B466" s="7">
+        <v>9635</v>
       </c>
       <c r="C466" s="3" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="D466" s="6">
-        <v>680.06</v>
+        <v>317.23</v>
       </c>
       <c r="E466" s="6">
-        <v>680.06</v>
+        <v>317.23</v>
       </c>
       <c r="F466" s="6">
-        <v>680.06</v>
+        <v>317.23</v>
       </c>
     </row>
     <row r="467" spans="1:6">
       <c r="A467" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B467" s="7">
-        <v>9635</v>
+        <v>620</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>621</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D467" s="6">
-        <v>317.23</v>
-      </c>
-      <c r="E467" s="6">
-        <v>317.23</v>
-      </c>
-      <c r="F467" s="6">
-        <v>317.23</v>
+        <v>162</v>
+      </c>
+      <c r="D467" s="5">
+        <v>2486.83</v>
+      </c>
+      <c r="E467" s="5">
+        <v>2486.83</v>
+      </c>
+      <c r="F467" s="5">
+        <v>2486.83</v>
       </c>
     </row>
     <row r="468" spans="1:6">
       <c r="A468" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>622</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="D468" s="5">
-        <v>2486.83</v>
+        <v>4991.01</v>
       </c>
       <c r="E468" s="5">
-        <v>2486.83</v>
+        <v>4991.01</v>
       </c>
       <c r="F468" s="5">
-        <v>2486.83</v>
+        <v>4991.01</v>
       </c>
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="2" t="s">
-        <v>621</v>
+        <v>138</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>623</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>191</v>
+        <v>624</v>
       </c>
       <c r="D469" s="5">
-        <v>4991.01</v>
+        <v>6232.46</v>
       </c>
       <c r="E469" s="5">
-        <v>4991.01</v>
+        <v>6232.46</v>
       </c>
       <c r="F469" s="5">
-        <v>4991.01</v>
+        <v>6232.46</v>
       </c>
     </row>
     <row r="470" spans="1:6">
@@ -11940,39 +11937,39 @@
         <v>138</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="C470" s="3" t="s">
         <v>625</v>
       </c>
+      <c r="C470" s="4" t="s">
+        <v>422</v>
+      </c>
       <c r="D470" s="5">
-        <v>6232.46</v>
+        <v>9370.36</v>
       </c>
       <c r="E470" s="5">
-        <v>6232.46</v>
+        <v>9370.36</v>
       </c>
       <c r="F470" s="5">
-        <v>6232.46</v>
+        <v>9370.36</v>
       </c>
     </row>
     <row r="471" spans="1:6">
       <c r="A471" s="2" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="C471" s="4" t="s">
-        <v>423</v>
+      <c r="C471" s="3" t="s">
+        <v>627</v>
       </c>
       <c r="D471" s="5">
-        <v>9370.36</v>
+        <v>2931.2</v>
       </c>
       <c r="E471" s="5">
-        <v>9370.36</v>
+        <v>2931.2</v>
       </c>
       <c r="F471" s="5">
-        <v>9370.36</v>
+        <v>2931.2</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -11980,19 +11977,19 @@
         <v>272</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D472" s="5">
-        <v>2931.2</v>
+        <v>2741.2</v>
       </c>
       <c r="E472" s="5">
-        <v>2931.2</v>
+        <v>2741.2</v>
       </c>
       <c r="F472" s="5">
-        <v>2931.2</v>
+        <v>2741.2</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -12000,19 +11997,19 @@
         <v>272</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D473" s="5">
-        <v>2741.2</v>
+        <v>3087.07</v>
       </c>
       <c r="E473" s="5">
-        <v>2741.2</v>
+        <v>3087.07</v>
       </c>
       <c r="F473" s="5">
-        <v>2741.2</v>
+        <v>3087.07</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -12020,19 +12017,19 @@
         <v>272</v>
       </c>
       <c r="B474" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="C474" s="3" t="s">
         <v>632</v>
       </c>
+      <c r="C474" s="4" t="s">
+        <v>633</v>
+      </c>
       <c r="D474" s="5">
-        <v>3087.07</v>
+        <v>2201.4</v>
       </c>
       <c r="E474" s="5">
-        <v>3087.07</v>
+        <v>2201.4</v>
       </c>
       <c r="F474" s="5">
-        <v>3087.07</v>
+        <v>2201.4</v>
       </c>
     </row>
     <row r="475" spans="1:6">
@@ -12040,118 +12037,98 @@
         <v>272</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>634</v>
+        <v>400</v>
       </c>
       <c r="D475" s="5">
-        <v>2201.4</v>
+        <v>2741.2</v>
       </c>
       <c r="E475" s="5">
-        <v>2201.4</v>
+        <v>2741.2</v>
       </c>
       <c r="F475" s="5">
-        <v>2201.4</v>
+        <v>2741.2</v>
       </c>
     </row>
     <row r="476" spans="1:6">
       <c r="A476" s="2" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>635</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>401</v>
+        <v>636</v>
       </c>
       <c r="D476" s="5">
-        <v>2741.2</v>
+        <v>1469.88</v>
       </c>
       <c r="E476" s="5">
-        <v>2741.2</v>
+        <v>1469.88</v>
       </c>
       <c r="F476" s="5">
-        <v>2741.2</v>
+        <v>1469.88</v>
       </c>
     </row>
     <row r="477" spans="1:6">
       <c r="A477" s="2" t="s">
-        <v>280</v>
+        <v>637</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D477" s="5">
-        <v>1469.88</v>
+        <v>1128.3</v>
       </c>
       <c r="E477" s="5">
-        <v>1469.88</v>
+        <v>1128.3</v>
       </c>
       <c r="F477" s="5">
-        <v>1469.88</v>
+        <v>1128.3</v>
       </c>
     </row>
     <row r="478" spans="1:6">
       <c r="A478" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="C478" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="D478" s="5">
-        <v>1128.3</v>
-      </c>
-      <c r="E478" s="5">
-        <v>1128.3</v>
-      </c>
-      <c r="F478" s="5">
-        <v>1128.3</v>
+        <v>641</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D478" s="6">
+        <v>628.79999999999995</v>
+      </c>
+      <c r="E478" s="6">
+        <v>262.77999999999997</v>
+      </c>
+      <c r="F478" s="6">
+        <v>262.77999999999997</v>
       </c>
     </row>
     <row r="479" spans="1:6">
       <c r="A479" s="2" t="s">
-        <v>641</v>
+        <v>272</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="D479" s="6">
-        <v>628.79999999999995</v>
-      </c>
-      <c r="E479" s="6">
-        <v>262.77999999999997</v>
-      </c>
-      <c r="F479" s="6">
-        <v>262.77999999999997</v>
-      </c>
-    </row>
-    <row r="480" spans="1:6">
-      <c r="A480" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B480" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="C480" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="D480" s="5">
+      <c r="D479" s="5">
         <v>2644.48</v>
       </c>
-      <c r="E480" s="5">
+      <c r="E479" s="5">
         <v>2644.48</v>
       </c>
-      <c r="F480" s="5">
+      <c r="F479" s="5">
         <v>2644.48</v>
       </c>
     </row>
